--- a/database/event/2062/event_2062_evp_summary.xlsx
+++ b/database/event/2062/event_2062_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.579</v>
+        <v>8.643800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>5.453</v>
+        <v>6.2191</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6404</v>
+        <v>2.9998</v>
       </c>
       <c r="E2" t="n">
-        <v>7.579</v>
+        <v>8.643800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.646</v>
+        <v>2.7108</v>
       </c>
       <c r="G2" t="n">
         <v>5.933</v>
       </c>
       <c r="H2" t="n">
-        <v>1.646</v>
+        <v>2.7108</v>
       </c>
       <c r="I2" t="n">
-        <v>1.646</v>
+        <v>2.7108</v>
       </c>
       <c r="J2" t="n">
         <v>5.933</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.579</v>
+        <v>8.643799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>238</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3817</v>
+        <v>5.8166</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8721</v>
+        <v>4.185</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7527</v>
+        <v>1.8734</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3817</v>
+        <v>5.8166</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3623</v>
+        <v>2.6126</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0194</v>
+        <v>3.204</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3623</v>
+        <v>2.6126</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3733</v>
+        <v>2.6126</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0194</v>
+        <v>3.204</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L3" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3927</v>
+        <v>5.8166</v>
       </c>
       <c r="N3" t="n">
-        <v>280</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8264</v>
+        <v>5.4256</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4726</v>
+        <v>3.9037</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5284</v>
+        <v>1.7176</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8264</v>
+        <v>5.4256</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6224</v>
+        <v>2.4062</v>
       </c>
       <c r="G4" t="n">
-        <v>3.204</v>
+        <v>3.0194</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6224</v>
+        <v>2.4062</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6224</v>
+        <v>2.4264</v>
       </c>
       <c r="J4" t="n">
-        <v>3.204</v>
+        <v>3.0194</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8264</v>
+        <v>5.4458</v>
       </c>
       <c r="N4" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.539</v>
+        <v>4.5316</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2658</v>
+        <v>3.2605</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4123</v>
+        <v>1.3615</v>
       </c>
       <c r="E5" t="n">
-        <v>4.539</v>
+        <v>4.5316</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9925</v>
+        <v>1.9851</v>
       </c>
       <c r="G5" t="n">
         <v>2.5465</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9925</v>
+        <v>1.9851</v>
       </c>
       <c r="I5" t="n">
         <v>2.0018</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3443</v>
+        <v>4.5288</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1257</v>
+        <v>3.2584</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3336</v>
+        <v>1.3604</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3443</v>
+        <v>4.5288</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4185</v>
+        <v>2.6577</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9258</v>
+        <v>1.8711</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4185</v>
+        <v>2.6577</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4185</v>
+        <v>2.6801</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9258</v>
+        <v>1.8711</v>
       </c>
       <c r="K6" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3443</v>
+        <v>4.5512</v>
       </c>
       <c r="N6" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.186</v>
+        <v>4.4841</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0118</v>
+        <v>3.2263</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2697</v>
+        <v>1.3426</v>
       </c>
       <c r="E7" t="n">
-        <v>4.186</v>
+        <v>4.4841</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4906</v>
+        <v>1.5583</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6954</v>
+        <v>2.9258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4906</v>
+        <v>1.5583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4906</v>
+        <v>1.5583</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6954</v>
+        <v>2.9258</v>
       </c>
       <c r="K7" t="n">
         <v>49</v>
@@ -759,7 +759,7 @@
         <v>189</v>
       </c>
       <c r="M7" t="n">
-        <v>4.186</v>
+        <v>4.4841</v>
       </c>
       <c r="N7" t="n">
         <v>238</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9897</v>
+        <v>4.186</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8706</v>
+        <v>3.0118</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1904</v>
+        <v>1.2238</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9897</v>
+        <v>4.186</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1186</v>
+        <v>0.4906</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8711</v>
+        <v>3.6954</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1186</v>
+        <v>0.4906</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1285</v>
+        <v>0.4906</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8711</v>
+        <v>3.6954</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9996</v>
+        <v>4.186</v>
       </c>
       <c r="N8" t="n">
-        <v>280</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.828</v>
+        <v>3.9563</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7542</v>
+        <v>2.8465</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1251</v>
+        <v>1.1323</v>
       </c>
       <c r="E9" t="n">
-        <v>3.828</v>
+        <v>3.9563</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9117</v>
+        <v>2.6973</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9162</v>
+        <v>1.259</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9117</v>
+        <v>2.6973</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9206</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9162</v>
+        <v>1.259</v>
       </c>
       <c r="K9" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="L9" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8368</v>
+        <v>3.979</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6993</v>
+        <v>3.8399</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6616</v>
+        <v>2.7628</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0731</v>
+        <v>1.0859</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6993</v>
+        <v>3.8399</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4403</v>
+        <v>1.9237</v>
       </c>
       <c r="G10" t="n">
-        <v>1.259</v>
+        <v>1.9162</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4403</v>
+        <v>1.9237</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4516</v>
+        <v>1.9399</v>
       </c>
       <c r="J10" t="n">
-        <v>1.259</v>
+        <v>1.9162</v>
       </c>
       <c r="K10" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="L10" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7106</v>
+        <v>3.8561</v>
       </c>
       <c r="N10" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8297</v>
+        <v>2.8246</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0359</v>
+        <v>2.0323</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7218</v>
+        <v>0.6814</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8297</v>
+        <v>2.8246</v>
       </c>
       <c r="F11" t="n">
-        <v>1.363</v>
+        <v>1.3579</v>
       </c>
       <c r="G11" t="n">
         <v>1.4667</v>
       </c>
       <c r="H11" t="n">
-        <v>1.363</v>
+        <v>1.3579</v>
       </c>
       <c r="I11" t="n">
         <v>1.3693</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.798</v>
+        <v>2.7969</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0131</v>
+        <v>2.0123</v>
       </c>
       <c r="D12" t="n">
-        <v>0.709</v>
+        <v>0.6704</v>
       </c>
       <c r="E12" t="n">
-        <v>2.798</v>
+        <v>2.7969</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2917</v>
+        <v>0.2907</v>
       </c>
       <c r="G12" t="n">
         <v>2.5063</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2917</v>
+        <v>0.2907</v>
       </c>
       <c r="I12" t="n">
         <v>0.2931</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4727</v>
+        <v>2.4649</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7791</v>
+        <v>1.7735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5776</v>
+        <v>0.5381</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4727</v>
+        <v>2.4649</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0981</v>
+        <v>2.0903</v>
       </c>
       <c r="G13" t="n">
         <v>0.3746</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0981</v>
+        <v>2.0903</v>
       </c>
       <c r="I13" t="n">
         <v>2.1079</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0323</v>
+        <v>2.2225</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4622</v>
+        <v>1.5991</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3996</v>
+        <v>0.4415</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0323</v>
+        <v>2.2225</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6922</v>
+        <v>0.8824</v>
       </c>
       <c r="G14" t="n">
         <v>1.3401</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6922</v>
+        <v>0.8824</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6922</v>
+        <v>0.8824</v>
       </c>
       <c r="J14" t="n">
         <v>1.3401</v>
@@ -1081,7 +1081,7 @@
         <v>189</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0323</v>
+        <v>2.2225</v>
       </c>
       <c r="N14" t="n">
         <v>238</v>
@@ -1090,725 +1090,725 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9353</v>
+        <v>2.1351</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3924</v>
+        <v>1.5362</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3605</v>
+        <v>0.4067</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9353</v>
+        <v>2.1351</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5229</v>
+        <v>2.2684</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4124</v>
+        <v>-0.1333</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5229</v>
+        <v>2.2684</v>
       </c>
       <c r="I15" t="n">
-        <v>1.53</v>
+        <v>2.2684</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4124</v>
+        <v>-0.1333</v>
       </c>
       <c r="K15" t="n">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9424</v>
+        <v>2.1351</v>
       </c>
       <c r="N15" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9011</v>
+        <v>2.1311</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3678</v>
+        <v>1.5333</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3466</v>
+        <v>0.4051</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9011</v>
+        <v>2.1311</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2445</v>
+        <v>2.4412</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6566</v>
+        <v>-0.3101</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2445</v>
+        <v>2.4412</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2445</v>
+        <v>2.4618</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6566</v>
+        <v>-0.3101</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="L16" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9011</v>
+        <v>2.1517</v>
       </c>
       <c r="N16" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7621</v>
+        <v>1.9723</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2678</v>
+        <v>1.4191</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2905</v>
+        <v>0.3419</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7621</v>
+        <v>1.9723</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0722</v>
+        <v>2.0928</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3101</v>
+        <v>-0.1205</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0722</v>
+        <v>2.0928</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0819</v>
+        <v>2.0928</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3101</v>
+        <v>-0.1205</v>
       </c>
       <c r="K17" t="n">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7718</v>
+        <v>1.9723</v>
       </c>
       <c r="N17" t="n">
-        <v>186</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6819</v>
+        <v>1.9451</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2101</v>
+        <v>1.3995</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2581</v>
+        <v>0.331</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6819</v>
+        <v>1.9451</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9879</v>
+        <v>1.2885</v>
       </c>
       <c r="G18" t="n">
-        <v>0.694</v>
+        <v>0.6566</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9879</v>
+        <v>1.2885</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9925</v>
+        <v>1.2885</v>
       </c>
       <c r="J18" t="n">
-        <v>0.694</v>
+        <v>0.6566</v>
       </c>
       <c r="K18" t="n">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6865</v>
+        <v>1.9451</v>
       </c>
       <c r="N18" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5403</v>
+        <v>1.9296</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1082</v>
+        <v>1.3883</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2009</v>
+        <v>0.3248</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5403</v>
+        <v>1.9296</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7447</v>
+        <v>1.5172</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7956</v>
+        <v>0.4124</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7447</v>
+        <v>1.5172</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7482</v>
+        <v>1.53</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7956</v>
+        <v>0.4124</v>
       </c>
       <c r="K19" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="L19" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5438</v>
+        <v>1.9424</v>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4638</v>
+        <v>1.7337</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0532</v>
+        <v>1.2474</v>
       </c>
       <c r="D20" t="n">
-        <v>0.17</v>
+        <v>0.2468</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4638</v>
+        <v>1.7337</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5843</v>
+        <v>1.7337</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1205</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5843</v>
+        <v>1.7337</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5843</v>
+        <v>1.7337</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1205</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="L20" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4638</v>
+        <v>1.7337</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4316</v>
+        <v>1.6782</v>
       </c>
       <c r="C21" t="n">
-        <v>1.03</v>
+        <v>1.2075</v>
       </c>
       <c r="D21" t="n">
-        <v>0.157</v>
+        <v>0.2247</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4316</v>
+        <v>1.6782</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5649</v>
+        <v>0.9842</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1333</v>
+        <v>0.694</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5649</v>
+        <v>0.9842</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5649</v>
+        <v>0.9925</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1333</v>
+        <v>0.694</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="L21" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4316</v>
+        <v>1.6865</v>
       </c>
       <c r="N21" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4064</v>
+        <v>1.5376</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0119</v>
+        <v>1.1063</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1468</v>
+        <v>0.1687</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4064</v>
+        <v>1.5376</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3073</v>
+        <v>0.742</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0991</v>
+        <v>0.7956</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3073</v>
+        <v>0.742</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3073</v>
+        <v>0.7482</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0991</v>
+        <v>0.7956</v>
       </c>
       <c r="K22" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="L22" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4064</v>
+        <v>1.5438</v>
       </c>
       <c r="N22" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3826</v>
+        <v>1.4764</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9948</v>
+        <v>1.0623</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1372</v>
+        <v>0.1443</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3826</v>
+        <v>1.4764</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3826</v>
+        <v>1.746</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.2696</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3826</v>
+        <v>1.746</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3826</v>
+        <v>1.746</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.2696</v>
       </c>
       <c r="K23" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3826</v>
+        <v>1.4764</v>
       </c>
       <c r="N23" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3078</v>
+        <v>1.4512</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.0441</v>
       </c>
       <c r="D24" t="n">
-        <v>0.107</v>
+        <v>0.1342</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3078</v>
+        <v>1.4512</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6015</v>
+        <v>2.1147</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2937</v>
+        <v>-0.6635</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6015</v>
+        <v>2.1147</v>
       </c>
       <c r="I24" t="n">
-        <v>1.609</v>
+        <v>2.1147</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2937</v>
+        <v>-0.6635</v>
       </c>
       <c r="K24" t="n">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3153</v>
+        <v>1.4512</v>
       </c>
       <c r="N24" t="n">
-        <v>186</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.2689</v>
+        <v>1.4064</v>
       </c>
       <c r="C25" t="n">
-        <v>0.913</v>
+        <v>1.0119</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0912</v>
+        <v>0.1164</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2689</v>
+        <v>1.4064</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2689</v>
+        <v>0.3073</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.0991</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2689</v>
+        <v>0.3073</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2689</v>
+        <v>0.3073</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.0991</v>
       </c>
       <c r="K25" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2689</v>
+        <v>1.4064</v>
       </c>
       <c r="N25" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.039</v>
+        <v>1.3709</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7476</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0016</v>
+        <v>0.1023</v>
       </c>
       <c r="E26" t="n">
-        <v>1.039</v>
+        <v>1.3709</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6566</v>
+        <v>1.3709</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6176</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6566</v>
+        <v>1.3709</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6643</v>
+        <v>1.3709</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6176</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0467</v>
+        <v>1.3709</v>
       </c>
       <c r="N26" t="n">
-        <v>211</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.0299</v>
+        <v>1.3378</v>
       </c>
       <c r="C27" t="n">
-        <v>0.741</v>
+        <v>0.9625</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0053</v>
+        <v>0.0891</v>
       </c>
       <c r="E27" t="n">
-        <v>1.0299</v>
+        <v>1.3378</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2995</v>
+        <v>1.3378</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2696</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2995</v>
+        <v>1.3378</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2995</v>
+        <v>1.3378</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2696</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="L27" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.0299</v>
+        <v>1.3378</v>
       </c>
       <c r="N27" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9462</v>
+        <v>1.3019</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6808</v>
+        <v>0.9367</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0391</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9462</v>
+        <v>1.3019</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3668</v>
+        <v>1.5956</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4206</v>
+        <v>-0.2937</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3668</v>
+        <v>1.5956</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3668</v>
+        <v>1.609</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4206</v>
+        <v>-0.2937</v>
       </c>
       <c r="K28" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="L28" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9462</v>
+        <v>1.3153</v>
       </c>
       <c r="N28" t="n">
-        <v>128</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.153</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6778</v>
+        <v>0.8296</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0408</v>
+        <v>0.0154</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.153</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7466</v>
+        <v>1.153</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1954</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7466</v>
+        <v>1.153</v>
       </c>
       <c r="I29" t="n">
-        <v>0.75</v>
+        <v>1.153</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1954</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="L29" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9454</v>
+        <v>1.153</v>
       </c>
       <c r="N29" t="n">
-        <v>211</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8465</v>
+        <v>1.1423</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6091</v>
+        <v>0.8219</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0794</v>
+        <v>0.0112</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8465</v>
+        <v>1.1423</v>
       </c>
       <c r="F30" t="n">
-        <v>1.51</v>
+        <v>2.1423</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6635</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>1.51</v>
+        <v>2.1423</v>
       </c>
       <c r="I30" t="n">
-        <v>1.51</v>
+        <v>2.1423</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6635</v>
+        <v>-1</v>
       </c>
       <c r="K30" t="n">
         <v>51</v>
@@ -1817,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8465</v>
+        <v>1.1423</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1826,262 +1826,262 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5808</v>
+        <v>0.8018</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8073</v>
+        <v>1.1144</v>
       </c>
       <c r="N31" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6536</v>
+        <v>1.0328</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4703</v>
+        <v>0.7431</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1573</v>
+        <v>-0.0324</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6536</v>
+        <v>1.0328</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6536</v>
+        <v>1.6504</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6176</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6536</v>
+        <v>1.6504</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6536</v>
+        <v>1.6643</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6176</v>
       </c>
       <c r="K32" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6536</v>
+        <v>1.0467</v>
       </c>
       <c r="N32" t="n">
-        <v>103</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6213</v>
+        <v>0.9883</v>
       </c>
       <c r="C33" t="n">
-        <v>0.447</v>
+        <v>0.7111</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1704</v>
+        <v>-0.0502</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6213</v>
+        <v>0.9883</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6213</v>
+        <v>1.4089</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4206</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6213</v>
+        <v>1.4089</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6213</v>
+        <v>1.4089</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4206</v>
       </c>
       <c r="K33" t="n">
         <v>51</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6213</v>
+        <v>0.9883000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.594</v>
+        <v>0.9392</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4274</v>
+        <v>0.6757</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1814</v>
+        <v>-0.0697</v>
       </c>
       <c r="E34" t="n">
-        <v>0.594</v>
+        <v>0.9392</v>
       </c>
       <c r="F34" t="n">
-        <v>0.594</v>
+        <v>0.7438</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1954</v>
       </c>
       <c r="H34" t="n">
-        <v>0.594</v>
+        <v>0.7438</v>
       </c>
       <c r="I34" t="n">
-        <v>0.594</v>
+        <v>0.75</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.1954</v>
       </c>
       <c r="K34" t="n">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M34" t="n">
-        <v>0.594</v>
+        <v>0.9454</v>
       </c>
       <c r="N34" t="n">
-        <v>56</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.586</v>
+        <v>0.8073</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4216</v>
+        <v>0.5808</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1846</v>
+        <v>-0.1223</v>
       </c>
       <c r="E35" t="n">
-        <v>0.586</v>
+        <v>0.8073</v>
       </c>
       <c r="F35" t="n">
-        <v>1.586</v>
+        <v>0.8073</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.586</v>
+        <v>0.8073</v>
       </c>
       <c r="I35" t="n">
-        <v>1.586</v>
+        <v>0.8073</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5860000000000001</v>
+        <v>0.8073</v>
       </c>
       <c r="N35" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3992</v>
+        <v>0.5733</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1972</v>
+        <v>-0.1265</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5548</v>
+        <v>0.7968</v>
       </c>
       <c r="N36" t="n">
         <v>123</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3167</v>
+        <v>0.4703</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2435</v>
+        <v>-0.1835</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4402</v>
+        <v>0.6536</v>
       </c>
       <c r="N37" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4394</v>
+        <v>0.6213</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3161</v>
+        <v>0.447</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2439</v>
+        <v>-0.1964</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4394</v>
+        <v>0.6213</v>
       </c>
       <c r="F38" t="n">
-        <v>0.637</v>
+        <v>0.6213</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1976</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.637</v>
+        <v>0.6213</v>
       </c>
       <c r="I38" t="n">
-        <v>0.637</v>
+        <v>0.6213</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1976</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>51</v>
       </c>
       <c r="L38" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4394</v>
+        <v>0.6213</v>
       </c>
       <c r="N38" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.407</v>
+        <v>0.594</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2928</v>
+        <v>0.4274</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2569</v>
+        <v>-0.2073</v>
       </c>
       <c r="E39" t="n">
-        <v>0.407</v>
+        <v>0.594</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1894</v>
+        <v>0.594</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7824</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1894</v>
+        <v>0.594</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1894</v>
+        <v>0.594</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7824</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L39" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.407</v>
+        <v>0.594</v>
       </c>
       <c r="N39" t="n">
-        <v>209</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2802</v>
+        <v>0.3661</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2641</v>
+        <v>-0.2412</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3894</v>
+        <v>0.5089</v>
       </c>
       <c r="N40" t="n">
         <v>49</v>
@@ -2286,323 +2286,323 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.362</v>
+        <v>0.4419</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2605</v>
+        <v>0.3179</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2751</v>
+        <v>-0.2679</v>
       </c>
       <c r="E41" t="n">
-        <v>0.362</v>
+        <v>0.4419</v>
       </c>
       <c r="F41" t="n">
-        <v>0.362</v>
+        <v>0.6395</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.1976</v>
       </c>
       <c r="H41" t="n">
-        <v>0.362</v>
+        <v>0.6395</v>
       </c>
       <c r="I41" t="n">
-        <v>0.362</v>
+        <v>0.6395</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.1976</v>
       </c>
       <c r="K41" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M41" t="n">
-        <v>0.362</v>
+        <v>0.4419</v>
       </c>
       <c r="N41" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2458</v>
+        <v>0.4237</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1769</v>
+        <v>0.3048</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3221</v>
+        <v>-0.2751</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2458</v>
+        <v>0.4237</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2458</v>
+        <v>1.2061</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.7824</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2458</v>
+        <v>1.2061</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2458</v>
+        <v>1.2061</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.7824</v>
       </c>
       <c r="K42" t="n">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2458</v>
+        <v>0.4237</v>
       </c>
       <c r="N42" t="n">
-        <v>123</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="C43" t="n">
-        <v>0.171</v>
+        <v>0.2212</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3253</v>
+        <v>-0.3214</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2377</v>
+        <v>0.3074</v>
       </c>
       <c r="N43" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1691</v>
+        <v>0.2478</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1217</v>
+        <v>0.1783</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.353</v>
+        <v>-0.3452</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1691</v>
+        <v>0.2478</v>
       </c>
       <c r="F44" t="n">
-        <v>1.1691</v>
+        <v>0.2478</v>
       </c>
       <c r="G44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1691</v>
+        <v>0.2478</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1745</v>
+        <v>0.2478</v>
       </c>
       <c r="J44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="L44" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1745000000000001</v>
+        <v>0.2478</v>
       </c>
       <c r="N44" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0958</v>
+        <v>0.1647</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0689</v>
+        <v>0.1185</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3827</v>
+        <v>-0.3783</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0958</v>
+        <v>0.1647</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0958</v>
+        <v>1.1647</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0958</v>
+        <v>1.1647</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0958</v>
+        <v>1.1745</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K45" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0958</v>
+        <v>0.1745000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0397</v>
+        <v>0.0689</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3991</v>
+        <v>-0.4057</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0552</v>
+        <v>0.0958</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0345</v>
+        <v>0.0397</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.402</v>
+        <v>-0.4219</v>
       </c>
       <c r="E47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="F47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="I47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.048</v>
+        <v>0.0552</v>
       </c>
       <c r="N47" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -2618,7 +2618,7 @@
         <v>-0.0171</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.431</v>
+        <v>-0.4534</v>
       </c>
       <c r="E48" t="n">
         <v>-0.0238</v>
@@ -2664,7 +2664,7 @@
         <v>-0.025</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4354</v>
+        <v>-0.4578</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0348</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0554</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4525</v>
+        <v>-0.4746</v>
       </c>
       <c r="E50" t="n">
         <v>-0.077</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0819</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4673</v>
+        <v>-0.4892</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1138</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1292</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4939</v>
+        <v>-0.5155</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1796</v>
@@ -2848,7 +2848,7 @@
         <v>-0.2089</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5386</v>
+        <v>-0.5596</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2903</v>
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2267</v>
+        <v>-0.2261</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5487</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3151</v>
+        <v>-0.3142</v>
       </c>
       <c r="N54" t="n">
         <v>46</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2512</v>
+        <v>-0.2262</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5624</v>
+        <v>-0.5692</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3492</v>
+        <v>-0.3144</v>
       </c>
       <c r="N55" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2564</v>
+        <v>-0.2512</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5653</v>
+        <v>-0.583</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3564</v>
+        <v>-0.3492</v>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
@@ -3032,7 +3032,7 @@
         <v>-0.2607</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5677</v>
+        <v>-0.5883</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3623</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2757</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5762</v>
+        <v>-0.5966</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3832</v>
@@ -3114,47 +3114,47 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5033</v>
+        <v>-0.4373</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3621</v>
+        <v>-0.3146</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6247</v>
+        <v>-0.6181</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5033</v>
+        <v>-0.4373</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.0965</v>
+        <v>0.0469</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5931999999999999</v>
+        <v>-0.4842</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.0965</v>
+        <v>0.0469</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0965</v>
+        <v>0.0473</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5931999999999999</v>
+        <v>-0.4842</v>
       </c>
       <c r="K59" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5033000000000001</v>
+        <v>-0.4369</v>
       </c>
       <c r="N59" t="n">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5456</v>
+        <v>-0.4944</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3926</v>
+        <v>-0.3557</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6418</v>
+        <v>-0.6409</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5456</v>
+        <v>-0.4944</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4544</v>
+        <v>0.5056</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4544</v>
+        <v>0.5056</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4544</v>
+        <v>0.5056</v>
       </c>
       <c r="J60" t="n">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>40</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5456</v>
+        <v>-0.4944</v>
       </c>
       <c r="N60" t="n">
         <v>91</v>
@@ -3206,461 +3206,461 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5522</v>
+        <v>-0.5033</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3973</v>
+        <v>-0.3621</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6444</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5522</v>
+        <v>-0.5033</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5522</v>
+        <v>-1.0965</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5522</v>
+        <v>-1.0965</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5522</v>
+        <v>-1.0965</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5522</v>
+        <v>-0.5033000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>56</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4314</v>
+        <v>-0.3973</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6636</v>
+        <v>-0.6639</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5996</v>
+        <v>-0.5522</v>
       </c>
       <c r="N62" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4602</v>
+        <v>-0.4314</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6797</v>
+        <v>-0.6828</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="N63" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4608</v>
+        <v>-0.4602</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6801</v>
+        <v>-0.6987</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6405</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4972</v>
+        <v>-0.4608</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7006</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6911</v>
+        <v>-0.6405</v>
       </c>
       <c r="N65" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6946</v>
+        <v>-0.666</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4998</v>
+        <v>-0.4792</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.702</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6946</v>
+        <v>-0.666</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2104</v>
+        <v>-0.3353</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.4842</v>
+        <v>-0.3307</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2104</v>
+        <v>-0.3353</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2114</v>
+        <v>-0.3381</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.4842</v>
+        <v>-0.3307</v>
       </c>
       <c r="K66" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L66" t="n">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6956</v>
+        <v>-0.6688000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>280</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.512</v>
+        <v>-0.4912</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7088</v>
+        <v>-0.7159</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7116</v>
+        <v>-0.6827</v>
       </c>
       <c r="N67" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.6911</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.4972</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.716</v>
+        <v>-0.7192</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.6911</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3986</v>
+        <v>-0.6911</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.3307</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3986</v>
+        <v>-0.6911</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4004</v>
+        <v>-0.6911</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.3307</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="L68" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7311</v>
+        <v>-0.6911</v>
       </c>
       <c r="N68" t="n">
-        <v>186</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7923</v>
+        <v>-0.7116</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.512</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7274</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7923</v>
+        <v>-0.7116</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2842</v>
+        <v>-0.7116</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.0765</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2842</v>
+        <v>-0.7116</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2855</v>
+        <v>-0.7116</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.0765</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="L69" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.791</v>
+        <v>-0.7116</v>
       </c>
       <c r="N69" t="n">
-        <v>280</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8021</v>
+        <v>-0.7934</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5708</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7454</v>
+        <v>-0.76</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8021</v>
+        <v>-0.7934</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.8021</v>
+        <v>0.2831</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-1.0765</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.8021</v>
+        <v>0.2831</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.8021</v>
+        <v>0.2855</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-1.0765</v>
       </c>
       <c r="K70" t="n">
         <v>100</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.8021</v>
+        <v>-0.791</v>
       </c>
       <c r="N70" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71">
@@ -3676,7 +3676,7 @@
         <v>-0.6175</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7681</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E71" t="n">
         <v>-0.8582</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6774</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8017</v>
+        <v>-0.819</v>
       </c>
       <c r="E72" t="n">
         <v>-0.9415</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7986</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8698</v>
+        <v>-0.8861</v>
       </c>
       <c r="E73" t="n">
         <v>-1.11</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8023</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8718</v>
+        <v>-0.8882</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1151</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8027</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.872</v>
+        <v>-0.8884</v>
       </c>
       <c r="E75" t="n">
         <v>-1.1156</v>
@@ -3906,7 +3906,7 @@
         <v>-0.8148</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8789</v>
+        <v>-0.8951</v>
       </c>
       <c r="E76" t="n">
         <v>-1.1325</v>
@@ -3952,7 +3952,7 @@
         <v>-0.8647</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9069</v>
+        <v>-0.9227</v>
       </c>
       <c r="E77" t="n">
         <v>-1.2018</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8668</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9081</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="E78" t="n">
         <v>-1.2048</v>
@@ -4044,7 +4044,7 @@
         <v>-0.916</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9357</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="E79" t="n">
         <v>-1.2731</v>
@@ -4090,7 +4090,7 @@
         <v>-0.9257</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.9411</v>
+        <v>-0.9565</v>
       </c>
       <c r="E80" t="n">
         <v>-1.2866</v>
@@ -4136,7 +4136,7 @@
         <v>-0.9933999999999999</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.9791</v>
+        <v>-0.994</v>
       </c>
       <c r="E81" t="n">
         <v>-1.3807</v>
@@ -4182,7 +4182,7 @@
         <v>-2.1963</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.6545</v>
+        <v>-1.66</v>
       </c>
       <c r="E82" t="n">
         <v>-3.0525</v>

--- a/database/event/2062/event_2062_evp_summary.xlsx
+++ b/database/event/2062/event_2062_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5694</v>
+        <v>7.7741</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4461</v>
+        <v>5.5934</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7792</v>
+        <v>2.9147</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5694</v>
+        <v>7.7741</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4908</v>
+        <v>2.3592</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0786</v>
+        <v>5.4149</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4908</v>
+        <v>2.4387</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4908</v>
+        <v>2.4387</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0786</v>
+        <v>5.4149</v>
       </c>
       <c r="K2" t="n">
         <v>49</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5694</v>
+        <v>7.8536</v>
       </c>
       <c r="N2" t="n">
         <v>238</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3225</v>
+        <v>5.4954</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8295</v>
+        <v>3.9539</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7648</v>
+        <v>1.8774</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3225</v>
+        <v>5.4954</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4118</v>
+        <v>2.3205</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9107</v>
+        <v>3.1749</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4118</v>
+        <v>2.3539</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4118</v>
+        <v>2.3539</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9107</v>
+        <v>3.1749</v>
       </c>
       <c r="K3" t="n">
         <v>49</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3225</v>
+        <v>5.5288</v>
       </c>
       <c r="N3" t="n">
         <v>238</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8367</v>
+        <v>4.9174</v>
       </c>
       <c r="C4" t="n">
-        <v>3.48</v>
+        <v>3.538</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5455</v>
+        <v>1.6143</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8367</v>
+        <v>4.9174</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5928</v>
+        <v>2.4038</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2439</v>
+        <v>2.5136</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5928</v>
+        <v>2.5363</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6994</v>
+        <v>2.6017</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2439</v>
+        <v>2.5136</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9433</v>
+        <v>5.1153</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5362</v>
+        <v>4.6484</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2638</v>
+        <v>3.3445</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4099</v>
+        <v>1.4918</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5362</v>
+        <v>4.6484</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7075</v>
+        <v>1.6276</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8287</v>
+        <v>3.0208</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7075</v>
+        <v>1.6276</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7075</v>
+        <v>1.6276</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8287</v>
+        <v>3.0208</v>
       </c>
       <c r="K5" t="n">
         <v>49</v>
@@ -667,7 +667,7 @@
         <v>189</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5362</v>
+        <v>4.6484</v>
       </c>
       <c r="N5" t="n">
         <v>238</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1806</v>
+        <v>4.3731</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0079</v>
+        <v>3.1464</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2493</v>
+        <v>1.3665</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1806</v>
+        <v>4.3731</v>
       </c>
       <c r="F6" t="n">
-        <v>2.635</v>
+        <v>0.7032</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5456</v>
+        <v>3.6699</v>
       </c>
       <c r="H6" t="n">
-        <v>2.635</v>
+        <v>0.7032</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7434</v>
+        <v>0.7032</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5456</v>
+        <v>3.6699</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>4.289</v>
+        <v>4.3731</v>
       </c>
       <c r="N6" t="n">
-        <v>280</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1204</v>
+        <v>4.2996</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9646</v>
+        <v>3.0935</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2221</v>
+        <v>1.3331</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1204</v>
+        <v>4.2996</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0372</v>
+        <v>1.9999</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0832</v>
+        <v>2.2998</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0372</v>
+        <v>1.9999</v>
       </c>
       <c r="I7" t="n">
-        <v>2.121</v>
+        <v>2.0514</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0832</v>
+        <v>2.2998</v>
       </c>
       <c r="K7" t="n">
         <v>107</v>
@@ -759,7 +759,7 @@
         <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2042</v>
+        <v>4.3512</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1127</v>
+        <v>4.1119</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9591</v>
+        <v>2.9585</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2187</v>
+        <v>1.2476</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1127</v>
+        <v>4.1119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6774</v>
+        <v>2.4294</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4353</v>
+        <v>1.6825</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6774</v>
+        <v>2.5922</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6774</v>
+        <v>2.659</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4353</v>
+        <v>1.6825</v>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1127</v>
+        <v>4.3415</v>
       </c>
       <c r="N8" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9736</v>
+        <v>3.7947</v>
       </c>
       <c r="C9" t="n">
-        <v>2.859</v>
+        <v>2.7303</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1559</v>
+        <v>1.1032</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9736</v>
+        <v>3.7947</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7954</v>
+        <v>2.4831</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1782</v>
+        <v>1.3116</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7954</v>
+        <v>2.7099</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9104</v>
+        <v>2.7797</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1782</v>
+        <v>1.3116</v>
       </c>
       <c r="K9" t="n">
         <v>141</v>
@@ -851,7 +851,7 @@
         <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0886</v>
+        <v>4.0913</v>
       </c>
       <c r="N9" t="n">
         <v>211</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5265</v>
+        <v>3.6765</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5373</v>
+        <v>2.6452</v>
       </c>
       <c r="D10" t="n">
-        <v>0.954</v>
+        <v>1.0494</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5265</v>
+        <v>3.6765</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9235</v>
+        <v>1.8881</v>
       </c>
       <c r="G10" t="n">
-        <v>1.603</v>
+        <v>1.7884</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9235</v>
+        <v>1.8881</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0026</v>
+        <v>1.9368</v>
       </c>
       <c r="J10" t="n">
-        <v>1.603</v>
+        <v>1.7884</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6056</v>
+        <v>3.7252</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -906,127 +906,127 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0614</v>
+        <v>3.0102</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2027</v>
+        <v>2.1658</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7441</v>
+        <v>0.7461</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0614</v>
+        <v>3.0102</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6093</v>
+        <v>1.3885</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4521</v>
+        <v>1.6217</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6093</v>
+        <v>1.3885</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7166</v>
+        <v>1.4243</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4521</v>
+        <v>1.6217</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1687</v>
+        <v>3.046</v>
       </c>
       <c r="N11" t="n">
-        <v>280</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9968</v>
+        <v>2.981</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1562</v>
+        <v>2.1448</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7149</v>
+        <v>0.7328</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9968</v>
+        <v>2.981</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0682</v>
+        <v>2.432</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3774</v>
+        <v>2.5979</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5163</v>
+        <v>2.6648</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="K12" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4449</v>
+        <v>3.2138</v>
       </c>
       <c r="N12" t="n">
-        <v>186</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8742</v>
+        <v>2.8234</v>
       </c>
       <c r="C13" t="n">
-        <v>2.068</v>
+        <v>2.0314</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6595</v>
+        <v>0.6611</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8742</v>
+        <v>2.8234</v>
       </c>
       <c r="F13" t="n">
-        <v>1.418</v>
+        <v>0.4793</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4562</v>
+        <v>2.3441</v>
       </c>
       <c r="H13" t="n">
-        <v>1.418</v>
+        <v>0.4793</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4763</v>
+        <v>0.4917</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4562</v>
+        <v>2.3441</v>
       </c>
       <c r="K13" t="n">
         <v>107</v>
@@ -1035,7 +1035,7 @@
         <v>98</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9325</v>
+        <v>2.8358</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6103</v>
+        <v>2.7741</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8781</v>
+        <v>1.9959</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5404</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6103</v>
+        <v>2.7741</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4808</v>
+        <v>2.8138</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1295</v>
+        <v>-0.0397</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4808</v>
+        <v>3.4336</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5006</v>
+        <v>3.5221</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1295</v>
+        <v>-0.0397</v>
       </c>
       <c r="K14" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="L14" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6301</v>
+        <v>3.4824</v>
       </c>
       <c r="N14" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3053</v>
+        <v>2.4943</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6586</v>
+        <v>1.7946</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4027</v>
+        <v>0.5113</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3053</v>
+        <v>2.4943</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0527</v>
+        <v>1.0381</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2526</v>
+        <v>1.4562</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0527</v>
+        <v>1.0381</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0527</v>
+        <v>1.0381</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2526</v>
+        <v>1.4562</v>
       </c>
       <c r="K15" t="n">
         <v>49</v>
@@ -1127,7 +1127,7 @@
         <v>189</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3053</v>
+        <v>2.4943</v>
       </c>
       <c r="N15" t="n">
         <v>238</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2256</v>
+        <v>2.2298</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6013</v>
+        <v>1.6043</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3667</v>
+        <v>0.3908</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2256</v>
+        <v>2.2298</v>
       </c>
       <c r="F16" t="n">
-        <v>1.941</v>
+        <v>1.9307</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2846</v>
+        <v>0.2991</v>
       </c>
       <c r="H16" t="n">
-        <v>1.941</v>
+        <v>1.9307</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0208</v>
+        <v>1.9805</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2846</v>
+        <v>0.2991</v>
       </c>
       <c r="K16" t="n">
         <v>141</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3054</v>
+        <v>2.2796</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1896</v>
+        <v>2.1742</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5754</v>
+        <v>1.5643</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3505</v>
+        <v>0.3655</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1896</v>
+        <v>2.1742</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0898</v>
+        <v>2.0197</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0998</v>
+        <v>0.1545</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0898</v>
+        <v>2.0197</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0898</v>
+        <v>2.0197</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0998</v>
+        <v>0.1545</v>
       </c>
       <c r="K17" t="n">
         <v>54</v>
@@ -1219,7 +1219,7 @@
         <v>155</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1896</v>
+        <v>2.1742</v>
       </c>
       <c r="N17" t="n">
         <v>209</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1025</v>
+        <v>2.1167</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5127</v>
+        <v>1.5229</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3112</v>
+        <v>0.3394</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1025</v>
+        <v>2.1167</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1683</v>
+        <v>2.1908</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0658</v>
+        <v>-0.0741</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1683</v>
+        <v>2.1908</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2575</v>
+        <v>2.2473</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0658</v>
+        <v>-0.0741</v>
       </c>
       <c r="K18" t="n">
         <v>127</v>
@@ -1265,7 +1265,7 @@
         <v>59</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1917</v>
+        <v>2.1732</v>
       </c>
       <c r="N18" t="n">
         <v>186</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0735</v>
+        <v>2.1075</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4919</v>
+        <v>1.5163</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2981</v>
+        <v>0.3352</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0735</v>
+        <v>2.1075</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6274</v>
+        <v>1.6481</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4461</v>
+        <v>0.4594</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6274</v>
+        <v>1.6481</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6943</v>
+        <v>1.6906</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4461</v>
+        <v>0.4594</v>
       </c>
       <c r="K19" t="n">
         <v>141</v>
@@ -1311,7 +1311,7 @@
         <v>70</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1404</v>
+        <v>2.15</v>
       </c>
       <c r="N19" t="n">
         <v>211</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0597</v>
+        <v>1.9624</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4819</v>
+        <v>1.4119</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2918</v>
+        <v>0.2691</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0597</v>
+        <v>1.9624</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0715</v>
+        <v>1.2313</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0118</v>
+        <v>0.7311</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0715</v>
+        <v>1.2313</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0715</v>
+        <v>1.263</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0118</v>
+        <v>0.7311</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="L20" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0597</v>
+        <v>1.9941</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9536</v>
+        <v>1.9538</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4056</v>
+        <v>1.4057</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2439</v>
+        <v>0.2652</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9536</v>
+        <v>1.9538</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3244</v>
+        <v>1.9739</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6292</v>
+        <v>-0.0201</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3244</v>
+        <v>1.9739</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3244</v>
+        <v>1.9739</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6292</v>
+        <v>-0.0201</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L21" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9536</v>
+        <v>1.9538</v>
       </c>
       <c r="N21" t="n">
-        <v>209</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9127</v>
+        <v>1.9352</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3762</v>
+        <v>1.3924</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2255</v>
+        <v>0.2567</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9127</v>
+        <v>1.9352</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2924</v>
+        <v>0.9216</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3797</v>
+        <v>1.0136</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2924</v>
+        <v>0.9216</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3867</v>
+        <v>0.9453</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3797</v>
+        <v>1.0136</v>
       </c>
       <c r="K22" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="L22" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="M22" t="n">
-        <v>2.007</v>
+        <v>1.9589</v>
       </c>
       <c r="N22" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8928</v>
+        <v>1.8988</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3619</v>
+        <v>1.3662</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2165</v>
+        <v>0.2402</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8928</v>
+        <v>1.8988</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2121</v>
+        <v>1.2702</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6807</v>
+        <v>0.6286</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2121</v>
+        <v>1.2702</v>
       </c>
       <c r="I23" t="n">
-        <v>1.262</v>
+        <v>1.2702</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6807</v>
+        <v>0.6286</v>
       </c>
       <c r="K23" t="n">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="L23" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9427</v>
+        <v>1.8988</v>
       </c>
       <c r="N23" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8593</v>
+        <v>1.8501</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3378</v>
+        <v>1.3311</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2014</v>
+        <v>0.218</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8593</v>
+        <v>1.8501</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9835</v>
+        <v>2.2539</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8758</v>
+        <v>-0.4038</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9835</v>
+        <v>2.2539</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0239</v>
+        <v>2.312</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8758</v>
+        <v>-0.4038</v>
       </c>
       <c r="K24" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="L24" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8997</v>
+        <v>1.9082</v>
       </c>
       <c r="N24" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3377</v>
+        <v>1.3113</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2013</v>
+        <v>0.2054</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8592</v>
+        <v>1.8225</v>
       </c>
       <c r="N25" t="n">
         <v>136</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2238</v>
+        <v>1.27</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1299</v>
+        <v>0.1794</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7009</v>
+        <v>1.7652</v>
       </c>
       <c r="N26" t="n">
         <v>136</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6847</v>
+        <v>1.6618</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2121</v>
+        <v>1.1957</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1225</v>
+        <v>0.1323</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6847</v>
+        <v>1.6618</v>
       </c>
       <c r="F27" t="n">
-        <v>1.701</v>
+        <v>1.6618</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0163</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.701</v>
+        <v>1.6618</v>
       </c>
       <c r="I27" t="n">
-        <v>1.701</v>
+        <v>1.6618</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0163</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>51</v>
@@ -1679,7 +1679,7 @@
         <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6847</v>
+        <v>1.6618</v>
       </c>
       <c r="N27" t="n">
         <v>128</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1177</v>
+        <v>1.1562</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0633</v>
+        <v>0.1073</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5534</v>
+        <v>1.6069</v>
       </c>
       <c r="N28" t="n">
         <v>136</v>
@@ -1734,277 +1734,277 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4187</v>
+        <v>1.5247</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0207</v>
+        <v>1.097</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0025</v>
+        <v>0.0699</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4187</v>
+        <v>1.5247</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9348</v>
+        <v>0.4887</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5161</v>
+        <v>1.036</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9348</v>
+        <v>0.4887</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9348</v>
+        <v>0.4887</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5161</v>
+        <v>1.036</v>
       </c>
       <c r="K29" t="n">
         <v>51</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>1.4187</v>
+        <v>1.5247</v>
       </c>
       <c r="N29" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.407</v>
+        <v>1.3145</v>
       </c>
       <c r="C30" t="n">
-        <v>1.0123</v>
+        <v>0.9458</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0028</v>
+        <v>-0.0258</v>
       </c>
       <c r="E30" t="n">
-        <v>1.407</v>
+        <v>1.3145</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4563</v>
+        <v>1.8842</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9507</v>
+        <v>-0.5697</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4563</v>
+        <v>1.8842</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4563</v>
+        <v>1.8842</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9507</v>
+        <v>-0.5697</v>
       </c>
       <c r="K30" t="n">
         <v>51</v>
       </c>
       <c r="L30" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>1.407</v>
+        <v>1.3145</v>
       </c>
       <c r="N30" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2624</v>
+        <v>1.24</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9083</v>
+        <v>0.8922</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0597</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2624</v>
+        <v>1.24</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2624</v>
+        <v>1.4275</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2624</v>
+        <v>1.4275</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2624</v>
+        <v>1.4275</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="K31" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2624</v>
+        <v>1.24</v>
       </c>
       <c r="N31" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2451</v>
+        <v>1.2311</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8958</v>
+        <v>0.8858</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0759</v>
+        <v>-0.0638</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2451</v>
+        <v>1.2311</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4928</v>
+        <v>1.2311</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4928</v>
+        <v>1.2311</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4928</v>
+        <v>1.2311</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L32" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2451</v>
+        <v>1.2311</v>
       </c>
       <c r="N32" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2186</v>
+        <v>1.2173</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8768</v>
+        <v>0.8758</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0701</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2186</v>
+        <v>1.2173</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0672</v>
+        <v>1.2173</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8486</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0672</v>
+        <v>1.2173</v>
       </c>
       <c r="I33" t="n">
-        <v>2.0672</v>
+        <v>1.2173</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8486</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2186</v>
+        <v>1.2173</v>
       </c>
       <c r="N33" t="n">
-        <v>91</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2077</v>
+        <v>1.0932</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8689</v>
+        <v>0.7865</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1266</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2077</v>
+        <v>1.0932</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2077</v>
+        <v>1.9707</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2077</v>
+        <v>1.9707</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2077</v>
+        <v>1.9707</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2077</v>
+        <v>1.0932</v>
       </c>
       <c r="N34" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7973</v>
+        <v>0.7692</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1377</v>
+        <v>-0.1375</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1082</v>
+        <v>1.0691</v>
       </c>
       <c r="N35" t="n">
         <v>123</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5783</v>
+        <v>0.5567</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2752</v>
+        <v>-0.272</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8037</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>103</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7994</v>
+        <v>0.7732</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5752</v>
+        <v>0.5563</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2771</v>
+        <v>-0.2722</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7994</v>
+        <v>0.7732</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7994</v>
+        <v>0.7847</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7994</v>
+        <v>0.7847</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7994</v>
+        <v>0.7847</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="K37" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7994</v>
+        <v>0.7732</v>
       </c>
       <c r="N37" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7726</v>
+        <v>0.7506</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5401</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2892</v>
+        <v>-0.2825</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7726</v>
+        <v>0.7506</v>
       </c>
       <c r="F38" t="n">
-        <v>0.795</v>
+        <v>0.7506</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0224</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.795</v>
+        <v>0.7506</v>
       </c>
       <c r="I38" t="n">
-        <v>0.795</v>
+        <v>0.7506</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0224</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="L38" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7726000000000001</v>
+        <v>0.7506</v>
       </c>
       <c r="N38" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5506</v>
+        <v>0.4981</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2925</v>
+        <v>-0.3091</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7653</v>
+        <v>0.6923</v>
       </c>
       <c r="N39" t="n">
         <v>49</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7018</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5049</v>
+        <v>0.4841</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3212</v>
+        <v>-0.3179</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7018</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2169</v>
+        <v>1.1747</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5151</v>
+        <v>-0.5018</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2169</v>
+        <v>1.1747</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2169</v>
+        <v>1.1747</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5151</v>
+        <v>-0.5018</v>
       </c>
       <c r="K40" t="n">
         <v>54</v>
@@ -2277,7 +2277,7 @@
         <v>155</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7018000000000001</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>209</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4832</v>
+        <v>0.4828</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3348</v>
+        <v>-0.3188</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6716</v>
+        <v>0.671</v>
       </c>
       <c r="N41" t="n">
         <v>56</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="C42" t="n">
-        <v>0.481</v>
+        <v>0.4641</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3362</v>
+        <v>-0.3306</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6685</v>
+        <v>0.645</v>
       </c>
       <c r="N42" t="n">
         <v>51</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4654</v>
+        <v>0.4264</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.346</v>
+        <v>-0.3544</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6469</v>
+        <v>0.5927</v>
       </c>
       <c r="N43" t="n">
         <v>123</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5923</v>
+        <v>0.5463</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4262</v>
+        <v>0.3931</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3706</v>
+        <v>-0.3755</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5923</v>
+        <v>0.5463</v>
       </c>
       <c r="F44" t="n">
-        <v>1.4897</v>
+        <v>1.4591</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.8974</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>1.4897</v>
+        <v>1.4591</v>
       </c>
       <c r="I44" t="n">
-        <v>1.551</v>
+        <v>1.4967</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8974</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>127</v>
@@ -2461,7 +2461,7 @@
         <v>59</v>
       </c>
       <c r="M44" t="n">
-        <v>0.6536</v>
+        <v>0.5839</v>
       </c>
       <c r="N44" t="n">
         <v>186</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4041</v>
+        <v>0.3668</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3845</v>
+        <v>-0.3921</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5616</v>
+        <v>0.5098</v>
       </c>
       <c r="N45" t="n">
         <v>56</v>
@@ -2520,31 +2520,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3045</v>
+        <v>0.2774</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2191</v>
+        <v>0.1996</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.4979</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3045</v>
+        <v>0.2774</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6211</v>
+        <v>0.6224</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.3166</v>
+        <v>-0.345</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6211</v>
+        <v>0.6224</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6211</v>
+        <v>0.6224</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3166</v>
+        <v>-0.345</v>
       </c>
       <c r="K46" t="n">
         <v>54</v>
@@ -2553,7 +2553,7 @@
         <v>155</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3045</v>
+        <v>0.2774</v>
       </c>
       <c r="N46" t="n">
         <v>209</v>
@@ -2562,185 +2562,185 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2269</v>
+        <v>0.2296</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1633</v>
+        <v>0.1652</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5356</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2269</v>
+        <v>0.2296</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2269</v>
+        <v>0.2959</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.0663</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2269</v>
+        <v>0.2959</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2269</v>
+        <v>0.3035</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.0663</v>
       </c>
       <c r="K47" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2269</v>
+        <v>0.2372</v>
       </c>
       <c r="N47" t="n">
-        <v>136</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1049</v>
+        <v>0.1385</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5722</v>
+        <v>-0.5366</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1458</v>
+        <v>0.1925</v>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="C49" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5847</v>
+        <v>-0.5627</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1181</v>
+        <v>0.135</v>
       </c>
       <c r="N49" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1058</v>
+        <v>0.0791</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0761</v>
+        <v>0.0569</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5903</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1058</v>
+        <v>0.0791</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2829</v>
+        <v>0.0791</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1771</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2829</v>
+        <v>0.0791</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2945</v>
+        <v>0.0791</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.1771</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="L50" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1174</v>
+        <v>0.0791</v>
       </c>
       <c r="N50" t="n">
-        <v>280</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="C51" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0568</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0992</v>
+        <v>0.079</v>
       </c>
       <c r="N51" t="n">
         <v>51</v>
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0629</v>
+        <v>0.0425</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5986</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4484</v>
+        <v>0.4763</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.361</v>
+        <v>-0.4173</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4484</v>
+        <v>0.4763</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4484</v>
+        <v>0.4763</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.361</v>
+        <v>-0.4173</v>
       </c>
       <c r="K52" t="n">
         <v>51</v>
@@ -2829,7 +2829,7 @@
         <v>40</v>
       </c>
       <c r="M52" t="n">
-        <v>0.08740000000000003</v>
+        <v>0.059</v>
       </c>
       <c r="N52" t="n">
         <v>91</v>
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0522</v>
+        <v>0.018</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6052</v>
+        <v>-0.6128</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0726</v>
+        <v>0.025</v>
       </c>
       <c r="N53" t="n">
         <v>103</v>
@@ -2888,31 +2888,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.037</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0266</v>
+        <v>-0.0061</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6213</v>
+        <v>-0.6281</v>
       </c>
       <c r="E54" t="n">
-        <v>0.037</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.278</v>
+        <v>0.2657</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.241</v>
+        <v>-0.2742</v>
       </c>
       <c r="H54" t="n">
-        <v>0.278</v>
+        <v>0.2657</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2894</v>
+        <v>0.2725</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.241</v>
+        <v>-0.2742</v>
       </c>
       <c r="K54" t="n">
         <v>127</v>
@@ -2921,7 +2921,7 @@
         <v>59</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0484</v>
+        <v>-0.001699999999999979</v>
       </c>
       <c r="N54" t="n">
         <v>186</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0219</v>
+        <v>-0.042</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6518</v>
+        <v>-0.6508</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0305</v>
+        <v>-0.0584</v>
       </c>
       <c r="N55" t="n">
         <v>46</v>
@@ -2976,32 +2976,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0292</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6563</v>
+        <v>-0.6695</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0406</v>
+        <v>-0.0994</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -3022,47 +3022,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0445</v>
+        <v>-0.0912</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6659</v>
+        <v>-0.6819</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0618</v>
+        <v>-0.1267</v>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0858</v>
+        <v>-0.0944</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6918</v>
+        <v>-0.6839</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1192</v>
+        <v>-0.1312</v>
       </c>
       <c r="N58" t="n">
         <v>51</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6935</v>
+        <v>-0.6869</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1228</v>
+        <v>-0.1378</v>
       </c>
       <c r="N59" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2046</v>
+        <v>-0.1997</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1472</v>
+        <v>-0.1437</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7304</v>
+        <v>-0.7151</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2046</v>
+        <v>-0.1997</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2046</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.7688</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2046</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2046</v>
+        <v>0.5838</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.7688</v>
       </c>
       <c r="K60" t="n">
         <v>100</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2046</v>
+        <v>-0.1850000000000001</v>
       </c>
       <c r="N60" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1507</v>
+        <v>-0.1659</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7326</v>
+        <v>-0.7292</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2095</v>
+        <v>-0.2306</v>
       </c>
       <c r="N61" t="n">
         <v>56</v>
@@ -3252,32 +3252,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2182</v>
+        <v>-0.2199</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7749</v>
+        <v>-0.7634</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3033</v>
+        <v>-0.3057</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
@@ -3298,32 +3298,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2252</v>
+        <v>-0.2407</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7793</v>
+        <v>-0.7765</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.313</v>
+        <v>-0.3345</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
@@ -3344,47 +3344,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3306</v>
+        <v>-0.335</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2379</v>
+        <v>-0.241</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7873</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3306</v>
+        <v>-0.335</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6472</v>
+        <v>-0.335</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.9778</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6472</v>
+        <v>-0.335</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6472</v>
+        <v>-0.335</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.9778</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3306</v>
+        <v>-0.335</v>
       </c>
       <c r="N64" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2441</v>
+        <v>-0.2636</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7912</v>
+        <v>-0.791</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3393</v>
+        <v>-0.3664</v>
       </c>
       <c r="N65" t="n">
         <v>56</v>
@@ -3436,139 +3436,139 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3397</v>
+        <v>-0.388</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2444</v>
+        <v>-0.2792</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7914</v>
+        <v>-0.8008</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3397</v>
+        <v>-0.388</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5191</v>
+        <v>-0.9061</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.8588</v>
+        <v>0.5181</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5191</v>
+        <v>-0.9061</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5404</v>
+        <v>-0.9061</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.8588</v>
+        <v>0.5181</v>
       </c>
       <c r="K66" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="L66" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3184</v>
+        <v>-0.388</v>
       </c>
       <c r="N66" t="n">
-        <v>280</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3412</v>
+        <v>-0.3904</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2455</v>
+        <v>-0.2809</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.792</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3412</v>
+        <v>-0.3904</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3412</v>
+        <v>0.6096</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3412</v>
+        <v>0.6096</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3412</v>
+        <v>0.6096</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K67" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3412</v>
+        <v>-0.3904</v>
       </c>
       <c r="N67" t="n">
-        <v>136</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3366</v>
+        <v>-0.2941</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8492</v>
+        <v>-0.8103</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4678</v>
+        <v>-0.4087</v>
       </c>
       <c r="N68" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3405</v>
+        <v>-0.3666</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8516</v>
+        <v>-0.8561</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4732</v>
+        <v>-0.5095</v>
       </c>
       <c r="N69" t="n">
         <v>49</v>
@@ -3620,47 +3620,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.4777</v>
+        <v>-0.5151</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3437</v>
+        <v>-0.3706</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8537</v>
+        <v>-0.8587</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.4777</v>
+        <v>-0.5151</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9644</v>
+        <v>-0.5151</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4867</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9644</v>
+        <v>-0.5151</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9644</v>
+        <v>-0.5151</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4867</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L70" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.4777</v>
+        <v>-0.5151</v>
       </c>
       <c r="N70" t="n">
-        <v>209</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3593</v>
+        <v>-0.3805</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8635</v>
+        <v>-0.8649</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.4994</v>
+        <v>-0.5288</v>
       </c>
       <c r="N71" t="n">
         <v>51</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4557</v>
+        <v>-0.4772</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9262</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6333</v>
+        <v>-0.6633</v>
       </c>
       <c r="N72" t="n">
         <v>49</v>
@@ -3758,47 +3758,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>DEVIL</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5371</v>
+        <v>-0.5552</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.975</v>
+        <v>-0.9755</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7716</v>
       </c>
       <c r="N73" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5383</v>
+        <v>-0.5567</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9758</v>
+        <v>-0.9765</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7482</v>
+        <v>-0.7738</v>
       </c>
       <c r="N74" t="n">
         <v>46</v>
@@ -3850,139 +3850,139 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DEVIL</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5392</v>
+        <v>-0.5595</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.9782</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7494</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5724</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9972</v>
+        <v>-1.0034</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.7956</v>
+        <v>-0.833</v>
       </c>
       <c r="N76" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.6005</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0033</v>
+        <v>-1.0041</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.8092</v>
+        <v>-0.8346</v>
       </c>
       <c r="N77" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5829</v>
+        <v>-0.6142</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0037</v>
+        <v>-1.0128</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.8101</v>
+        <v>-0.8536</v>
       </c>
       <c r="N78" t="n">
         <v>103</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.645</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0305</v>
+        <v>-1.0323</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.8693</v>
+        <v>-0.8965</v>
       </c>
       <c r="N79" t="n">
         <v>49</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7201</v>
+        <v>-0.7299</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0898</v>
+        <v>-1.086</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.0008</v>
+        <v>-1.0144</v>
       </c>
       <c r="N80" t="n">
         <v>123</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.1382</v>
+        <v>-1.1141</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.8189</v>
+        <v>-0.8016</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.1519</v>
+        <v>-1.1314</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.1382</v>
+        <v>-1.1141</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.239</v>
+        <v>-0.1906</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.8992</v>
+        <v>-0.9235</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.239</v>
+        <v>-0.1906</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.239</v>
+        <v>-0.1906</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.8992</v>
+        <v>-0.9235</v>
       </c>
       <c r="K81" t="n">
         <v>51</v>
@@ -4163,7 +4163,7 @@
         <v>40</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.1382</v>
+        <v>-1.1141</v>
       </c>
       <c r="N81" t="n">
         <v>91</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.5906</v>
+        <v>-2.4931</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.8639</v>
+        <v>-1.7938</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8075</v>
+        <v>-1.7591</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.5906</v>
+        <v>-2.4931</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.8047</v>
+        <v>-1.6884</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.7859</v>
+        <v>-0.8047</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.8047</v>
+        <v>-1.6884</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.8047</v>
+        <v>-1.6884</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.7859</v>
+        <v>-0.8047</v>
       </c>
       <c r="K82" t="n">
         <v>91</v>
@@ -4209,7 +4209,7 @@
         <v>70</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.5906</v>
+        <v>-2.4931</v>
       </c>
       <c r="N82" t="n">
         <v>161</v>
@@ -4315,10 +4315,10 @@
         <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3506</v>
+        <v>1.4431</v>
       </c>
       <c r="J2" t="n">
-        <v>31.0638</v>
+        <v>33.1913</v>
       </c>
     </row>
     <row r="3">
@@ -4355,10 +4355,10 @@
         <v>1.55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1904</v>
+        <v>1.2142</v>
       </c>
       <c r="J3" t="n">
-        <v>27.3792</v>
+        <v>27.9266</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>1.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4754</v>
+        <v>0.4711</v>
       </c>
       <c r="J4" t="n">
-        <v>10.9342</v>
+        <v>10.8353</v>
       </c>
     </row>
     <row r="5">
@@ -4435,10 +4435,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0698</v>
+        <v>0.0939</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6054</v>
+        <v>2.1597</v>
       </c>
     </row>
     <row r="6">
@@ -4475,10 +4475,10 @@
         <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5027</v>
+        <v>-0.4678</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.5621</v>
+        <v>-10.7594</v>
       </c>
     </row>
     <row r="7">
@@ -4515,10 +4515,10 @@
         <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2918</v>
+        <v>0.281</v>
       </c>
       <c r="J7" t="n">
-        <v>6.7114</v>
+        <v>6.463</v>
       </c>
     </row>
     <row r="8">
@@ -4555,10 +4555,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0907</v>
+        <v>-0.1076</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0861</v>
+        <v>-2.4748</v>
       </c>
     </row>
     <row r="9">
@@ -4595,10 +4595,10 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2169</v>
+        <v>-0.2353</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9887</v>
+        <v>-5.4119</v>
       </c>
     </row>
     <row r="10">
@@ -4635,10 +4635,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3128</v>
+        <v>-0.3293</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.1944</v>
+        <v>-7.5739</v>
       </c>
     </row>
     <row r="11">
@@ -4675,10 +4675,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4349</v>
+        <v>-0.4462</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.0027</v>
+        <v>-10.2626</v>
       </c>
     </row>
     <row r="12">
@@ -4715,10 +4715,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2732</v>
+        <v>1.3377</v>
       </c>
       <c r="J12" t="n">
-        <v>28.0104</v>
+        <v>29.4294</v>
       </c>
     </row>
     <row r="13">
@@ -4755,10 +4755,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7909</v>
+        <v>0.7556</v>
       </c>
       <c r="J13" t="n">
-        <v>17.3998</v>
+        <v>16.6232</v>
       </c>
     </row>
     <row r="14">
@@ -4795,10 +4795,10 @@
         <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7013</v>
+        <v>0.6763</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4286</v>
+        <v>14.8786</v>
       </c>
     </row>
     <row r="15">
@@ -4835,10 +4835,10 @@
         <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6551</v>
+        <v>0.6352</v>
       </c>
       <c r="J15" t="n">
-        <v>14.4122</v>
+        <v>13.9744</v>
       </c>
     </row>
     <row r="16">
@@ -4875,10 +4875,10 @@
         <v>1.19</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5103</v>
+        <v>0.5058</v>
       </c>
       <c r="J16" t="n">
-        <v>11.2266</v>
+        <v>11.1276</v>
       </c>
     </row>
     <row r="17">
@@ -4915,10 +4915,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4207</v>
+        <v>0.4018</v>
       </c>
       <c r="J17" t="n">
-        <v>9.2554</v>
+        <v>8.839600000000001</v>
       </c>
     </row>
     <row r="18">
@@ -4955,10 +4955,10 @@
         <v>0.82</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1979</v>
+        <v>-0.2162</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.3538</v>
+        <v>-4.7564</v>
       </c>
     </row>
     <row r="19">
@@ -4995,10 +4995,10 @@
         <v>0.79</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2263</v>
+        <v>-0.2447</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.9786</v>
+        <v>-5.3834</v>
       </c>
     </row>
     <row r="20">
@@ -5035,10 +5035,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2934</v>
+        <v>-0.3106</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.4548</v>
+        <v>-6.8332</v>
       </c>
     </row>
     <row r="21">
@@ -5075,10 +5075,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.416</v>
+        <v>-0.4284</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.151999999999999</v>
+        <v>-9.424799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -5115,10 +5115,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4448</v>
+        <v>0.4863</v>
       </c>
       <c r="J22" t="n">
-        <v>12.8992</v>
+        <v>14.1027</v>
       </c>
     </row>
     <row r="23">
@@ -5155,10 +5155,10 @@
         <v>1.07</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2463</v>
+        <v>0.2501</v>
       </c>
       <c r="J23" t="n">
-        <v>7.1427</v>
+        <v>7.2529</v>
       </c>
     </row>
     <row r="24">
@@ -5195,10 +5195,10 @@
         <v>1.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2164</v>
+        <v>0.2218</v>
       </c>
       <c r="J24" t="n">
-        <v>6.2756</v>
+        <v>6.4322</v>
       </c>
     </row>
     <row r="25">
@@ -5235,10 +5235,10 @@
         <v>0.99</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0653</v>
+        <v>-0.0668</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8937</v>
+        <v>-1.9372</v>
       </c>
     </row>
     <row r="26">
@@ -5275,10 +5275,10 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1431</v>
+        <v>-0.1444</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.1499</v>
+        <v>-4.1876</v>
       </c>
     </row>
     <row r="27">
@@ -5315,10 +5315,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4214</v>
+        <v>0.4662</v>
       </c>
       <c r="J27" t="n">
-        <v>12.2206</v>
+        <v>13.5198</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2184</v>
+        <v>0.2273</v>
       </c>
       <c r="J28" t="n">
-        <v>6.3336</v>
+        <v>6.5917</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.062</v>
+        <v>0.0706</v>
       </c>
       <c r="J29" t="n">
-        <v>1.798</v>
+        <v>2.0474</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0391</v>
+        <v>-0.0451</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.1339</v>
+        <v>-1.3079</v>
       </c>
     </row>
     <row r="31">
@@ -5475,10 +5475,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1918</v>
+        <v>-0.2045</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.5622</v>
+        <v>-5.9305</v>
       </c>
     </row>
     <row r="32">
@@ -5515,10 +5515,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8794</v>
+        <v>0.9649</v>
       </c>
       <c r="J32" t="n">
-        <v>25.5026</v>
+        <v>27.9821</v>
       </c>
     </row>
     <row r="33">
@@ -5555,10 +5555,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8131</v>
+        <v>0.8937</v>
       </c>
       <c r="J33" t="n">
-        <v>23.5799</v>
+        <v>25.9173</v>
       </c>
     </row>
     <row r="34">
@@ -5595,10 +5595,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.38</v>
+        <v>-0.3636</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.02</v>
+        <v>-10.5444</v>
       </c>
     </row>
     <row r="35">
@@ -5635,10 +5635,10 @@
         <v>0.88</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4371</v>
+        <v>-0.4159</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.6759</v>
+        <v>-12.0611</v>
       </c>
     </row>
     <row r="36">
@@ -5675,10 +5675,10 @@
         <v>0.84</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5152</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.8601</v>
+        <v>-14.9408</v>
       </c>
     </row>
     <row r="37">
@@ -5715,10 +5715,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.392</v>
+        <v>0.424</v>
       </c>
       <c r="J37" t="n">
-        <v>11.368</v>
+        <v>12.296</v>
       </c>
     </row>
     <row r="38">
@@ -5755,10 +5755,10 @@
         <v>1.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1474</v>
+        <v>0.1537</v>
       </c>
       <c r="J38" t="n">
-        <v>4.2746</v>
+        <v>4.4573</v>
       </c>
     </row>
     <row r="39">
@@ -5795,10 +5795,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0475</v>
+        <v>-0.0563</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.3775</v>
+        <v>-1.6327</v>
       </c>
     </row>
     <row r="40">
@@ -5835,10 +5835,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1838</v>
+        <v>-0.1982</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.3302</v>
+        <v>-5.7478</v>
       </c>
     </row>
     <row r="41">
@@ -5875,10 +5875,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2743</v>
+        <v>-0.2881</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.9547</v>
+        <v>-8.354900000000001</v>
       </c>
     </row>
     <row r="42">
@@ -5915,10 +5915,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3547</v>
+        <v>0.3784</v>
       </c>
       <c r="J42" t="n">
-        <v>12.7692</v>
+        <v>13.6224</v>
       </c>
     </row>
     <row r="43">
@@ -5955,10 +5955,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.079</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>2.844</v>
+        <v>3.2364</v>
       </c>
     </row>
     <row r="44">
@@ -5995,10 +5995,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0624</v>
+        <v>0.0721</v>
       </c>
       <c r="J44" t="n">
-        <v>2.2464</v>
+        <v>2.5956</v>
       </c>
     </row>
     <row r="45">
@@ -6035,10 +6035,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0232</v>
+        <v>-0.0273</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-0.9828</v>
       </c>
     </row>
     <row r="46">
@@ -6075,10 +6075,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1916</v>
+        <v>-0.2043</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.8976</v>
+        <v>-7.3548</v>
       </c>
     </row>
     <row r="47">
@@ -6115,10 +6115,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3409</v>
+        <v>0.3543</v>
       </c>
       <c r="J47" t="n">
-        <v>12.2724</v>
+        <v>12.7548</v>
       </c>
     </row>
     <row r="48">
@@ -6155,10 +6155,10 @@
         <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3192</v>
+        <v>0.3284</v>
       </c>
       <c r="J48" t="n">
-        <v>11.4912</v>
+        <v>11.8224</v>
       </c>
     </row>
     <row r="49">
@@ -6195,10 +6195,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1775</v>
+        <v>0.1896</v>
       </c>
       <c r="J49" t="n">
-        <v>6.39</v>
+        <v>6.8256</v>
       </c>
     </row>
     <row r="50">
@@ -6235,10 +6235,10 @@
         <v>0.97</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0569</v>
+        <v>-0.0635</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.0484</v>
+        <v>-2.286</v>
       </c>
     </row>
     <row r="51">
@@ -6275,10 +6275,10 @@
         <v>0.86</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1853</v>
+        <v>-0.197</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.6708</v>
+        <v>-7.092</v>
       </c>
     </row>
     <row r="52">
@@ -6315,10 +6315,10 @@
         <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0397</v>
+        <v>-0.0581</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.8337</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="53">
@@ -6355,10 +6355,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0978</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.6422</v>
+        <v>-2.0538</v>
       </c>
     </row>
     <row r="54">
@@ -6395,10 +6395,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2301</v>
+        <v>-0.2498</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.8321</v>
+        <v>-5.2458</v>
       </c>
     </row>
     <row r="55">
@@ -6435,10 +6435,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3325</v>
+        <v>-0.35</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.9825</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="56">
@@ -6475,10 +6475,10 @@
         <v>0.46</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5284</v>
+        <v>-0.5354</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.0964</v>
+        <v>-11.2434</v>
       </c>
     </row>
     <row r="57">
@@ -6515,10 +6515,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8051</v>
+        <v>0.8944</v>
       </c>
       <c r="J57" t="n">
-        <v>16.9071</v>
+        <v>18.7824</v>
       </c>
     </row>
     <row r="58">
@@ -6555,10 +6555,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6415</v>
+        <v>0.7155</v>
       </c>
       <c r="J58" t="n">
-        <v>13.4715</v>
+        <v>15.0255</v>
       </c>
     </row>
     <row r="59">
@@ -6595,10 +6595,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6038</v>
+        <v>0.6736</v>
       </c>
       <c r="J59" t="n">
-        <v>12.6798</v>
+        <v>14.1456</v>
       </c>
     </row>
     <row r="60">
@@ -6635,10 +6635,10 @@
         <v>1.3</v>
       </c>
       <c r="I60" t="n">
-        <v>0.591</v>
+        <v>0.6593</v>
       </c>
       <c r="J60" t="n">
-        <v>12.411</v>
+        <v>13.8453</v>
       </c>
     </row>
     <row r="61">
@@ -6675,10 +6675,10 @@
         <v>1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>0.439</v>
+        <v>0.4892</v>
       </c>
       <c r="J61" t="n">
-        <v>9.218999999999999</v>
+        <v>10.2732</v>
       </c>
     </row>
     <row r="62">
@@ -6715,10 +6715,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3647</v>
+        <v>0.3801</v>
       </c>
       <c r="J62" t="n">
-        <v>10.2116</v>
+        <v>10.6428</v>
       </c>
     </row>
     <row r="63">
@@ -6755,10 +6755,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0448</v>
+        <v>-0.0542</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.2544</v>
+        <v>-1.5176</v>
       </c>
     </row>
     <row r="64">
@@ -6795,10 +6795,10 @@
         <v>0.89</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.138</v>
+        <v>-0.1526</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.864</v>
+        <v>-4.2728</v>
       </c>
     </row>
     <row r="65">
@@ -6835,10 +6835,10 @@
         <v>0.83</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2008</v>
+        <v>-0.2161</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.6224</v>
+        <v>-6.0508</v>
       </c>
     </row>
     <row r="66">
@@ -6875,10 +6875,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.211</v>
+        <v>-0.2263</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.908</v>
+        <v>-6.3364</v>
       </c>
     </row>
     <row r="67">
@@ -6915,10 +6915,10 @@
         <v>1.29</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6086</v>
+        <v>0.6713</v>
       </c>
       <c r="J67" t="n">
-        <v>17.0408</v>
+        <v>18.7964</v>
       </c>
     </row>
     <row r="68">
@@ -6955,10 +6955,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.494</v>
+        <v>0.5442</v>
       </c>
       <c r="J68" t="n">
-        <v>13.832</v>
+        <v>15.2376</v>
       </c>
     </row>
     <row r="69">
@@ -6995,10 +6995,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4196</v>
+        <v>0.46</v>
       </c>
       <c r="J69" t="n">
-        <v>11.7488</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="70">
@@ -7035,10 +7035,10 @@
         <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1748</v>
+        <v>0.185</v>
       </c>
       <c r="J70" t="n">
-        <v>4.8944</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="71">
@@ -7075,10 +7075,10 @@
         <v>0.83</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.0468</v>
+        <v>-15.0864</v>
       </c>
     </row>
     <row r="72">
@@ -7115,10 +7115,10 @@
         <v>0.87</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1336</v>
+        <v>-0.1546</v>
       </c>
       <c r="J72" t="n">
-        <v>-2.8056</v>
+        <v>-3.2466</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>0.75</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2567</v>
+        <v>-0.2765</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.3907</v>
+        <v>-5.8065</v>
       </c>
     </row>
     <row r="74">
@@ -7195,10 +7195,10 @@
         <v>0.75</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2567</v>
+        <v>-0.2765</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.3907</v>
+        <v>-5.8065</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>0.74</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2656</v>
+        <v>-0.2853</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.5776</v>
+        <v>-5.9913</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.396</v>
+        <v>-0.4111</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.633100000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1269</v>
+        <v>1.2394</v>
       </c>
       <c r="J77" t="n">
-        <v>23.6649</v>
+        <v>26.0274</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.46</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7887</v>
+        <v>0.8774</v>
       </c>
       <c r="J78" t="n">
-        <v>16.5627</v>
+        <v>18.4254</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>1.39</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7016</v>
+        <v>0.7825</v>
       </c>
       <c r="J79" t="n">
-        <v>14.7336</v>
+        <v>16.4325</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3754</v>
+        <v>0.4104</v>
       </c>
       <c r="J80" t="n">
-        <v>7.8834</v>
+        <v>8.618399999999999</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0837</v>
+        <v>-0.0581</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.7577</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="82">
@@ -7515,10 +7515,10 @@
         <v>0.7</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2274</v>
+        <v>-0.2627</v>
       </c>
       <c r="J82" t="n">
-        <v>-4.3206</v>
+        <v>-4.9913</v>
       </c>
     </row>
     <row r="83">
@@ -7555,10 +7555,10 @@
         <v>0.68</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2505</v>
+        <v>-0.2844</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.7595</v>
+        <v>-5.4036</v>
       </c>
     </row>
     <row r="84">
@@ -7595,10 +7595,10 @@
         <v>0.35</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5818</v>
+        <v>-0.5919</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.0542</v>
+        <v>-11.2461</v>
       </c>
     </row>
     <row r="85">
@@ -7635,10 +7635,10 @@
         <v>0.34</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5919</v>
+        <v>-0.601</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.2461</v>
+        <v>-11.419</v>
       </c>
     </row>
     <row r="86">
@@ -7675,10 +7675,10 @@
         <v>0.29</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6425</v>
+        <v>-0.647</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.2075</v>
+        <v>-12.293</v>
       </c>
     </row>
     <row r="87">
@@ -7715,10 +7715,10 @@
         <v>2.14</v>
       </c>
       <c r="I87" t="n">
-        <v>1.5117</v>
+        <v>1.6534</v>
       </c>
       <c r="J87" t="n">
-        <v>28.7223</v>
+        <v>31.4146</v>
       </c>
     </row>
     <row r="88">
@@ -7755,10 +7755,10 @@
         <v>1.63</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9573</v>
+        <v>1.0667</v>
       </c>
       <c r="J88" t="n">
-        <v>18.1887</v>
+        <v>20.2673</v>
       </c>
     </row>
     <row r="89">
@@ -7795,10 +7795,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.9433</v>
       </c>
       <c r="J89" t="n">
-        <v>16.0208</v>
+        <v>17.9227</v>
       </c>
     </row>
     <row r="90">
@@ -7835,10 +7835,10 @@
         <v>1.46</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7593</v>
+        <v>0.8522</v>
       </c>
       <c r="J90" t="n">
-        <v>14.4267</v>
+        <v>16.1918</v>
       </c>
     </row>
     <row r="91">
@@ -7875,10 +7875,10 @@
         <v>1.45</v>
       </c>
       <c r="I91" t="n">
-        <v>0.7471</v>
+        <v>0.8389</v>
       </c>
       <c r="J91" t="n">
-        <v>14.1949</v>
+        <v>15.9391</v>
       </c>
     </row>
     <row r="92">
@@ -7915,10 +7915,10 @@
         <v>1.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5579</v>
+        <v>0.6369</v>
       </c>
       <c r="J92" t="n">
-        <v>15.0633</v>
+        <v>17.1963</v>
       </c>
     </row>
     <row r="93">
@@ -7955,10 +7955,10 @@
         <v>1.19</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2749</v>
+        <v>0.2911</v>
       </c>
       <c r="J93" t="n">
-        <v>7.4223</v>
+        <v>7.8597</v>
       </c>
     </row>
     <row r="94">
@@ -7995,10 +7995,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1726</v>
+        <v>0.1891</v>
       </c>
       <c r="J94" t="n">
-        <v>4.6602</v>
+        <v>5.1057</v>
       </c>
     </row>
     <row r="95">
@@ -8035,10 +8035,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.05</v>
+        <v>-0.0535</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.35</v>
+        <v>-1.4445</v>
       </c>
     </row>
     <row r="96">
@@ -8075,10 +8075,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1929</v>
+        <v>-0.2029</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.2083</v>
+        <v>-5.4783</v>
       </c>
     </row>
     <row r="97">
@@ -8115,10 +8115,10 @@
         <v>1.14</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2669</v>
+        <v>0.2702</v>
       </c>
       <c r="J97" t="n">
-        <v>7.2063</v>
+        <v>7.2954</v>
       </c>
     </row>
     <row r="98">
@@ -8155,10 +8155,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2046</v>
+        <v>0.2097</v>
       </c>
       <c r="J98" t="n">
-        <v>5.5242</v>
+        <v>5.6619</v>
       </c>
     </row>
     <row r="99">
@@ -8195,10 +8195,10 @@
         <v>1.08</v>
       </c>
       <c r="I99" t="n">
-        <v>0.172</v>
+        <v>0.1776</v>
       </c>
       <c r="J99" t="n">
-        <v>4.644</v>
+        <v>4.7952</v>
       </c>
     </row>
     <row r="100">
@@ -8235,10 +8235,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2699</v>
+        <v>-0.2846</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.2873</v>
+        <v>-7.6842</v>
       </c>
     </row>
     <row r="101">
@@ -8275,10 +8275,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.458</v>
+        <v>-0.4659</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.366</v>
+        <v>-12.5793</v>
       </c>
     </row>
     <row r="102">
@@ -8315,10 +8315,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.68</v>
+        <v>0.763</v>
       </c>
       <c r="J102" t="n">
-        <v>19.04</v>
+        <v>21.364</v>
       </c>
     </row>
     <row r="103">
@@ -8355,10 +8355,10 @@
         <v>1.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4095</v>
+        <v>0.4548</v>
       </c>
       <c r="J103" t="n">
-        <v>11.466</v>
+        <v>12.7344</v>
       </c>
     </row>
     <row r="104">
@@ -8395,10 +8395,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1231</v>
+        <v>0.1364</v>
       </c>
       <c r="J104" t="n">
-        <v>3.4468</v>
+        <v>3.8192</v>
       </c>
     </row>
     <row r="105">
@@ -8435,10 +8435,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0756</v>
+        <v>0.0885</v>
       </c>
       <c r="J105" t="n">
-        <v>2.1168</v>
+        <v>2.478</v>
       </c>
     </row>
     <row r="106">
@@ -8475,10 +8475,10 @@
         <v>0.73</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3193</v>
+        <v>-0.329</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.9404</v>
+        <v>-9.212</v>
       </c>
     </row>
     <row r="107">
@@ -8515,10 +8515,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6394</v>
+        <v>0.7015</v>
       </c>
       <c r="J107" t="n">
-        <v>17.9032</v>
+        <v>19.642</v>
       </c>
     </row>
     <row r="108">
@@ -8555,10 +8555,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5962</v>
+        <v>0.6541</v>
       </c>
       <c r="J108" t="n">
-        <v>16.6936</v>
+        <v>18.3148</v>
       </c>
     </row>
     <row r="109">
@@ -8595,10 +8595,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1752</v>
+        <v>-0.1762</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.9056</v>
+        <v>-4.9336</v>
       </c>
     </row>
     <row r="110">
@@ -8635,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3317</v>
+        <v>-0.3234</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.287599999999999</v>
+        <v>-9.055199999999999</v>
       </c>
     </row>
     <row r="111">
@@ -8675,10 +8675,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7108</v>
+        <v>-0.6644</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.9024</v>
+        <v>-18.6032</v>
       </c>
     </row>
     <row r="112">
@@ -8715,10 +8715,10 @@
         <v>0.98</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0042</v>
+        <v>-0.0181</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.0924</v>
+        <v>-0.3982</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>0.92</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0849</v>
+        <v>-0.103</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.8678</v>
+        <v>-2.266</v>
       </c>
     </row>
     <row r="114">
@@ -8795,10 +8795,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2329</v>
+        <v>-0.2519</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.1238</v>
+        <v>-5.5418</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2706</v>
+        <v>-0.2891</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.9532</v>
+        <v>-6.3602</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4863</v>
+        <v>-0.4954</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.6986</v>
+        <v>-10.8988</v>
       </c>
     </row>
     <row r="117">
@@ -8915,10 +8915,10 @@
         <v>1.89</v>
       </c>
       <c r="I117" t="n">
-        <v>1.279</v>
+        <v>1.4032</v>
       </c>
       <c r="J117" t="n">
-        <v>28.138</v>
+        <v>30.8704</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>1.47</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7896</v>
+        <v>0.881</v>
       </c>
       <c r="J118" t="n">
-        <v>17.3712</v>
+        <v>19.382</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7184</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>15.8048</v>
+        <v>17.6638</v>
       </c>
     </row>
     <row r="120">
@@ -9035,10 +9035,10 @@
         <v>1.24</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4956</v>
+        <v>0.5565</v>
       </c>
       <c r="J120" t="n">
-        <v>10.9032</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4384</v>
+        <v>0.4924</v>
       </c>
       <c r="J121" t="n">
-        <v>9.6448</v>
+        <v>10.8328</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.95</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3584</v>
+        <v>1.4846</v>
       </c>
       <c r="J122" t="n">
-        <v>31.2432</v>
+        <v>34.1458</v>
       </c>
     </row>
     <row r="123">
@@ -9155,10 +9155,10 @@
         <v>1.6</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9510999999999999</v>
+        <v>1.0541</v>
       </c>
       <c r="J123" t="n">
-        <v>21.8753</v>
+        <v>24.2443</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6732</v>
+        <v>0.7521</v>
       </c>
       <c r="J124" t="n">
-        <v>15.4836</v>
+        <v>17.2983</v>
       </c>
     </row>
     <row r="125">
@@ -9235,10 +9235,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5152</v>
+        <v>0.577</v>
       </c>
       <c r="J125" t="n">
-        <v>11.8496</v>
+        <v>13.271</v>
       </c>
     </row>
     <row r="126">
@@ -9275,10 +9275,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6908</v>
+        <v>-0.6317</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.8884</v>
+        <v>-14.5291</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5444</v>
+        <v>0.5854</v>
       </c>
       <c r="J127" t="n">
-        <v>12.5212</v>
+        <v>13.4642</v>
       </c>
     </row>
     <row r="128">
@@ -9355,10 +9355,10 @@
         <v>0.86</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1393</v>
+        <v>-0.1614</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.2039</v>
+        <v>-3.7122</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>0.59</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4015</v>
+        <v>-0.417</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.234500000000001</v>
+        <v>-9.590999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>0.5</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4856</v>
+        <v>-0.4963</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.1688</v>
+        <v>-11.4149</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.39</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.588</v>
+        <v>-0.5916</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.524</v>
+        <v>-13.6068</v>
       </c>
     </row>
     <row r="132">
@@ -9515,10 +9515,10 @@
         <v>1.22</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5109</v>
+        <v>0.5626</v>
       </c>
       <c r="J132" t="n">
-        <v>18.3924</v>
+        <v>20.2536</v>
       </c>
     </row>
     <row r="133">
@@ -9555,10 +9555,10 @@
         <v>1.11</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3428</v>
+        <v>0.3496</v>
       </c>
       <c r="J133" t="n">
-        <v>12.3408</v>
+        <v>12.5856</v>
       </c>
     </row>
     <row r="134">
@@ -9595,10 +9595,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2089</v>
+        <v>0.2168</v>
       </c>
       <c r="J134" t="n">
-        <v>7.5204</v>
+        <v>7.8048</v>
       </c>
     </row>
     <row r="135">
@@ -9635,10 +9635,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1775</v>
+        <v>0.1869</v>
       </c>
       <c r="J135" t="n">
-        <v>6.39</v>
+        <v>6.7284</v>
       </c>
     </row>
     <row r="136">
@@ -9675,10 +9675,10 @@
         <v>1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J136" t="n">
-        <v>5.2164</v>
+        <v>5.6016</v>
       </c>
     </row>
     <row r="137">
@@ -9715,10 +9715,10 @@
         <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4142</v>
+        <v>0.4566</v>
       </c>
       <c r="J137" t="n">
-        <v>14.9112</v>
+        <v>16.4376</v>
       </c>
     </row>
     <row r="138">
@@ -9755,10 +9755,10 @@
         <v>1.15</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3357</v>
+        <v>0.3429</v>
       </c>
       <c r="J138" t="n">
-        <v>12.0852</v>
+        <v>12.3444</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>1.05</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1363</v>
+        <v>0.1457</v>
       </c>
       <c r="J139" t="n">
-        <v>4.9068</v>
+        <v>5.2452</v>
       </c>
     </row>
     <row r="140">
@@ -9835,10 +9835,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1017</v>
+        <v>-0.1128</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.6612</v>
+        <v>-4.0608</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3094</v>
+        <v>-0.3212</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.1384</v>
+        <v>-11.5632</v>
       </c>
     </row>
     <row r="142">
@@ -9915,10 +9915,10 @@
         <v>1.28</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6005</v>
+        <v>0.661</v>
       </c>
       <c r="J142" t="n">
-        <v>21.618</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="143">
@@ -9955,10 +9955,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4084</v>
+        <v>0.4449</v>
       </c>
       <c r="J143" t="n">
-        <v>14.7024</v>
+        <v>16.0164</v>
       </c>
     </row>
     <row r="144">
@@ -9995,10 +9995,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2704</v>
+        <v>0.2742</v>
       </c>
       <c r="J144" t="n">
-        <v>9.734400000000001</v>
+        <v>9.8712</v>
       </c>
     </row>
     <row r="145">
@@ -10035,10 +10035,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0771</v>
+        <v>0.0883</v>
       </c>
       <c r="J145" t="n">
-        <v>2.7756</v>
+        <v>3.1788</v>
       </c>
     </row>
     <row r="146">
@@ -10075,10 +10075,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4294</v>
+        <v>-0.4105</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.4584</v>
+        <v>-14.778</v>
       </c>
     </row>
     <row r="147">
@@ -10115,10 +10115,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5672</v>
       </c>
       <c r="J147" t="n">
-        <v>18.3816</v>
+        <v>20.4192</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>1.18</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3736</v>
+        <v>0.3987</v>
       </c>
       <c r="J148" t="n">
-        <v>13.4496</v>
+        <v>14.3532</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>1.12</v>
       </c>
       <c r="I149" t="n">
-        <v>0.286</v>
+        <v>0.2905</v>
       </c>
       <c r="J149" t="n">
-        <v>10.296</v>
+        <v>10.458</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2788</v>
+        <v>-0.2916</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.0368</v>
+        <v>-10.4976</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3926</v>
+        <v>-0.4021</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.1336</v>
+        <v>-14.4756</v>
       </c>
     </row>
     <row r="152">
@@ -10315,10 +10315,10 @@
         <v>1.12</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3686</v>
+        <v>0.3849</v>
       </c>
       <c r="J152" t="n">
-        <v>12.5324</v>
+        <v>13.0866</v>
       </c>
     </row>
     <row r="153">
@@ -10355,10 +10355,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.279</v>
+        <v>0.28</v>
       </c>
       <c r="J153" t="n">
-        <v>9.486000000000001</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="154">
@@ -10395,10 +10395,10 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0871</v>
+        <v>0.0951</v>
       </c>
       <c r="J154" t="n">
-        <v>2.9614</v>
+        <v>3.2334</v>
       </c>
     </row>
     <row r="155">
@@ -10435,10 +10435,10 @@
         <v>1.02</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0871</v>
+        <v>0.0951</v>
       </c>
       <c r="J155" t="n">
-        <v>2.9614</v>
+        <v>3.2334</v>
       </c>
     </row>
     <row r="156">
@@ -10475,10 +10475,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2073</v>
+        <v>-0.2072</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.0482</v>
+        <v>-7.0448</v>
       </c>
     </row>
     <row r="157">
@@ -10515,10 +10515,10 @@
         <v>1.47</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6676</v>
+        <v>0.7444</v>
       </c>
       <c r="J157" t="n">
-        <v>22.6984</v>
+        <v>25.3096</v>
       </c>
     </row>
     <row r="158">
@@ -10555,10 +10555,10 @@
         <v>1.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1601</v>
+        <v>0.1689</v>
       </c>
       <c r="J158" t="n">
-        <v>5.4434</v>
+        <v>5.7426</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.089</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.026</v>
+        <v>-3.3864</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>0.93</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1009</v>
+        <v>-0.1122</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.4306</v>
+        <v>-3.8148</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3933</v>
+        <v>-0.4026</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.3722</v>
+        <v>-13.6884</v>
       </c>
     </row>
     <row r="162">
@@ -10715,10 +10715,10 @@
         <v>1.19</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4309</v>
+        <v>0.4244</v>
       </c>
       <c r="J162" t="n">
-        <v>10.7725</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="163">
@@ -10755,10 +10755,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1913</v>
+        <v>0.1972</v>
       </c>
       <c r="J163" t="n">
-        <v>4.7825</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="164">
@@ -10795,10 +10795,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0431</v>
+        <v>0.0472</v>
       </c>
       <c r="J164" t="n">
-        <v>1.0775</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="165">
@@ -10835,10 +10835,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2151</v>
+        <v>-0.2294</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.3775</v>
+        <v>-5.735</v>
       </c>
     </row>
     <row r="166">
@@ -10875,10 +10875,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2845</v>
+        <v>-0.298</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.1125</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="167">
@@ -10915,10 +10915,10 @@
         <v>1.38</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9747</v>
+        <v>0.9157</v>
       </c>
       <c r="J167" t="n">
-        <v>24.3675</v>
+        <v>22.8925</v>
       </c>
     </row>
     <row r="168">
@@ -10955,10 +10955,10 @@
         <v>1.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5627</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>14.0675</v>
+        <v>13.6725</v>
       </c>
     </row>
     <row r="169">
@@ -10995,10 +10995,10 @@
         <v>1.18</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5151</v>
+        <v>0.5037</v>
       </c>
       <c r="J169" t="n">
-        <v>12.8775</v>
+        <v>12.5925</v>
       </c>
     </row>
     <row r="170">
@@ -11035,10 +11035,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3067</v>
+        <v>0.3131</v>
       </c>
       <c r="J170" t="n">
-        <v>7.6675</v>
+        <v>7.8275</v>
       </c>
     </row>
     <row r="171">
@@ -11075,10 +11075,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1567</v>
+        <v>0.1726</v>
       </c>
       <c r="J171" t="n">
-        <v>3.9175</v>
+        <v>4.315</v>
       </c>
     </row>
     <row r="172">
@@ -11115,10 +11115,10 @@
         <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0298</v>
       </c>
       <c r="J172" t="n">
-        <v>1.7204</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="173">
@@ -11155,10 +11155,10 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3273</v>
+        <v>-0.3478</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.5279</v>
+        <v>-7.9994</v>
       </c>
     </row>
     <row r="174">
@@ -11195,10 +11195,10 @@
         <v>0.61</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3714</v>
+        <v>-0.3904</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.542199999999999</v>
+        <v>-8.979200000000001</v>
       </c>
     </row>
     <row r="175">
@@ -11235,10 +11235,10 @@
         <v>0.55</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.821</v>
+        <v>-10.1913</v>
       </c>
     </row>
     <row r="176">
@@ -11275,10 +11275,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5304</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.1992</v>
+        <v>-12.4154</v>
       </c>
     </row>
     <row r="177">
@@ -11315,10 +11315,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2724</v>
+        <v>1.2522</v>
       </c>
       <c r="J177" t="n">
-        <v>29.2652</v>
+        <v>28.8006</v>
       </c>
     </row>
     <row r="178">
@@ -11355,10 +11355,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0294</v>
+        <v>0.9842</v>
       </c>
       <c r="J178" t="n">
-        <v>23.6762</v>
+        <v>22.6366</v>
       </c>
     </row>
     <row r="179">
@@ -11395,10 +11395,10 @@
         <v>1.41</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9341</v>
       </c>
       <c r="J179" t="n">
-        <v>22.6182</v>
+        <v>21.4843</v>
       </c>
     </row>
     <row r="180">
@@ -11435,10 +11435,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.665</v>
+        <v>0.6466</v>
       </c>
       <c r="J180" t="n">
-        <v>15.295</v>
+        <v>14.8718</v>
       </c>
     </row>
     <row r="181">
@@ -11475,10 +11475,10 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>0.594</v>
+        <v>0.5835</v>
       </c>
       <c r="J181" t="n">
-        <v>13.662</v>
+        <v>13.4205</v>
       </c>
     </row>
     <row r="182">
@@ -11515,10 +11515,10 @@
         <v>1.47</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1165</v>
+        <v>1.0747</v>
       </c>
       <c r="J182" t="n">
-        <v>30.1455</v>
+        <v>29.0169</v>
       </c>
     </row>
     <row r="183">
@@ -11555,10 +11555,10 @@
         <v>1.19</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5457</v>
+        <v>0.53</v>
       </c>
       <c r="J183" t="n">
-        <v>14.7339</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="184">
@@ -11595,10 +11595,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5209</v>
+        <v>0.5077</v>
       </c>
       <c r="J184" t="n">
-        <v>14.0643</v>
+        <v>13.7079</v>
       </c>
     </row>
     <row r="185">
@@ -11635,10 +11635,10 @@
         <v>1.05</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1656</v>
+        <v>0.1787</v>
       </c>
       <c r="J185" t="n">
-        <v>4.4712</v>
+        <v>4.8249</v>
       </c>
     </row>
     <row r="186">
@@ -11675,10 +11675,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5565</v>
+        <v>-0.5219</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.0255</v>
+        <v>-14.0913</v>
       </c>
     </row>
     <row r="187">
@@ -11715,10 +11715,10 @@
         <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>0.718</v>
+        <v>0.6862</v>
       </c>
       <c r="J187" t="n">
-        <v>19.386</v>
+        <v>18.5274</v>
       </c>
     </row>
     <row r="188">
@@ -11755,10 +11755,10 @@
         <v>1.07</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1919</v>
+        <v>0.1976</v>
       </c>
       <c r="J188" t="n">
-        <v>5.1813</v>
+        <v>5.3352</v>
       </c>
     </row>
     <row r="189">
@@ -11795,10 +11795,10 @@
         <v>0.89</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1415</v>
+        <v>-0.1553</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.8205</v>
+        <v>-4.1931</v>
       </c>
     </row>
     <row r="190">
@@ -11835,10 +11835,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1735</v>
+        <v>-0.1879</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.6845</v>
+        <v>-5.0733</v>
       </c>
     </row>
     <row r="191">
@@ -11875,10 +11875,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.37</v>
+        <v>-0.381</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.99</v>
+        <v>-10.287</v>
       </c>
     </row>
     <row r="192">
@@ -11915,10 +11915,10 @@
         <v>1.54</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1772</v>
+        <v>1.1454</v>
       </c>
       <c r="J192" t="n">
-        <v>25.8984</v>
+        <v>25.1988</v>
       </c>
     </row>
     <row r="193">
@@ -11955,10 +11955,10 @@
         <v>1.5</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1271</v>
+        <v>1.0916</v>
       </c>
       <c r="J193" t="n">
-        <v>24.7962</v>
+        <v>24.0152</v>
       </c>
     </row>
     <row r="194">
@@ -11995,10 +11995,10 @@
         <v>1.4</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9895</v>
+        <v>0.9353</v>
       </c>
       <c r="J194" t="n">
-        <v>21.769</v>
+        <v>20.5766</v>
       </c>
     </row>
     <row r="195">
@@ -12035,10 +12035,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2295</v>
+        <v>0.246</v>
       </c>
       <c r="J195" t="n">
-        <v>5.049</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="196">
@@ -12075,10 +12075,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6897</v>
+        <v>-0.6357</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.1734</v>
+        <v>-13.9854</v>
       </c>
     </row>
     <row r="197">
@@ -12115,10 +12115,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0225</v>
+        <v>-0.0369</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.495</v>
+        <v>-0.8118</v>
       </c>
     </row>
     <row r="198">
@@ -12155,10 +12155,10 @@
         <v>0.9</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1112</v>
+        <v>-0.1293</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.4464</v>
+        <v>-2.8446</v>
       </c>
     </row>
     <row r="199">
@@ -12195,10 +12195,10 @@
         <v>0.88</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1338</v>
+        <v>-0.1522</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.9436</v>
+        <v>-3.3484</v>
       </c>
     </row>
     <row r="200">
@@ -12235,10 +12235,10 @@
         <v>0.73</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.282</v>
+        <v>-0.2998</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.204</v>
+        <v>-6.5956</v>
       </c>
     </row>
     <row r="201">
@@ -12275,10 +12275,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.479</v>
+        <v>-0.4882</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.538</v>
+        <v>-10.7404</v>
       </c>
     </row>
     <row r="202">
@@ -12315,10 +12315,10 @@
         <v>1.19</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2821</v>
+        <v>0.2965</v>
       </c>
       <c r="J202" t="n">
-        <v>8.462999999999999</v>
+        <v>8.895</v>
       </c>
     </row>
     <row r="203">
@@ -12355,10 +12355,10 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2564</v>
+        <v>0.2714</v>
       </c>
       <c r="J203" t="n">
-        <v>7.692</v>
+        <v>8.141999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -12395,10 +12395,10 @@
         <v>1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2172</v>
+        <v>0.2326</v>
       </c>
       <c r="J204" t="n">
-        <v>6.516</v>
+        <v>6.978</v>
       </c>
     </row>
     <row r="205">
@@ -12435,10 +12435,10 @@
         <v>0.99</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0289</v>
+        <v>-0.0316</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.867</v>
+        <v>-0.948</v>
       </c>
     </row>
     <row r="206">
@@ -12475,10 +12475,10 @@
         <v>0.96</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.172</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="207">
@@ -12515,10 +12515,10 @@
         <v>1.15</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2618</v>
+        <v>0.2695</v>
       </c>
       <c r="J207" t="n">
-        <v>7.854</v>
+        <v>8.085000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2323</v>
+        <v>0.241</v>
       </c>
       <c r="J208" t="n">
-        <v>6.969</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="209">
@@ -12595,10 +12595,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1867</v>
+        <v>0.1964</v>
       </c>
       <c r="J209" t="n">
-        <v>5.601</v>
+        <v>5.892</v>
       </c>
     </row>
     <row r="210">
@@ -12635,10 +12635,10 @@
         <v>1.02</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0494</v>
+        <v>0.0567</v>
       </c>
       <c r="J210" t="n">
-        <v>1.482</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3842</v>
+        <v>-0.3939</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.526</v>
+        <v>-11.817</v>
       </c>
     </row>
     <row r="212">
@@ -12715,10 +12715,10 @@
         <v>0.91</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0543</v>
+        <v>-0.0819</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.9774</v>
+        <v>-1.4742</v>
       </c>
     </row>
     <row r="213">
@@ -12755,10 +12755,10 @@
         <v>0.83</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1505</v>
+        <v>-0.1771</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.709</v>
+        <v>-3.1878</v>
       </c>
     </row>
     <row r="214">
@@ -12795,10 +12795,10 @@
         <v>0.53</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4439</v>
+        <v>-0.4593</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.9902</v>
+        <v>-8.2674</v>
       </c>
     </row>
     <row r="215">
@@ -12835,10 +12835,10 @@
         <v>0.46</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5098</v>
+        <v>-0.5208</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.176399999999999</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="216">
@@ -12875,10 +12875,10 @@
         <v>0.46</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5098</v>
+        <v>-0.5208</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.176399999999999</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="217">
@@ -12915,10 +12915,10 @@
         <v>2.21</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8338</v>
+        <v>1.909</v>
       </c>
       <c r="J217" t="n">
-        <v>33.0084</v>
+        <v>34.362</v>
       </c>
     </row>
     <row r="218">
@@ -12955,10 +12955,10 @@
         <v>1.86</v>
       </c>
       <c r="I218" t="n">
-        <v>1.5075</v>
+        <v>1.5049</v>
       </c>
       <c r="J218" t="n">
-        <v>27.135</v>
+        <v>27.0882</v>
       </c>
     </row>
     <row r="219">
@@ -12995,10 +12995,10 @@
         <v>1.35</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8486</v>
+        <v>0.8123</v>
       </c>
       <c r="J219" t="n">
-        <v>15.2748</v>
+        <v>14.6214</v>
       </c>
     </row>
     <row r="220">
@@ -13035,10 +13035,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1489</v>
+        <v>0.1825</v>
       </c>
       <c r="J220" t="n">
-        <v>2.6802</v>
+        <v>3.285</v>
       </c>
     </row>
     <row r="221">
@@ -13075,10 +13075,10 @@
         <v>0.99</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1689</v>
+        <v>-0.1393</v>
       </c>
       <c r="J221" t="n">
-        <v>-3.0402</v>
+        <v>-2.5074</v>
       </c>
     </row>
     <row r="222">
@@ -13115,10 +13115,10 @@
         <v>1.05</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1653</v>
+        <v>0.1667</v>
       </c>
       <c r="J222" t="n">
-        <v>4.4631</v>
+        <v>4.5009</v>
       </c>
     </row>
     <row r="223">
@@ -13155,10 +13155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0795</v>
+        <v>-0.0925</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.1465</v>
+        <v>-2.4975</v>
       </c>
     </row>
     <row r="224">
@@ -13195,10 +13195,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1454</v>
+        <v>-0.161</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.9258</v>
+        <v>-4.347</v>
       </c>
     </row>
     <row r="225">
@@ -13235,10 +13235,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1662</v>
+        <v>-0.1822</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.4874</v>
+        <v>-4.9194</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2469</v>
+        <v>-0.2627</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.6663</v>
+        <v>-7.0929</v>
       </c>
     </row>
     <row r="227">
@@ -13315,10 +13315,10 @@
         <v>1.55</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1985</v>
+        <v>1.1666</v>
       </c>
       <c r="J227" t="n">
-        <v>32.3595</v>
+        <v>31.4982</v>
       </c>
     </row>
     <row r="228">
@@ -13355,10 +13355,10 @@
         <v>1.24</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6492</v>
+        <v>0.6262</v>
       </c>
       <c r="J228" t="n">
-        <v>17.5284</v>
+        <v>16.9074</v>
       </c>
     </row>
     <row r="229">
@@ -13395,10 +13395,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6263</v>
+        <v>0.6057</v>
       </c>
       <c r="J229" t="n">
-        <v>16.9101</v>
+        <v>16.3539</v>
       </c>
     </row>
     <row r="230">
@@ -13435,10 +13435,10 @@
         <v>1.2</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5564</v>
+        <v>0.5427</v>
       </c>
       <c r="J230" t="n">
-        <v>15.0228</v>
+        <v>14.6529</v>
       </c>
     </row>
     <row r="231">
@@ -13475,10 +13475,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3807</v>
+        <v>-0.3577</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.2789</v>
+        <v>-9.6579</v>
       </c>
     </row>
     <row r="232">
@@ -13515,10 +13515,10 @@
         <v>1.2</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3209</v>
+        <v>0.3287</v>
       </c>
       <c r="J232" t="n">
-        <v>11.2315</v>
+        <v>11.5045</v>
       </c>
     </row>
     <row r="233">
@@ -13555,10 +13555,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3209</v>
+        <v>0.3287</v>
       </c>
       <c r="J233" t="n">
-        <v>11.2315</v>
+        <v>11.5045</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1777</v>
+        <v>0.1898</v>
       </c>
       <c r="J234" t="n">
-        <v>6.2195</v>
+        <v>6.643</v>
       </c>
     </row>
     <row r="235">
@@ -13635,10 +13635,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0992</v>
+        <v>0.1104</v>
       </c>
       <c r="J235" t="n">
-        <v>3.472</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="236">
@@ -13675,10 +13675,10 @@
         <v>0.79</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2566</v>
+        <v>-0.2683</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.981</v>
+        <v>-9.390499999999999</v>
       </c>
     </row>
     <row r="237">
@@ -13715,10 +13715,10 @@
         <v>1.4</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5436</v>
+        <v>0.5448</v>
       </c>
       <c r="J237" t="n">
-        <v>19.026</v>
+        <v>19.068</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3128</v>
+        <v>0.3253</v>
       </c>
       <c r="J238" t="n">
-        <v>10.948</v>
+        <v>11.3855</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.04</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0769</v>
+        <v>0.0883</v>
       </c>
       <c r="J239" t="n">
-        <v>2.6915</v>
+        <v>3.0905</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2051</v>
+        <v>-0.2172</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.1785</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2357</v>
+        <v>-0.2478</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.249499999999999</v>
+        <v>-8.673</v>
       </c>
     </row>
     <row r="242">
@@ -13915,10 +13915,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.229</v>
+        <v>1.2027</v>
       </c>
       <c r="J242" t="n">
-        <v>31.954</v>
+        <v>31.2702</v>
       </c>
     </row>
     <row r="243">
@@ -13955,10 +13955,10 @@
         <v>1.54</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1677</v>
+        <v>1.137</v>
       </c>
       <c r="J243" t="n">
-        <v>30.3602</v>
+        <v>29.562</v>
       </c>
     </row>
     <row r="244">
@@ -13995,10 +13995,10 @@
         <v>1.45</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0555</v>
+        <v>1.0119</v>
       </c>
       <c r="J244" t="n">
-        <v>27.443</v>
+        <v>26.3094</v>
       </c>
     </row>
     <row r="245">
@@ -14035,10 +14035,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4127</v>
+        <v>0.4168</v>
       </c>
       <c r="J245" t="n">
-        <v>10.7302</v>
+        <v>10.8368</v>
       </c>
     </row>
     <row r="246">
@@ -14075,10 +14075,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6478</v>
+        <v>-0.5964</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.8428</v>
+        <v>-15.5064</v>
       </c>
     </row>
     <row r="247">
@@ -14115,10 +14115,10 @@
         <v>1.04</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1749</v>
+        <v>0.1675</v>
       </c>
       <c r="J247" t="n">
-        <v>4.5474</v>
+        <v>4.355</v>
       </c>
     </row>
     <row r="248">
@@ -14155,10 +14155,10 @@
         <v>0.85</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1679</v>
+        <v>-0.1861</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.3654</v>
+        <v>-4.8386</v>
       </c>
     </row>
     <row r="249">
@@ -14195,10 +14195,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2647</v>
+        <v>-0.2826</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.8822</v>
+        <v>-7.3476</v>
       </c>
     </row>
     <row r="250">
@@ -14235,10 +14235,10 @@
         <v>0.72</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2934</v>
+        <v>-0.3106</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.6284</v>
+        <v>-8.0756</v>
       </c>
     </row>
     <row r="251">
@@ -14275,10 +14275,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.303</v>
+        <v>-0.3199</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.878</v>
+        <v>-8.317399999999999</v>
       </c>
     </row>
     <row r="252">
@@ -14315,10 +14315,10 @@
         <v>1.63</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3057</v>
+        <v>1.2794</v>
       </c>
       <c r="J252" t="n">
-        <v>39.171</v>
+        <v>38.382</v>
       </c>
     </row>
     <row r="253">
@@ -14355,10 +14355,10 @@
         <v>1.27</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7241</v>
+        <v>0.6918</v>
       </c>
       <c r="J253" t="n">
-        <v>21.723</v>
+        <v>20.754</v>
       </c>
     </row>
     <row r="254">
@@ -14395,10 +14395,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7008</v>
+        <v>0.6711</v>
       </c>
       <c r="J254" t="n">
-        <v>21.024</v>
+        <v>20.133</v>
       </c>
     </row>
     <row r="255">
@@ -14435,10 +14435,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3847</v>
+        <v>0.3858</v>
       </c>
       <c r="J255" t="n">
-        <v>11.541</v>
+        <v>11.574</v>
       </c>
     </row>
     <row r="256">
@@ -14475,10 +14475,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9003</v>
+        <v>-0.8237</v>
       </c>
       <c r="J256" t="n">
-        <v>-27.009</v>
+        <v>-24.711</v>
       </c>
     </row>
     <row r="257">
@@ -14515,10 +14515,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.478</v>
+        <v>0.4661</v>
       </c>
       <c r="J257" t="n">
-        <v>14.34</v>
+        <v>13.983</v>
       </c>
     </row>
     <row r="258">
@@ -14555,10 +14555,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1532</v>
+        <v>0.1579</v>
       </c>
       <c r="J258" t="n">
-        <v>4.596</v>
+        <v>4.737</v>
       </c>
     </row>
     <row r="259">
@@ -14595,10 +14595,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1045</v>
+        <v>0.1091</v>
       </c>
       <c r="J259" t="n">
-        <v>3.135</v>
+        <v>3.273</v>
       </c>
     </row>
     <row r="260">
@@ -14635,10 +14635,10 @@
         <v>0.79</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.242</v>
+        <v>-0.2569</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.26</v>
+        <v>-7.707</v>
       </c>
     </row>
     <row r="261">
@@ -14675,10 +14675,10 @@
         <v>0.63</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3952</v>
+        <v>-0.4057</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.856</v>
+        <v>-12.171</v>
       </c>
     </row>
     <row r="262">
@@ -14715,10 +14715,10 @@
         <v>1.46</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8437</v>
+        <v>0.8078</v>
       </c>
       <c r="J262" t="n">
-        <v>24.4673</v>
+        <v>23.4262</v>
       </c>
     </row>
     <row r="263">
@@ -14755,10 +14755,10 @@
         <v>1.15</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3206</v>
+        <v>0.3286</v>
       </c>
       <c r="J263" t="n">
-        <v>9.2974</v>
+        <v>9.529400000000001</v>
       </c>
     </row>
     <row r="264">
@@ -14795,10 +14795,10 @@
         <v>1.04</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1006</v>
+        <v>0.1136</v>
       </c>
       <c r="J264" t="n">
-        <v>2.9174</v>
+        <v>3.2944</v>
       </c>
     </row>
     <row r="265">
@@ -14835,10 +14835,10 @@
         <v>0.98</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0463</v>
+        <v>-0.0506</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.3427</v>
+        <v>-1.4674</v>
       </c>
     </row>
     <row r="266">
@@ -14875,10 +14875,10 @@
         <v>0.9</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1458</v>
+        <v>-0.1559</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.2282</v>
+        <v>-4.5211</v>
       </c>
     </row>
     <row r="267">
@@ -14915,10 +14915,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6611</v>
+        <v>0.6249</v>
       </c>
       <c r="J267" t="n">
-        <v>19.1719</v>
+        <v>18.1221</v>
       </c>
     </row>
     <row r="268">
@@ -14955,10 +14955,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.584</v>
+        <v>0.5565</v>
       </c>
       <c r="J268" t="n">
-        <v>16.936</v>
+        <v>16.1385</v>
       </c>
     </row>
     <row r="269">
@@ -14995,10 +14995,10 @@
         <v>1.1</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3403</v>
+        <v>0.336</v>
       </c>
       <c r="J269" t="n">
-        <v>9.8687</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="270">
@@ -15035,10 +15035,10 @@
         <v>0.91</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3272</v>
+        <v>-0.3203</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.488799999999999</v>
+        <v>-9.2887</v>
       </c>
     </row>
     <row r="271">
@@ -15075,10 +15075,10 @@
         <v>0.71</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8566</v>
+        <v>-0.7929</v>
       </c>
       <c r="J271" t="n">
-        <v>-24.8414</v>
+        <v>-22.9941</v>
       </c>
     </row>
     <row r="272">
@@ -15115,10 +15115,10 @@
         <v>1.83</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4658</v>
+        <v>1.4623</v>
       </c>
       <c r="J272" t="n">
-        <v>32.2476</v>
+        <v>32.1706</v>
       </c>
     </row>
     <row r="273">
@@ -15155,10 +15155,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4546</v>
+        <v>1.4504</v>
       </c>
       <c r="J273" t="n">
-        <v>32.0012</v>
+        <v>31.9088</v>
       </c>
     </row>
     <row r="274">
@@ -15195,10 +15195,10 @@
         <v>1.47</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0553</v>
+        <v>1.0181</v>
       </c>
       <c r="J274" t="n">
-        <v>23.2166</v>
+        <v>22.3982</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>1.4</v>
       </c>
       <c r="I275" t="n">
-        <v>0.9458</v>
+        <v>0.901</v>
       </c>
       <c r="J275" t="n">
-        <v>20.8076</v>
+        <v>19.822</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>1.18</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4412</v>
+        <v>0.4525</v>
       </c>
       <c r="J276" t="n">
-        <v>9.7064</v>
+        <v>9.955</v>
       </c>
     </row>
     <row r="277">
@@ -15315,10 +15315,10 @@
         <v>0.82</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1396</v>
+        <v>-0.1707</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.0712</v>
+        <v>-3.7554</v>
       </c>
     </row>
     <row r="278">
@@ -15355,10 +15355,10 @@
         <v>0.74</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2298</v>
+        <v>-0.2575</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.0556</v>
+        <v>-5.665</v>
       </c>
     </row>
     <row r="279">
@@ -15395,10 +15395,10 @@
         <v>0.57</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3967</v>
+        <v>-0.4165</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.727399999999999</v>
+        <v>-9.163</v>
       </c>
     </row>
     <row r="280">
@@ -15435,10 +15435,10 @@
         <v>0.45</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5079</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.1738</v>
+        <v>-11.4554</v>
       </c>
     </row>
     <row r="281">
@@ -15475,10 +15475,10 @@
         <v>0.31</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6429</v>
+        <v>-0.6449</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.1438</v>
+        <v>-14.1878</v>
       </c>
     </row>
     <row r="282">
@@ -15515,10 +15515,10 @@
         <v>1.23</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5094</v>
+        <v>0.496</v>
       </c>
       <c r="J282" t="n">
-        <v>14.2632</v>
+        <v>13.888</v>
       </c>
     </row>
     <row r="283">
@@ -15555,10 +15555,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3587</v>
+        <v>0.3562</v>
       </c>
       <c r="J283" t="n">
-        <v>10.0436</v>
+        <v>9.973599999999999</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.6772</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>0.79</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2438</v>
+        <v>-0.2582</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.8264</v>
+        <v>-7.2296</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3782</v>
+        <v>-0.3891</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.5896</v>
+        <v>-10.8948</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>1.16</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4852</v>
+        <v>0.4722</v>
       </c>
       <c r="J287" t="n">
-        <v>13.5856</v>
+        <v>13.2216</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4063</v>
+        <v>0.4005</v>
       </c>
       <c r="J288" t="n">
-        <v>11.3764</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4063</v>
+        <v>0.4005</v>
       </c>
       <c r="J289" t="n">
-        <v>11.3764</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>1.06</v>
       </c>
       <c r="I290" t="n">
-        <v>0.211</v>
+        <v>0.2182</v>
       </c>
       <c r="J290" t="n">
-        <v>5.908</v>
+        <v>6.1096</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.95</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2204</v>
+        <v>-0.2163</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.1712</v>
+        <v>-6.0564</v>
       </c>
     </row>
     <row r="292">
@@ -15915,10 +15915,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9372</v>
+        <v>0.8903</v>
       </c>
       <c r="J292" t="n">
-        <v>26.2416</v>
+        <v>24.9284</v>
       </c>
     </row>
     <row r="293">
@@ -15955,10 +15955,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2522</v>
+        <v>0.2615</v>
       </c>
       <c r="J293" t="n">
-        <v>7.0616</v>
+        <v>7.322</v>
       </c>
     </row>
     <row r="294">
@@ -15995,10 +15995,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1926</v>
+        <v>0.2036</v>
       </c>
       <c r="J294" t="n">
-        <v>5.3928</v>
+        <v>5.7008</v>
       </c>
     </row>
     <row r="295">
@@ -16035,10 +16035,10 @@
         <v>0.82</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2263</v>
+        <v>-0.2382</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.3364</v>
+        <v>-6.6696</v>
       </c>
     </row>
     <row r="296">
@@ -16075,10 +16075,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2364</v>
+        <v>-0.2483</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.6192</v>
+        <v>-6.9524</v>
       </c>
     </row>
     <row r="297">
@@ -16115,10 +16115,10 @@
         <v>1.29</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7935</v>
+        <v>0.7487</v>
       </c>
       <c r="J297" t="n">
-        <v>22.218</v>
+        <v>20.9636</v>
       </c>
     </row>
     <row r="298">
@@ -16155,10 +16155,10 @@
         <v>1.26</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7219</v>
+        <v>0.6857</v>
       </c>
       <c r="J298" t="n">
-        <v>20.2132</v>
+        <v>19.1996</v>
       </c>
     </row>
     <row r="299">
@@ -16195,10 +16195,10 @@
         <v>1.17</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5004</v>
+        <v>0.4881</v>
       </c>
       <c r="J299" t="n">
-        <v>14.0112</v>
+        <v>13.6668</v>
       </c>
     </row>
     <row r="300">
@@ -16235,10 +16235,10 @@
         <v>1.02</v>
       </c>
       <c r="I300" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>1.8508</v>
+        <v>2.2596</v>
       </c>
     </row>
     <row r="301">
@@ -16275,10 +16275,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4131</v>
+        <v>-0.3931</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.5668</v>
+        <v>-11.0068</v>
       </c>
     </row>
     <row r="302">
@@ -16315,10 +16315,10 @@
         <v>1.48</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1248</v>
+        <v>1.0845</v>
       </c>
       <c r="J302" t="n">
-        <v>32.6192</v>
+        <v>31.4505</v>
       </c>
     </row>
     <row r="303">
@@ -16355,10 +16355,10 @@
         <v>1.14</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4184</v>
+        <v>0.4149</v>
       </c>
       <c r="J303" t="n">
-        <v>12.1336</v>
+        <v>12.0321</v>
       </c>
     </row>
     <row r="304">
@@ -16395,10 +16395,10 @@
         <v>1.08</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2534</v>
+        <v>0.2626</v>
       </c>
       <c r="J304" t="n">
-        <v>7.3486</v>
+        <v>7.6154</v>
       </c>
     </row>
     <row r="305">
@@ -16435,10 +16435,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2534</v>
+        <v>0.2626</v>
       </c>
       <c r="J305" t="n">
-        <v>7.3486</v>
+        <v>7.6154</v>
       </c>
     </row>
     <row r="306">
@@ -16475,10 +16475,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1282</v>
+        <v>0.144</v>
       </c>
       <c r="J306" t="n">
-        <v>3.7178</v>
+        <v>4.176</v>
       </c>
     </row>
     <row r="307">
@@ -16515,10 +16515,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0515</v>
+        <v>1.0048</v>
       </c>
       <c r="J307" t="n">
-        <v>30.4935</v>
+        <v>29.1392</v>
       </c>
     </row>
     <row r="308">
@@ -16555,10 +16555,10 @@
         <v>0.91</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1164</v>
+        <v>-0.1303</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.3756</v>
+        <v>-3.7787</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>0.88</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1489</v>
+        <v>-0.1637</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.3181</v>
+        <v>-4.7473</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>0.74</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2903</v>
+        <v>-0.3044</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.418699999999999</v>
+        <v>-8.8276</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.59</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4315</v>
+        <v>-0.4405</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.5135</v>
+        <v>-12.7745</v>
       </c>
     </row>
     <row r="312">
@@ -16715,10 +16715,10 @@
         <v>1.4</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0074</v>
+        <v>0.9507</v>
       </c>
       <c r="J312" t="n">
-        <v>28.2072</v>
+        <v>26.6196</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7028</v>
+        <v>0.6725</v>
       </c>
       <c r="J313" t="n">
-        <v>19.6784</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5137</v>
+        <v>0.5028</v>
       </c>
       <c r="J314" t="n">
-        <v>14.3836</v>
+        <v>14.0784</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>1.1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3044</v>
+        <v>0.3115</v>
       </c>
       <c r="J315" t="n">
-        <v>8.523199999999999</v>
+        <v>8.722</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>1.02</v>
       </c>
       <c r="I316" t="n">
-        <v>0.0494</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J316" t="n">
-        <v>1.3832</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="317">
@@ -16915,10 +16915,10 @@
         <v>1.17</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4023</v>
+        <v>0.396</v>
       </c>
       <c r="J317" t="n">
-        <v>11.2644</v>
+        <v>11.088</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.11</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2835</v>
+        <v>0.2841</v>
       </c>
       <c r="J318" t="n">
-        <v>7.938</v>
+        <v>7.9548</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.083</v>
+        <v>-0.0951</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.324</v>
+        <v>-2.6628</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>0.88</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1496</v>
+        <v>-0.1642</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.1888</v>
+        <v>-4.5976</v>
       </c>
     </row>
     <row r="321">
@@ -17075,10 +17075,10 @@
         <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4137</v>
+        <v>-0.4234</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.5836</v>
+        <v>-11.8552</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>3.01</v>
       </c>
       <c r="I322" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J322" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>1.61</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2018</v>
+        <v>1.184</v>
       </c>
       <c r="J323" t="n">
-        <v>20.4306</v>
+        <v>20.128</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>1.41</v>
       </c>
       <c r="I324" t="n">
-        <v>0.9346</v>
+        <v>0.8963</v>
       </c>
       <c r="J324" t="n">
-        <v>15.8882</v>
+        <v>15.2371</v>
       </c>
     </row>
     <row r="325">
@@ -17235,10 +17235,10 @@
         <v>1.31</v>
       </c>
       <c r="I325" t="n">
-        <v>0.7169</v>
+        <v>0.7042</v>
       </c>
       <c r="J325" t="n">
-        <v>12.1873</v>
+        <v>11.9714</v>
       </c>
     </row>
     <row r="326">
@@ -17275,10 +17275,10 @@
         <v>1.28</v>
       </c>
       <c r="I326" t="n">
-        <v>0.6483</v>
+        <v>0.6437</v>
       </c>
       <c r="J326" t="n">
-        <v>11.0211</v>
+        <v>10.9429</v>
       </c>
     </row>
     <row r="327">
@@ -17315,10 +17315,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.2368</v>
+        <v>-0.2718</v>
       </c>
       <c r="J327" t="n">
-        <v>-4.0256</v>
+        <v>-4.6206</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>0.67</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2599</v>
+        <v>-0.2934</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.4183</v>
+        <v>-4.9878</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>0.37</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.5609</v>
+        <v>-0.5729</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.535299999999999</v>
+        <v>-9.7393</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>0.35</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5809</v>
+        <v>-0.5911</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.875299999999999</v>
+        <v>-10.0487</v>
       </c>
     </row>
     <row r="331">
@@ -17475,10 +17475,10 @@
         <v>0.26</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6724</v>
+        <v>-0.6741</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.4308</v>
+        <v>-11.4597</v>
       </c>
     </row>
     <row r="332">
@@ -17515,10 +17515,10 @@
         <v>1.09</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2768</v>
+        <v>0.2699</v>
       </c>
       <c r="J332" t="n">
-        <v>6.0896</v>
+        <v>5.9378</v>
       </c>
     </row>
     <row r="333">
@@ -17555,10 +17555,10 @@
         <v>0.95</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.0592</v>
+        <v>-0.0733</v>
       </c>
       <c r="J333" t="n">
-        <v>-1.3024</v>
+        <v>-1.6126</v>
       </c>
     </row>
     <row r="334">
@@ -17595,10 +17595,10 @@
         <v>0.88</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1407</v>
+        <v>-0.1575</v>
       </c>
       <c r="J334" t="n">
-        <v>-3.0954</v>
+        <v>-3.465</v>
       </c>
     </row>
     <row r="335">
@@ -17635,10 +17635,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3268</v>
+        <v>-0.342</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.1896</v>
+        <v>-7.524</v>
       </c>
     </row>
     <row r="336">
@@ -17675,10 +17675,10 @@
         <v>0.63</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3834</v>
+        <v>-0.3964</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.434799999999999</v>
+        <v>-8.720800000000001</v>
       </c>
     </row>
     <row r="337">
@@ -17715,10 +17715,10 @@
         <v>1.65</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2936</v>
+        <v>1.2731</v>
       </c>
       <c r="J337" t="n">
-        <v>28.4592</v>
+        <v>28.0082</v>
       </c>
     </row>
     <row r="338">
@@ -17755,10 +17755,10 @@
         <v>1.52</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1363</v>
+        <v>1.1046</v>
       </c>
       <c r="J338" t="n">
-        <v>24.9986</v>
+        <v>24.3012</v>
       </c>
     </row>
     <row r="339">
@@ -17795,10 +17795,10 @@
         <v>1.33</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8316</v>
+        <v>0.7922</v>
       </c>
       <c r="J339" t="n">
-        <v>18.2952</v>
+        <v>17.4284</v>
       </c>
     </row>
     <row r="340">
@@ -17835,10 +17835,10 @@
         <v>1.18</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4813</v>
+        <v>0.4805</v>
       </c>
       <c r="J340" t="n">
-        <v>10.5886</v>
+        <v>10.571</v>
       </c>
     </row>
     <row r="341">
@@ -17875,10 +17875,10 @@
         <v>1.06</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1492</v>
+        <v>0.1753</v>
       </c>
       <c r="J341" t="n">
-        <v>3.2824</v>
+        <v>3.8566</v>
       </c>
     </row>
     <row r="342">
@@ -17915,10 +17915,10 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3969</v>
+        <v>0.3882</v>
       </c>
       <c r="J342" t="n">
-        <v>11.907</v>
+        <v>11.646</v>
       </c>
     </row>
     <row r="343">
@@ -17955,10 +17955,10 @@
         <v>0.93</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.0917</v>
+        <v>-0.1052</v>
       </c>
       <c r="J343" t="n">
-        <v>-2.751</v>
+        <v>-3.156</v>
       </c>
     </row>
     <row r="344">
@@ -17995,10 +17995,10 @@
         <v>0.84</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1873</v>
+        <v>-0.2033</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.619</v>
+        <v>-6.099</v>
       </c>
     </row>
     <row r="345">
@@ -18035,10 +18035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2176</v>
+        <v>-0.2336</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.528</v>
+        <v>-7.008</v>
       </c>
     </row>
     <row r="346">
@@ -18075,10 +18075,10 @@
         <v>0.79</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2376</v>
+        <v>-0.2534</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.128</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="347">
@@ -18115,10 +18115,10 @@
         <v>1.32</v>
       </c>
       <c r="I347" t="n">
-        <v>0.848</v>
+        <v>0.7992</v>
       </c>
       <c r="J347" t="n">
-        <v>25.44</v>
+        <v>23.976</v>
       </c>
     </row>
     <row r="348">
@@ -18155,10 +18155,10 @@
         <v>1.27</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7316</v>
+        <v>0.6969</v>
       </c>
       <c r="J348" t="n">
-        <v>21.948</v>
+        <v>20.907</v>
       </c>
     </row>
     <row r="349">
@@ -18195,10 +18195,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4169</v>
+        <v>0.4139</v>
       </c>
       <c r="J349" t="n">
-        <v>12.507</v>
+        <v>12.417</v>
       </c>
     </row>
     <row r="350">
@@ -18235,10 +18235,10 @@
         <v>1.07</v>
       </c>
       <c r="I350" t="n">
-        <v>0.2217</v>
+        <v>0.2334</v>
       </c>
       <c r="J350" t="n">
-        <v>6.651</v>
+        <v>7.002</v>
       </c>
     </row>
     <row r="351">
@@ -18275,10 +18275,10 @@
         <v>1.06</v>
       </c>
       <c r="I351" t="n">
-        <v>0.191</v>
+        <v>0.2044</v>
       </c>
       <c r="J351" t="n">
-        <v>5.73</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="352">
@@ -18315,10 +18315,10 @@
         <v>1.42</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0281</v>
+        <v>0.9764</v>
       </c>
       <c r="J352" t="n">
-        <v>27.7587</v>
+        <v>26.3628</v>
       </c>
     </row>
     <row r="353">
@@ -18355,10 +18355,10 @@
         <v>1.38</v>
       </c>
       <c r="I353" t="n">
-        <v>0.9595</v>
+        <v>0.9035</v>
       </c>
       <c r="J353" t="n">
-        <v>25.9065</v>
+        <v>24.3945</v>
       </c>
     </row>
     <row r="354">
@@ -18395,10 +18395,10 @@
         <v>1.29</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7617</v>
+        <v>0.7266</v>
       </c>
       <c r="J354" t="n">
-        <v>20.5659</v>
+        <v>19.6182</v>
       </c>
     </row>
     <row r="355">
@@ -18435,10 +18435,10 @@
         <v>1.08</v>
       </c>
       <c r="I355" t="n">
-        <v>0.2362</v>
+        <v>0.2507</v>
       </c>
       <c r="J355" t="n">
-        <v>6.3774</v>
+        <v>6.7689</v>
       </c>
     </row>
     <row r="356">
@@ -18475,10 +18475,10 @@
         <v>1.01</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.0026</v>
+        <v>0.02</v>
       </c>
       <c r="J356" t="n">
-        <v>-0.0702</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="357">
@@ -18515,10 +18515,10 @@
         <v>1.13</v>
       </c>
       <c r="I357" t="n">
-        <v>0.351</v>
+        <v>0.3424</v>
       </c>
       <c r="J357" t="n">
-        <v>9.477</v>
+        <v>9.2448</v>
       </c>
     </row>
     <row r="358">
@@ -18555,10 +18555,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1632</v>
+        <v>-0.18</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.4064</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="359">
@@ -18595,10 +18595,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1935</v>
+        <v>-0.2105</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.2245</v>
+        <v>-5.6835</v>
       </c>
     </row>
     <row r="360">
@@ -18635,10 +18635,10 @@
         <v>0.8</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2234</v>
+        <v>-0.2403</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.0318</v>
+        <v>-6.4881</v>
       </c>
     </row>
     <row r="361">
@@ -18675,10 +18675,10 @@
         <v>0.74</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2821</v>
+        <v>-0.298</v>
       </c>
       <c r="J361" t="n">
-        <v>-7.6167</v>
+        <v>-8.045999999999999</v>
       </c>
     </row>
     <row r="362">
@@ -18715,10 +18715,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.2963</v>
+        <v>1.271</v>
       </c>
       <c r="J362" t="n">
-        <v>33.7038</v>
+        <v>33.046</v>
       </c>
     </row>
     <row r="363">
@@ -18755,10 +18755,10 @@
         <v>1.27</v>
       </c>
       <c r="I363" t="n">
-        <v>0.7165</v>
+        <v>0.6866</v>
       </c>
       <c r="J363" t="n">
-        <v>18.629</v>
+        <v>17.8516</v>
       </c>
     </row>
     <row r="364">
@@ -18795,10 +18795,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J364" t="n">
-        <v>15.665</v>
+        <v>15.197</v>
       </c>
     </row>
     <row r="365">
@@ -18835,10 +18835,10 @@
         <v>1.2</v>
       </c>
       <c r="I365" t="n">
-        <v>0.555</v>
+        <v>0.5417</v>
       </c>
       <c r="J365" t="n">
-        <v>14.43</v>
+        <v>14.0842</v>
       </c>
     </row>
     <row r="366">
@@ -18875,10 +18875,10 @@
         <v>0.85</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5513</v>
+        <v>-0.513</v>
       </c>
       <c r="J366" t="n">
-        <v>-14.3338</v>
+        <v>-13.338</v>
       </c>
     </row>
     <row r="367">
@@ -18915,10 +18915,10 @@
         <v>1.08</v>
       </c>
       <c r="I367" t="n">
-        <v>0.2335</v>
+        <v>0.2332</v>
       </c>
       <c r="J367" t="n">
-        <v>6.071</v>
+        <v>6.0632</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>0.98</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0264</v>
+        <v>-0.0354</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.6864</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="369">
@@ -18995,10 +18995,10 @@
         <v>0.92</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1028</v>
+        <v>-0.1169</v>
       </c>
       <c r="J369" t="n">
-        <v>-2.6728</v>
+        <v>-3.0394</v>
       </c>
     </row>
     <row r="370">
@@ -19035,10 +19035,10 @@
         <v>0.86</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1662</v>
+        <v>-0.1822</v>
       </c>
       <c r="J370" t="n">
-        <v>-4.3212</v>
+        <v>-4.7372</v>
       </c>
     </row>
     <row r="371">
@@ -19075,10 +19075,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3529</v>
+        <v>-0.3659</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.1754</v>
+        <v>-9.513400000000001</v>
       </c>
     </row>
     <row r="372">
@@ -19115,10 +19115,10 @@
         <v>1.61</v>
       </c>
       <c r="I372" t="n">
-        <v>1.2569</v>
+        <v>1.2319</v>
       </c>
       <c r="J372" t="n">
-        <v>28.9087</v>
+        <v>28.3337</v>
       </c>
     </row>
     <row r="373">
@@ -19155,10 +19155,10 @@
         <v>1.44</v>
       </c>
       <c r="I373" t="n">
-        <v>1.0449</v>
+        <v>0.9987</v>
       </c>
       <c r="J373" t="n">
-        <v>24.0327</v>
+        <v>22.9701</v>
       </c>
     </row>
     <row r="374">
@@ -19195,10 +19195,10 @@
         <v>1.23</v>
       </c>
       <c r="I374" t="n">
-        <v>0.6152</v>
+        <v>0.5982</v>
       </c>
       <c r="J374" t="n">
-        <v>14.1496</v>
+        <v>13.7586</v>
       </c>
     </row>
     <row r="375">
@@ -19235,10 +19235,10 @@
         <v>1.1</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2804</v>
+        <v>0.2949</v>
       </c>
       <c r="J375" t="n">
-        <v>6.4492</v>
+        <v>6.7827</v>
       </c>
     </row>
     <row r="376">
@@ -19275,10 +19275,10 @@
         <v>1.09</v>
       </c>
       <c r="I376" t="n">
-        <v>0.2518</v>
+        <v>0.2684</v>
       </c>
       <c r="J376" t="n">
-        <v>5.7914</v>
+        <v>6.1732</v>
       </c>
     </row>
     <row r="377">
@@ -19315,10 +19315,10 @@
         <v>1.03</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1591</v>
+        <v>0.149</v>
       </c>
       <c r="J377" t="n">
-        <v>3.6593</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="378">
@@ -19355,10 +19355,10 @@
         <v>1.03</v>
       </c>
       <c r="I378" t="n">
-        <v>0.1591</v>
+        <v>0.149</v>
       </c>
       <c r="J378" t="n">
-        <v>3.6593</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="379">
@@ -19395,10 +19395,10 @@
         <v>0.89</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1212</v>
+        <v>-0.1397</v>
       </c>
       <c r="J379" t="n">
-        <v>-2.7876</v>
+        <v>-3.2131</v>
       </c>
     </row>
     <row r="380">
@@ -19435,10 +19435,10 @@
         <v>0.52</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4779</v>
+        <v>-0.4874</v>
       </c>
       <c r="J380" t="n">
-        <v>-10.9917</v>
+        <v>-11.2102</v>
       </c>
     </row>
     <row r="381">
@@ -19475,10 +19475,10 @@
         <v>0.49</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5056</v>
+        <v>-0.5134</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.6288</v>
+        <v>-11.8082</v>
       </c>
     </row>
     <row r="382">
@@ -19515,10 +19515,10 @@
         <v>1.99</v>
       </c>
       <c r="I382" t="n">
-        <v>1.6455</v>
+        <v>1.651</v>
       </c>
       <c r="J382" t="n">
-        <v>32.91</v>
+        <v>33.02</v>
       </c>
     </row>
     <row r="383">
@@ -19555,10 +19555,10 @@
         <v>1.67</v>
       </c>
       <c r="I383" t="n">
-        <v>1.2864</v>
+        <v>1.2712</v>
       </c>
       <c r="J383" t="n">
-        <v>25.728</v>
+        <v>25.424</v>
       </c>
     </row>
     <row r="384">
@@ -19595,10 +19595,10 @@
         <v>1.6</v>
       </c>
       <c r="I384" t="n">
-        <v>1.2062</v>
+        <v>1.1852</v>
       </c>
       <c r="J384" t="n">
-        <v>24.124</v>
+        <v>23.704</v>
       </c>
     </row>
     <row r="385">
@@ -19635,10 +19635,10 @@
         <v>1.51</v>
       </c>
       <c r="I385" t="n">
-        <v>1.1037</v>
+        <v>1.0737</v>
       </c>
       <c r="J385" t="n">
-        <v>22.074</v>
+        <v>21.474</v>
       </c>
     </row>
     <row r="386">
@@ -19675,10 +19675,10 @@
         <v>0.88</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.4804</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.574</v>
+        <v>-9.608000000000001</v>
       </c>
     </row>
     <row r="387">
@@ -19715,10 +19715,10 @@
         <v>0.68</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.2862</v>
+        <v>-0.3125</v>
       </c>
       <c r="J387" t="n">
-        <v>-5.724</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="388">
@@ -19755,10 +19755,10 @@
         <v>0.61</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3568</v>
+        <v>-0.3792</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.136</v>
+        <v>-7.584</v>
       </c>
     </row>
     <row r="389">
@@ -19795,10 +19795,10 @@
         <v>0.52</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.4378</v>
+        <v>-0.456</v>
       </c>
       <c r="J389" t="n">
-        <v>-8.756</v>
+        <v>-9.119999999999999</v>
       </c>
     </row>
     <row r="390">
@@ -19835,10 +19835,10 @@
         <v>0.5</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4562</v>
+        <v>-0.4733</v>
       </c>
       <c r="J390" t="n">
-        <v>-9.124000000000001</v>
+        <v>-9.465999999999999</v>
       </c>
     </row>
     <row r="391">
@@ -19875,10 +19875,10 @@
         <v>0.47</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4844</v>
+        <v>-0.4996</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.688000000000001</v>
+        <v>-9.992000000000001</v>
       </c>
     </row>
     <row r="392">
@@ -19915,10 +19915,10 @@
         <v>1.56</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1873</v>
+        <v>1.159</v>
       </c>
       <c r="J392" t="n">
-        <v>27.3079</v>
+        <v>26.657</v>
       </c>
     </row>
     <row r="393">
@@ -19955,10 +19955,10 @@
         <v>1.46</v>
       </c>
       <c r="I393" t="n">
-        <v>1.0641</v>
+        <v>1.0232</v>
       </c>
       <c r="J393" t="n">
-        <v>24.4743</v>
+        <v>23.5336</v>
       </c>
     </row>
     <row r="394">
@@ -19995,10 +19995,10 @@
         <v>1.31</v>
       </c>
       <c r="I394" t="n">
-        <v>0.79</v>
+        <v>0.755</v>
       </c>
       <c r="J394" t="n">
-        <v>18.17</v>
+        <v>17.365</v>
       </c>
     </row>
     <row r="395">
@@ -20035,10 +20035,10 @@
         <v>1.29</v>
       </c>
       <c r="I395" t="n">
-        <v>0.7456</v>
+        <v>0.7157</v>
       </c>
       <c r="J395" t="n">
-        <v>17.1488</v>
+        <v>16.4611</v>
       </c>
     </row>
     <row r="396">
@@ -20075,10 +20075,10 @@
         <v>1.06</v>
       </c>
       <c r="I396" t="n">
-        <v>0.1519</v>
+        <v>0.1772</v>
       </c>
       <c r="J396" t="n">
-        <v>3.4937</v>
+        <v>4.0756</v>
       </c>
     </row>
     <row r="397">
@@ -20115,10 +20115,10 @@
         <v>1.44</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9698</v>
+        <v>0.9008</v>
       </c>
       <c r="J397" t="n">
-        <v>22.3054</v>
+        <v>20.7184</v>
       </c>
     </row>
     <row r="398">
@@ -20155,10 +20155,10 @@
         <v>0.85</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.1669</v>
+        <v>-0.1853</v>
       </c>
       <c r="J398" t="n">
-        <v>-3.8387</v>
+        <v>-4.2619</v>
       </c>
     </row>
     <row r="399">
@@ -20195,10 +20195,10 @@
         <v>0.68</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.3304</v>
+        <v>-0.3466</v>
       </c>
       <c r="J399" t="n">
-        <v>-7.5992</v>
+        <v>-7.9718</v>
       </c>
     </row>
     <row r="400">
@@ -20235,10 +20235,10 @@
         <v>0.62</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.3869</v>
+        <v>-0.4008</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.8987</v>
+        <v>-9.218400000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20275,10 +20275,10 @@
         <v>0.44</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5532</v>
+        <v>-0.5577</v>
       </c>
       <c r="J401" t="n">
-        <v>-12.7236</v>
+        <v>-12.8271</v>
       </c>
     </row>
     <row r="402">
@@ -20315,10 +20315,10 @@
         <v>1.4</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7905</v>
+        <v>0.7532</v>
       </c>
       <c r="J402" t="n">
-        <v>22.9245</v>
+        <v>21.8428</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J403" t="n">
-        <v>5.9827</v>
+        <v>6.1886</v>
       </c>
     </row>
     <row r="404">
@@ -20395,10 +20395,10 @@
         <v>0.85</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.1873</v>
+        <v>-0.2009</v>
       </c>
       <c r="J404" t="n">
-        <v>-5.4317</v>
+        <v>-5.8261</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>0.83</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2079</v>
+        <v>-0.2217</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.0291</v>
+        <v>-6.4293</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2283</v>
+        <v>-0.2419</v>
       </c>
       <c r="J406" t="n">
-        <v>-6.6207</v>
+        <v>-7.0151</v>
       </c>
     </row>
     <row r="407">
@@ -20515,10 +20515,10 @@
         <v>1.34</v>
       </c>
       <c r="I407" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8661</v>
       </c>
       <c r="J407" t="n">
-        <v>26.9961</v>
+        <v>25.1169</v>
       </c>
     </row>
     <row r="408">
@@ -20555,10 +20555,10 @@
         <v>1.22</v>
       </c>
       <c r="I408" t="n">
-        <v>0.6412</v>
+        <v>0.6111</v>
       </c>
       <c r="J408" t="n">
-        <v>18.5948</v>
+        <v>17.7219</v>
       </c>
     </row>
     <row r="409">
@@ -20595,10 +20595,10 @@
         <v>1.09</v>
       </c>
       <c r="I409" t="n">
-        <v>0.2992</v>
+        <v>0.301</v>
       </c>
       <c r="J409" t="n">
-        <v>8.6768</v>
+        <v>8.728999999999999</v>
       </c>
     </row>
     <row r="410">
@@ -20635,10 +20635,10 @@
         <v>0.96</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1844</v>
+        <v>-0.1826</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.3476</v>
+        <v>-5.2954</v>
       </c>
     </row>
     <row r="411">
@@ -20675,10 +20675,10 @@
         <v>0.77</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6711</v>
       </c>
       <c r="J411" t="n">
-        <v>-20.8887</v>
+        <v>-19.4619</v>
       </c>
     </row>
     <row r="412">
@@ -20715,10 +20715,10 @@
         <v>1.41</v>
       </c>
       <c r="I412" t="n">
-        <v>1.0356</v>
+        <v>0.9802</v>
       </c>
       <c r="J412" t="n">
-        <v>28.9968</v>
+        <v>27.4456</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.18</v>
       </c>
       <c r="I413" t="n">
-        <v>0.5209</v>
+        <v>0.5077</v>
       </c>
       <c r="J413" t="n">
-        <v>14.5852</v>
+        <v>14.2156</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>1.17</v>
       </c>
       <c r="I414" t="n">
-        <v>0.4961</v>
+        <v>0.4852</v>
       </c>
       <c r="J414" t="n">
-        <v>13.8908</v>
+        <v>13.5856</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.09</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2865</v>
+        <v>0.2925</v>
       </c>
       <c r="J415" t="n">
-        <v>8.022</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>0.88</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4467</v>
+        <v>-0.4226</v>
       </c>
       <c r="J416" t="n">
-        <v>-12.5076</v>
+        <v>-11.8328</v>
       </c>
     </row>
     <row r="417">
@@ -20915,10 +20915,10 @@
         <v>1.3</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6088</v>
       </c>
       <c r="J417" t="n">
-        <v>17.7128</v>
+        <v>17.0464</v>
       </c>
     </row>
     <row r="418">
@@ -20955,10 +20955,10 @@
         <v>0.99</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.0178</v>
+        <v>-0.0232</v>
       </c>
       <c r="J418" t="n">
-        <v>-0.4984</v>
+        <v>-0.6496</v>
       </c>
     </row>
     <row r="419">
@@ -20995,10 +20995,10 @@
         <v>0.95</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0834</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.0272</v>
+        <v>-2.3352</v>
       </c>
     </row>
     <row r="420">
@@ -21035,10 +21035,10 @@
         <v>0.87</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1625</v>
+        <v>-0.1768</v>
       </c>
       <c r="J420" t="n">
-        <v>-4.55</v>
+        <v>-4.9504</v>
       </c>
     </row>
     <row r="421">
@@ -21075,10 +21075,10 @@
         <v>0.7</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3319</v>
+        <v>-0.3442</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.293200000000001</v>
+        <v>-9.637600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2062/event_2062_evp_summary.xlsx
+++ b/database/event/2062/event_2062_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7741</v>
+        <v>7.7477</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5934</v>
+        <v>5.5744</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9147</v>
+        <v>2.9237</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7741</v>
+        <v>7.7477</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3592</v>
+        <v>2.3617</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4149</v>
+        <v>5.386</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4387</v>
+        <v>2.4621</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4387</v>
+        <v>2.4621</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4149</v>
+        <v>5.386</v>
       </c>
       <c r="K2" t="n">
         <v>49</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8536</v>
+        <v>7.848100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>238</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4954</v>
+        <v>5.5109</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9539</v>
+        <v>3.965</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8774</v>
+        <v>1.9047</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4954</v>
+        <v>5.5109</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3205</v>
+        <v>2.3203</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1749</v>
+        <v>3.1906</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3539</v>
+        <v>2.3674</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3539</v>
+        <v>2.3674</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1749</v>
+        <v>3.1906</v>
       </c>
       <c r="K3" t="n">
         <v>49</v>
@@ -575,7 +575,7 @@
         <v>189</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5288</v>
+        <v>5.558</v>
       </c>
       <c r="N3" t="n">
         <v>238</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9174</v>
+        <v>4.8507</v>
       </c>
       <c r="C4" t="n">
-        <v>3.538</v>
+        <v>3.49</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6143</v>
+        <v>1.6039</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9174</v>
+        <v>4.8507</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4038</v>
+        <v>2.336</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5136</v>
+        <v>2.5147</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5363</v>
+        <v>2.4032</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6017</v>
+        <v>2.4674</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5136</v>
+        <v>2.5147</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1153</v>
+        <v>4.9821</v>
       </c>
       <c r="N4" t="n">
         <v>280</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6484</v>
+        <v>4.5115</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3445</v>
+        <v>3.246</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4918</v>
+        <v>1.4494</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6484</v>
+        <v>4.5115</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6276</v>
+        <v>1.5983</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0208</v>
+        <v>2.9132</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6276</v>
+        <v>1.5983</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6276</v>
+        <v>1.5983</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0208</v>
+        <v>2.9132</v>
       </c>
       <c r="K5" t="n">
         <v>49</v>
@@ -667,7 +667,7 @@
         <v>189</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6484</v>
+        <v>4.5115</v>
       </c>
       <c r="N5" t="n">
         <v>238</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3731</v>
+        <v>4.2407</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1464</v>
+        <v>3.0512</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3665</v>
+        <v>1.3261</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3731</v>
+        <v>4.2407</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7032</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6699</v>
+        <v>3.5991</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7032</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7032</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6699</v>
+        <v>3.5991</v>
       </c>
       <c r="K6" t="n">
         <v>49</v>
@@ -713,7 +713,7 @@
         <v>189</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3731</v>
+        <v>4.2407</v>
       </c>
       <c r="N6" t="n">
         <v>238</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2996</v>
+        <v>4.113</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0935</v>
+        <v>2.9593</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3331</v>
+        <v>1.2679</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2996</v>
+        <v>4.113</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9999</v>
+        <v>1.8725</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2998</v>
+        <v>2.2406</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9999</v>
+        <v>1.8725</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0514</v>
+        <v>1.9225</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2998</v>
+        <v>2.2406</v>
       </c>
       <c r="K7" t="n">
         <v>107</v>
@@ -759,7 +759,7 @@
         <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3512</v>
+        <v>4.1631</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1119</v>
+        <v>4.1046</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9585</v>
+        <v>2.9532</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2476</v>
+        <v>1.2641</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1119</v>
+        <v>4.1046</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4294</v>
+        <v>2.4224</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6825</v>
+        <v>1.6822</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5922</v>
+        <v>2.6012</v>
       </c>
       <c r="I8" t="n">
-        <v>2.659</v>
+        <v>2.6707</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6825</v>
+        <v>1.6822</v>
       </c>
       <c r="K8" t="n">
         <v>100</v>
@@ -805,7 +805,7 @@
         <v>180</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3415</v>
+        <v>4.3529</v>
       </c>
       <c r="N8" t="n">
         <v>280</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7947</v>
+        <v>3.6952</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7303</v>
+        <v>2.6587</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1032</v>
+        <v>1.0776</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7947</v>
+        <v>3.6952</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4831</v>
+        <v>2.4519</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3116</v>
+        <v>1.2432</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7099</v>
+        <v>2.669</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7797</v>
+        <v>2.7403</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3116</v>
+        <v>1.2432</v>
       </c>
       <c r="K9" t="n">
         <v>141</v>
@@ -851,7 +851,7 @@
         <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0913</v>
+        <v>3.9835</v>
       </c>
       <c r="N9" t="n">
         <v>211</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6765</v>
+        <v>3.6044</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6452</v>
+        <v>2.5933</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0494</v>
+        <v>1.0362</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6765</v>
+        <v>3.6044</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8881</v>
+        <v>1.8538</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7884</v>
+        <v>1.7506</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8881</v>
+        <v>1.8538</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9368</v>
+        <v>1.9033</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7884</v>
+        <v>1.7506</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7252</v>
+        <v>3.6539</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -906,127 +906,127 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0102</v>
+        <v>2.9285</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1658</v>
+        <v>2.107</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7461</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0102</v>
+        <v>2.9285</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3885</v>
+        <v>2.3977</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6217</v>
+        <v>0.5308</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3885</v>
+        <v>2.5446</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4243</v>
+        <v>2.6126</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6217</v>
+        <v>0.5308</v>
       </c>
       <c r="K11" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
-        <v>3.046</v>
+        <v>3.1434</v>
       </c>
       <c r="N11" t="n">
-        <v>205</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.981</v>
+        <v>2.8805</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1448</v>
+        <v>2.0725</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7328</v>
+        <v>0.7064</v>
       </c>
       <c r="E12" t="n">
-        <v>2.981</v>
+        <v>2.8805</v>
       </c>
       <c r="F12" t="n">
-        <v>2.432</v>
+        <v>0.4895</v>
       </c>
       <c r="G12" t="n">
-        <v>0.549</v>
+        <v>2.391</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5979</v>
+        <v>0.4895</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6648</v>
+        <v>0.5026</v>
       </c>
       <c r="J12" t="n">
-        <v>0.549</v>
+        <v>2.391</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L12" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2138</v>
+        <v>2.8936</v>
       </c>
       <c r="N12" t="n">
-        <v>280</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8234</v>
+        <v>2.8626</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0314</v>
+        <v>2.0596</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6611</v>
+        <v>0.6983</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8234</v>
+        <v>2.8626</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4793</v>
+        <v>1.3054</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3441</v>
+        <v>1.5571</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4793</v>
+        <v>1.3054</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4917</v>
+        <v>1.3403</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3441</v>
+        <v>1.5571</v>
       </c>
       <c r="K13" t="n">
         <v>107</v>
@@ -1035,7 +1035,7 @@
         <v>98</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8358</v>
+        <v>2.8974</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7741</v>
+        <v>2.7166</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9959</v>
+        <v>1.9546</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6318</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7741</v>
+        <v>2.7166</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8138</v>
+        <v>2.8055</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0397</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4336</v>
+        <v>3.4792</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5221</v>
+        <v>3.5722</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0397</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>127</v>
@@ -1081,7 +1081,7 @@
         <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4824</v>
+        <v>3.4833</v>
       </c>
       <c r="N14" t="n">
         <v>186</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4943</v>
+        <v>2.4511</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7946</v>
+        <v>1.7635</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5113</v>
+        <v>0.5108</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4943</v>
+        <v>2.4511</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0381</v>
+        <v>1.0401</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4562</v>
+        <v>1.411</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0381</v>
+        <v>1.0401</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0381</v>
+        <v>1.0401</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4562</v>
+        <v>1.411</v>
       </c>
       <c r="K15" t="n">
         <v>49</v>
@@ -1127,7 +1127,7 @@
         <v>189</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4943</v>
+        <v>2.4511</v>
       </c>
       <c r="N15" t="n">
         <v>238</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2298</v>
+        <v>2.2656</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6043</v>
+        <v>1.6301</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3908</v>
+        <v>0.4263</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2298</v>
+        <v>2.2656</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9307</v>
+        <v>2.0075</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2991</v>
+        <v>0.2581</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9307</v>
+        <v>2.0075</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9805</v>
+        <v>2.0611</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2991</v>
+        <v>0.2581</v>
       </c>
       <c r="K16" t="n">
         <v>141</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2796</v>
+        <v>2.3192</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1742</v>
+        <v>2.0827</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5643</v>
+        <v>1.4985</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3655</v>
+        <v>0.343</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1742</v>
+        <v>2.0827</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0197</v>
+        <v>2.0081</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1545</v>
+        <v>0.0746</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0197</v>
+        <v>2.0081</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0197</v>
+        <v>2.0081</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1545</v>
+        <v>0.0746</v>
       </c>
       <c r="K17" t="n">
         <v>54</v>
@@ -1219,7 +1219,7 @@
         <v>155</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1742</v>
+        <v>2.0827</v>
       </c>
       <c r="N17" t="n">
         <v>209</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1167</v>
+        <v>2.0485</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5229</v>
+        <v>1.4739</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3394</v>
+        <v>0.3274</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1167</v>
+        <v>2.0485</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1908</v>
+        <v>2.166</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0741</v>
+        <v>-0.1175</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1908</v>
+        <v>2.166</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2473</v>
+        <v>2.2239</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0741</v>
+        <v>-0.1175</v>
       </c>
       <c r="K18" t="n">
         <v>127</v>
@@ -1265,7 +1265,7 @@
         <v>59</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1732</v>
+        <v>2.1064</v>
       </c>
       <c r="N18" t="n">
         <v>186</v>
@@ -1274,277 +1274,277 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1075</v>
+        <v>1.9439</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5163</v>
+        <v>1.3986</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3352</v>
+        <v>0.2798</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1075</v>
+        <v>1.9439</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6481</v>
+        <v>1.9668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4594</v>
+        <v>-0.0229</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6481</v>
+        <v>1.9668</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6906</v>
+        <v>1.9668</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4594</v>
+        <v>-0.0229</v>
       </c>
       <c r="K19" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>2.15</v>
+        <v>1.9439</v>
       </c>
       <c r="N19" t="n">
-        <v>211</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9624</v>
+        <v>1.9167</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4119</v>
+        <v>1.3791</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2691</v>
+        <v>0.2674</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9624</v>
+        <v>1.9167</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2313</v>
+        <v>0.9397</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7311</v>
+        <v>0.977</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2313</v>
+        <v>0.9397</v>
       </c>
       <c r="I20" t="n">
-        <v>1.263</v>
+        <v>0.9648</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7311</v>
+        <v>0.977</v>
       </c>
       <c r="K20" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="L20" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9941</v>
+        <v>1.9418</v>
       </c>
       <c r="N20" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9538</v>
+        <v>1.8568</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4057</v>
+        <v>1.336</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2652</v>
+        <v>0.2401</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9538</v>
+        <v>1.8568</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9739</v>
+        <v>1.4866</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0201</v>
+        <v>0.3702</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9739</v>
+        <v>1.4866</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9739</v>
+        <v>1.5264</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0201</v>
+        <v>0.3702</v>
       </c>
       <c r="K21" t="n">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M21" t="n">
-        <v>1.9538</v>
+        <v>1.8966</v>
       </c>
       <c r="N21" t="n">
-        <v>128</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9352</v>
+        <v>1.8451</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3924</v>
+        <v>1.3275</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2567</v>
+        <v>0.2347</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9352</v>
+        <v>1.8451</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9216</v>
+        <v>1.1587</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0136</v>
+        <v>0.6863</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9216</v>
+        <v>1.1587</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9453</v>
+        <v>1.1897</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0136</v>
+        <v>0.6863</v>
       </c>
       <c r="K22" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="L22" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9589</v>
+        <v>1.876</v>
       </c>
       <c r="N22" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8988</v>
+        <v>1.8351</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3662</v>
+        <v>1.3203</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2402</v>
+        <v>0.2302</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8988</v>
+        <v>1.8351</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2702</v>
+        <v>2.2027</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6286</v>
+        <v>-0.3676</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2702</v>
+        <v>2.2027</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2702</v>
+        <v>2.2616</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6286</v>
+        <v>-0.3676</v>
       </c>
       <c r="K23" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8988</v>
+        <v>1.894</v>
       </c>
       <c r="N23" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8501</v>
+        <v>1.7475</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3311</v>
+        <v>1.2573</v>
       </c>
       <c r="D24" t="n">
-        <v>0.218</v>
+        <v>0.1903</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8501</v>
+        <v>1.7475</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2539</v>
+        <v>1.7475</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4038</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2539</v>
+        <v>1.7475</v>
       </c>
       <c r="I24" t="n">
-        <v>2.312</v>
+        <v>1.7475</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4038</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9082</v>
+        <v>1.7475</v>
       </c>
       <c r="N24" t="n">
-        <v>211</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3113</v>
+        <v>1.2543</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2054</v>
+        <v>0.1884</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8225</v>
+        <v>1.7433</v>
       </c>
       <c r="N25" t="n">
         <v>136</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7652</v>
+        <v>1.7243</v>
       </c>
       <c r="C26" t="n">
-        <v>1.27</v>
+        <v>1.2406</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1794</v>
+        <v>0.1797</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7652</v>
+        <v>1.7243</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7652</v>
+        <v>1.2053</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7652</v>
+        <v>1.2053</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7652</v>
+        <v>1.2053</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="K26" t="n">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7652</v>
+        <v>1.7243</v>
       </c>
       <c r="N26" t="n">
-        <v>136</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6618</v>
+        <v>1.6273</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1957</v>
+        <v>1.1708</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1323</v>
+        <v>0.1355</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6618</v>
+        <v>1.6273</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6618</v>
+        <v>1.641</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0137</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6618</v>
+        <v>1.641</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6618</v>
+        <v>1.641</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0137</v>
       </c>
       <c r="K27" t="n">
         <v>51</v>
@@ -1679,7 +1679,7 @@
         <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6618</v>
+        <v>1.6273</v>
       </c>
       <c r="N27" t="n">
         <v>128</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1562</v>
+        <v>1.0884</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1073</v>
+        <v>0.0834</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6069</v>
+        <v>1.5128</v>
       </c>
       <c r="N28" t="n">
         <v>136</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5247</v>
+        <v>1.3745</v>
       </c>
       <c r="C29" t="n">
-        <v>1.097</v>
+        <v>0.9889</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0699</v>
+        <v>0.0204</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5247</v>
+        <v>1.3745</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4887</v>
+        <v>0.4275</v>
       </c>
       <c r="G29" t="n">
-        <v>1.036</v>
+        <v>0.947</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4887</v>
+        <v>0.4275</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4887</v>
+        <v>0.4275</v>
       </c>
       <c r="J29" t="n">
-        <v>1.036</v>
+        <v>0.947</v>
       </c>
       <c r="K29" t="n">
         <v>51</v>
@@ -1771,7 +1771,7 @@
         <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5247</v>
+        <v>1.3745</v>
       </c>
       <c r="N29" t="n">
         <v>128</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3145</v>
+        <v>1.3263</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9458</v>
+        <v>0.9543</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0258</v>
+        <v>-0.0016</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3145</v>
+        <v>1.3263</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8842</v>
+        <v>1.8645</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5697</v>
+        <v>-0.5382</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8842</v>
+        <v>1.8645</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8842</v>
+        <v>1.8645</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5697</v>
+        <v>-0.5382</v>
       </c>
       <c r="K30" t="n">
         <v>51</v>
@@ -1817,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3145</v>
+        <v>1.3263</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.24</v>
+        <v>1.2601</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8922</v>
+        <v>0.9066</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0597</v>
+        <v>-0.0318</v>
       </c>
       <c r="E31" t="n">
-        <v>1.24</v>
+        <v>1.2601</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4275</v>
+        <v>1.2601</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4275</v>
+        <v>1.2601</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4275</v>
+        <v>1.2601</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.24</v>
+        <v>1.2601</v>
       </c>
       <c r="N31" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8858</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0638</v>
+        <v>-0.0687</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2311</v>
+        <v>1.179</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2173</v>
+        <v>1.1654</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8758</v>
+        <v>0.8385</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0701</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2173</v>
+        <v>1.1654</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2173</v>
+        <v>1.376</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.2106</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2173</v>
+        <v>1.376</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2173</v>
+        <v>1.376</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.2106</v>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2173</v>
+        <v>1.1654</v>
       </c>
       <c r="N33" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0932</v>
+        <v>1.0905</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7865</v>
+        <v>0.7846</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1266</v>
+        <v>-0.109</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0932</v>
+        <v>1.0905</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9707</v>
+        <v>1.9628</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.8723</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9707</v>
+        <v>1.9628</v>
       </c>
       <c r="I34" t="n">
-        <v>1.9707</v>
+        <v>1.9628</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.8723</v>
       </c>
       <c r="K34" t="n">
         <v>51</v>
@@ -2001,7 +2001,7 @@
         <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0932</v>
+        <v>1.0905</v>
       </c>
       <c r="N34" t="n">
         <v>91</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7692</v>
+        <v>0.7177</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1375</v>
+        <v>-0.1514</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0691</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>123</v>
@@ -2056,185 +2056,185 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.6906</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5567</v>
+        <v>0.4969</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.272</v>
+        <v>-0.2912</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.6906</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.0559</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.0559</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.6906000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7732</v>
+        <v>0.6847</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5563</v>
+        <v>0.4926</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2722</v>
+        <v>-0.2939</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7732</v>
+        <v>0.6847</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7847</v>
+        <v>0.6847</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7847</v>
+        <v>0.6847</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7847</v>
+        <v>0.6847</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0115</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7732</v>
+        <v>0.6847</v>
       </c>
       <c r="N37" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5401</v>
+        <v>0.4851</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2825</v>
+        <v>-0.2987</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7506</v>
+        <v>0.6742</v>
       </c>
       <c r="N38" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4981</v>
+        <v>0.4755</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3091</v>
+        <v>-0.3047</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6923</v>
+        <v>0.6609</v>
       </c>
       <c r="N39" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6167</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4841</v>
+        <v>0.4437</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3179</v>
+        <v>-0.3249</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6167</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1747</v>
+        <v>1.1076</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5018</v>
+        <v>-0.4909</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1747</v>
+        <v>1.1076</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1747</v>
+        <v>1.1076</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5018</v>
+        <v>-0.4909</v>
       </c>
       <c r="K40" t="n">
         <v>54</v>
@@ -2277,7 +2277,7 @@
         <v>155</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6166999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>209</v>
@@ -2286,139 +2286,139 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4828</v>
+        <v>0.4236</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3188</v>
+        <v>-0.3376</v>
       </c>
       <c r="E41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="F41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="I41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.671</v>
+        <v>0.5887</v>
       </c>
       <c r="N41" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4641</v>
+        <v>0.4069</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3306</v>
+        <v>-0.3481</v>
       </c>
       <c r="E42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="F42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="I42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.645</v>
+        <v>0.5656</v>
       </c>
       <c r="N42" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4264</v>
+        <v>0.3983</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3544</v>
+        <v>-0.3536</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5927</v>
+        <v>0.5536</v>
       </c>
       <c r="N43" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5463</v>
+        <v>0.4732</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3931</v>
+        <v>0.3405</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3755</v>
+        <v>-0.3902</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5463</v>
+        <v>0.4732</v>
       </c>
       <c r="F44" t="n">
-        <v>1.4591</v>
+        <v>1.3812</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.908</v>
       </c>
       <c r="H44" t="n">
-        <v>1.4591</v>
+        <v>1.3812</v>
       </c>
       <c r="I44" t="n">
-        <v>1.4967</v>
+        <v>1.4181</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.908</v>
       </c>
       <c r="K44" t="n">
         <v>127</v>
@@ -2461,7 +2461,7 @@
         <v>59</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5839</v>
+        <v>0.5100999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>186</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3668</v>
+        <v>0.3367</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3921</v>
+        <v>-0.3926</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5098</v>
+        <v>0.4679</v>
       </c>
       <c r="N45" t="n">
         <v>56</v>
@@ -2516,93 +2516,93 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2774</v>
+        <v>0.2794</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1996</v>
+        <v>0.201</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4979</v>
+        <v>-0.4785</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2774</v>
+        <v>0.2794</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6224</v>
+        <v>0.3182</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.345</v>
+        <v>-0.0388</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6224</v>
+        <v>0.3182</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6224</v>
+        <v>0.3267</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.345</v>
+        <v>-0.0388</v>
       </c>
       <c r="K46" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="L46" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2774</v>
+        <v>0.2879</v>
       </c>
       <c r="N46" t="n">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2296</v>
+        <v>0.2438</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1652</v>
+        <v>0.1754</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.4947</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2296</v>
+        <v>0.2438</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2959</v>
+        <v>0.5729</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0663</v>
+        <v>-0.3291</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2959</v>
+        <v>0.5729</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3035</v>
+        <v>0.5729</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.0663</v>
+        <v>-0.3291</v>
       </c>
       <c r="K47" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="L47" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2372</v>
+        <v>0.2438</v>
       </c>
       <c r="N47" t="n">
-        <v>280</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1385</v>
+        <v>0.1332</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5366</v>
+        <v>-0.5215</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1925</v>
+        <v>0.1851</v>
       </c>
       <c r="N48" t="n">
         <v>136</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5627</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="F49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="I49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.135</v>
+        <v>0.1182</v>
       </c>
       <c r="N49" t="n">
         <v>50</v>
@@ -2700,231 +2700,231 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0569</v>
+        <v>0.0446</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5775</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0791</v>
+        <v>0.062</v>
       </c>
       <c r="N50" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.079</v>
+        <v>0.0314</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0568</v>
+        <v>0.0226</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5915</v>
       </c>
       <c r="E51" t="n">
-        <v>0.079</v>
+        <v>0.0314</v>
       </c>
       <c r="F51" t="n">
-        <v>0.079</v>
+        <v>0.272</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.2406</v>
       </c>
       <c r="H51" t="n">
-        <v>0.079</v>
+        <v>0.272</v>
       </c>
       <c r="I51" t="n">
-        <v>0.079</v>
+        <v>0.2792</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.2406</v>
       </c>
       <c r="K51" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M51" t="n">
-        <v>0.079</v>
+        <v>0.0386</v>
       </c>
       <c r="N51" t="n">
-        <v>51</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>spaze</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.059</v>
+        <v>0.029</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0425</v>
+        <v>0.0209</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.5926</v>
       </c>
       <c r="E52" t="n">
-        <v>0.059</v>
+        <v>0.029</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4763</v>
+        <v>0.029</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4173</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4763</v>
+        <v>0.029</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4763</v>
+        <v>0.029</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.4173</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.059</v>
+        <v>0.029</v>
       </c>
       <c r="N52" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>spaze</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.025</v>
+        <v>0.0278</v>
       </c>
       <c r="C53" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.6128</v>
+        <v>-0.5931</v>
       </c>
       <c r="E53" t="n">
-        <v>0.025</v>
+        <v>0.0278</v>
       </c>
       <c r="F53" t="n">
-        <v>0.025</v>
+        <v>0.4107</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.3829</v>
       </c>
       <c r="H53" t="n">
-        <v>0.025</v>
+        <v>0.4107</v>
       </c>
       <c r="I53" t="n">
-        <v>0.025</v>
+        <v>0.4107</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.3829</v>
       </c>
       <c r="K53" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M53" t="n">
-        <v>0.025</v>
+        <v>0.02779999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0018</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0061</v>
+        <v>-0.0013</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6281</v>
+        <v>-0.6066</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0018</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2657</v>
+        <v>-0.0018</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.2742</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2657</v>
+        <v>-0.0018</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2725</v>
+        <v>-0.0018</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.2742</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="L54" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.001699999999999979</v>
+        <v>-0.0018</v>
       </c>
       <c r="N54" t="n">
-        <v>186</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.042</v>
+        <v>-0.0606</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6508</v>
+        <v>-0.6441</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0584</v>
+        <v>-0.0842</v>
       </c>
       <c r="N55" t="n">
         <v>46</v>
@@ -2976,32 +2976,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6695</v>
+        <v>-0.662</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0994</v>
+        <v>-0.1235</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0912</v>
+        <v>-0.0961</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6819</v>
+        <v>-0.6666</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1267</v>
+        <v>-0.1335</v>
       </c>
       <c r="N57" t="n">
         <v>56</v>
@@ -3068,139 +3068,139 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0944</v>
+        <v>-0.1143</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6839</v>
+        <v>-0.6781</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1312</v>
+        <v>-0.1588</v>
       </c>
       <c r="N58" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1378</v>
+        <v>-0.163</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1173</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6869</v>
+        <v>-0.68</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1378</v>
+        <v>-0.163</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1378</v>
+        <v>0.5043</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1378</v>
+        <v>0.5043</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1378</v>
+        <v>0.5178</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="K59" t="n">
         <v>100</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1378</v>
+        <v>-0.1495</v>
       </c>
       <c r="N59" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1997</v>
+        <v>-0.1848</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1437</v>
+        <v>-0.133</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7151</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1997</v>
+        <v>-0.1848</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5691000000000001</v>
+        <v>-0.1848</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.7688</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5691000000000001</v>
+        <v>-0.1848</v>
       </c>
       <c r="I60" t="n">
-        <v>0.5838</v>
+        <v>-0.1848</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.7688</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="L60" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1850000000000001</v>
+        <v>-0.1848</v>
       </c>
       <c r="N60" t="n">
-        <v>280</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1659</v>
+        <v>-0.144</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7292</v>
+        <v>-0.6969</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2306</v>
+        <v>-0.2001</v>
       </c>
       <c r="N61" t="n">
         <v>56</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2199</v>
+        <v>-0.2133</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7634</v>
+        <v>-0.7408</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3057</v>
+        <v>-0.2964</v>
       </c>
       <c r="N62" t="n">
         <v>100</v>
@@ -3298,369 +3298,369 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3345</v>
+        <v>-0.3032</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2407</v>
+        <v>-0.2182</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7765</v>
+        <v>-0.7439</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3345</v>
+        <v>-0.3032</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3345</v>
+        <v>-0.8254</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.5222</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3345</v>
+        <v>-0.8254</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3345</v>
+        <v>-0.8254</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.5222</v>
       </c>
       <c r="K63" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3345</v>
+        <v>-0.3032</v>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.241</v>
+        <v>-0.2353</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7548</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.335</v>
+        <v>-0.3271</v>
       </c>
       <c r="N64" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2636</v>
+        <v>-0.2577</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.791</v>
+        <v>-0.7689</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.3664</v>
+        <v>-0.3581</v>
       </c>
       <c r="N65" t="n">
-        <v>56</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.388</v>
+        <v>-0.374</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2792</v>
+        <v>-0.2691</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8008</v>
+        <v>-0.7762</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.388</v>
+        <v>-0.374</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9061</v>
+        <v>0.626</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5181</v>
+        <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9061</v>
+        <v>0.626</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9061</v>
+        <v>0.626</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5181</v>
+        <v>-1</v>
       </c>
       <c r="K66" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L66" t="n">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.388</v>
+        <v>-0.374</v>
       </c>
       <c r="N66" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3904</v>
+        <v>-0.3752</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2809</v>
+        <v>-0.27</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3904</v>
+        <v>-0.3752</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6096</v>
+        <v>-0.3752</v>
       </c>
       <c r="G67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6096</v>
+        <v>-0.3752</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6096</v>
+        <v>-0.3752</v>
       </c>
       <c r="J67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L67" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3904</v>
+        <v>-0.3752</v>
       </c>
       <c r="N67" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2941</v>
+        <v>-0.2978</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8103</v>
+        <v>-0.7943</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4087</v>
+        <v>-0.4139</v>
       </c>
       <c r="N68" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3666</v>
+        <v>-0.3449</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8561</v>
+        <v>-0.8242</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5095</v>
+        <v>-0.4794</v>
       </c>
       <c r="N69" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3706</v>
+        <v>-0.349</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8587</v>
+        <v>-0.8268</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5151</v>
+        <v>-0.4851</v>
       </c>
       <c r="N70" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71">
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3805</v>
+        <v>-0.361</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8649</v>
+        <v>-0.8344</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.5288</v>
+        <v>-0.5018</v>
       </c>
       <c r="N71" t="n">
         <v>51</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4772</v>
+        <v>-0.4623</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9262</v>
+        <v>-0.8985</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6633</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="N72" t="n">
         <v>49</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5552</v>
+        <v>-0.5416</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9755</v>
+        <v>-0.9487</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7716</v>
+        <v>-0.7527</v>
       </c>
       <c r="N73" t="n">
         <v>51</v>
@@ -3804,216 +3804,216 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5567</v>
+        <v>-0.5444</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9765</v>
+        <v>-0.9505</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7738</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5595</v>
+        <v>-0.547</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9782</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="N75" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.5475</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0034</v>
+        <v>-0.9524</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.833</v>
+        <v>-0.7609</v>
       </c>
       <c r="N76" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6005</v>
+        <v>-0.5914</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0041</v>
+        <v>-0.9802</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.8346</v>
+        <v>-0.8219</v>
       </c>
       <c r="N77" t="n">
-        <v>103</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6142</v>
+        <v>-0.6087</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0128</v>
+        <v>-0.9912</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.8536</v>
+        <v>-0.846</v>
       </c>
       <c r="N78" t="n">
         <v>103</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.645</v>
+        <v>-0.6373</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0323</v>
+        <v>-1.0093</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.8965</v>
+        <v>-0.8858</v>
       </c>
       <c r="N79" t="n">
         <v>49</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7299</v>
+        <v>-0.6601</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.086</v>
+        <v>-1.0237</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.0144</v>
+        <v>-0.9174</v>
       </c>
       <c r="N80" t="n">
         <v>123</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.1141</v>
+        <v>-1.1124</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.8016</v>
+        <v>-0.8004</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.1314</v>
+        <v>-1.1125</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.1141</v>
+        <v>-1.1124</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.1906</v>
+        <v>-0.187</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.9235</v>
+        <v>-0.9254</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.1906</v>
+        <v>-0.187</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1906</v>
+        <v>-0.187</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.9235</v>
+        <v>-0.9254</v>
       </c>
       <c r="K81" t="n">
         <v>51</v>
@@ -4163,7 +4163,7 @@
         <v>40</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.1141</v>
+        <v>-1.1124</v>
       </c>
       <c r="N81" t="n">
         <v>91</v>
@@ -4176,31 +4176,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.4931</v>
+        <v>-2.4039</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7938</v>
+        <v>-1.7296</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.7591</v>
+        <v>-1.7009</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.4931</v>
+        <v>-2.4039</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.6884</v>
+        <v>-1.6191</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.8047</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.6884</v>
+        <v>-1.6191</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.6884</v>
+        <v>-1.6191</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.8047</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="K82" t="n">
         <v>91</v>
@@ -4209,7 +4209,7 @@
         <v>70</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.4931</v>
+        <v>-2.4039</v>
       </c>
       <c r="N82" t="n">
         <v>161</v>
@@ -4315,10 +4315,10 @@
         <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4431</v>
+        <v>1.4788</v>
       </c>
       <c r="J2" t="n">
-        <v>33.1913</v>
+        <v>34.0124</v>
       </c>
     </row>
     <row r="3">
@@ -4355,10 +4355,10 @@
         <v>1.55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2142</v>
+        <v>1.2311</v>
       </c>
       <c r="J3" t="n">
-        <v>27.9266</v>
+        <v>28.3153</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>1.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4711</v>
+        <v>0.4388</v>
       </c>
       <c r="J4" t="n">
-        <v>10.8353</v>
+        <v>10.0924</v>
       </c>
     </row>
     <row r="5">
@@ -4435,10 +4435,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0939</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1597</v>
+        <v>1.6882</v>
       </c>
     </row>
     <row r="6">
@@ -4475,10 +4475,10 @@
         <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4678</v>
+        <v>-0.4291</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.7594</v>
+        <v>-9.869300000000001</v>
       </c>
     </row>
     <row r="7">
@@ -4515,10 +4515,10 @@
         <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.281</v>
+        <v>0.2364</v>
       </c>
       <c r="J7" t="n">
-        <v>6.463</v>
+        <v>5.4372</v>
       </c>
     </row>
     <row r="8">
@@ -4555,10 +4555,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1076</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.4748</v>
+        <v>-2.1459</v>
       </c>
     </row>
     <row r="9">
@@ -4595,10 +4595,10 @@
         <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2353</v>
+        <v>-0.2173</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.4119</v>
+        <v>-4.9979</v>
       </c>
     </row>
     <row r="10">
@@ -4635,10 +4635,10 @@
         <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3293</v>
+        <v>-0.3131</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.5739</v>
+        <v>-7.2013</v>
       </c>
     </row>
     <row r="11">
@@ -4675,10 +4675,10 @@
         <v>0.57</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4462</v>
+        <v>-0.4391</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.2626</v>
+        <v>-10.0993</v>
       </c>
     </row>
     <row r="12">
@@ -4715,10 +4715,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3377</v>
+        <v>1.3699</v>
       </c>
       <c r="J12" t="n">
-        <v>29.4294</v>
+        <v>30.1378</v>
       </c>
     </row>
     <row r="13">
@@ -4755,10 +4755,10 @@
         <v>1.31</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7556</v>
+        <v>0.7351</v>
       </c>
       <c r="J13" t="n">
-        <v>16.6232</v>
+        <v>16.1722</v>
       </c>
     </row>
     <row r="14">
@@ -4795,10 +4795,10 @@
         <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6763</v>
+        <v>0.6522</v>
       </c>
       <c r="J14" t="n">
-        <v>14.8786</v>
+        <v>14.3484</v>
       </c>
     </row>
     <row r="15">
@@ -4835,10 +4835,10 @@
         <v>1.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6352</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>13.9744</v>
+        <v>13.4068</v>
       </c>
     </row>
     <row r="16">
@@ -4875,10 +4875,10 @@
         <v>1.19</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5058</v>
+        <v>0.4759</v>
       </c>
       <c r="J16" t="n">
-        <v>11.1276</v>
+        <v>10.4698</v>
       </c>
     </row>
     <row r="17">
@@ -4915,10 +4915,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4018</v>
+        <v>0.3526</v>
       </c>
       <c r="J17" t="n">
-        <v>8.839600000000001</v>
+        <v>7.7572</v>
       </c>
     </row>
     <row r="18">
@@ -4955,10 +4955,10 @@
         <v>0.82</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2162</v>
+        <v>-0.1986</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.7564</v>
+        <v>-4.3692</v>
       </c>
     </row>
     <row r="19">
@@ -4995,10 +4995,10 @@
         <v>0.79</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2447</v>
+        <v>-0.2267</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.3834</v>
+        <v>-4.9874</v>
       </c>
     </row>
     <row r="20">
@@ -5035,10 +5035,10 @@
         <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3106</v>
+        <v>-0.2937</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.8332</v>
+        <v>-6.4614</v>
       </c>
     </row>
     <row r="21">
@@ -5075,10 +5075,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4284</v>
+        <v>-0.4194</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.424799999999999</v>
+        <v>-9.226800000000001</v>
       </c>
     </row>
     <row r="22">
@@ -5115,10 +5115,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4863</v>
+        <v>0.4618</v>
       </c>
       <c r="J22" t="n">
-        <v>14.1027</v>
+        <v>13.3922</v>
       </c>
     </row>
     <row r="23">
@@ -5155,10 +5155,10 @@
         <v>1.07</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2501</v>
+        <v>0.2144</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2529</v>
+        <v>6.2176</v>
       </c>
     </row>
     <row r="24">
@@ -5195,10 +5195,10 @@
         <v>1.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2218</v>
+        <v>0.1881</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4322</v>
+        <v>5.4549</v>
       </c>
     </row>
     <row r="25">
@@ -5235,10 +5235,10 @@
         <v>0.99</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0668</v>
+        <v>-0.0481</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.9372</v>
+        <v>-1.3949</v>
       </c>
     </row>
     <row r="26">
@@ -5275,10 +5275,10 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1444</v>
+        <v>-0.1143</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.1876</v>
+        <v>-3.3147</v>
       </c>
     </row>
     <row r="27">
@@ -5315,10 +5315,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4662</v>
+        <v>0.4174</v>
       </c>
       <c r="J27" t="n">
-        <v>13.5198</v>
+        <v>12.1046</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2273</v>
+        <v>0.1841</v>
       </c>
       <c r="J28" t="n">
-        <v>6.5917</v>
+        <v>5.3389</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0706</v>
+        <v>0.0513</v>
       </c>
       <c r="J29" t="n">
-        <v>2.0474</v>
+        <v>1.4877</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>0.98</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0451</v>
+        <v>-0.034</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.3079</v>
+        <v>-0.986</v>
       </c>
     </row>
     <row r="31">
@@ -5475,10 +5475,10 @@
         <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2045</v>
+        <v>-0.1838</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.9305</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="32">
@@ -5515,10 +5515,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9649</v>
+        <v>0.9523</v>
       </c>
       <c r="J32" t="n">
-        <v>27.9821</v>
+        <v>27.6167</v>
       </c>
     </row>
     <row r="33">
@@ -5555,10 +5555,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8937</v>
+        <v>0.879</v>
       </c>
       <c r="J33" t="n">
-        <v>25.9173</v>
+        <v>25.491</v>
       </c>
     </row>
     <row r="34">
@@ -5595,10 +5595,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3636</v>
+        <v>-0.3212</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.5444</v>
+        <v>-9.3148</v>
       </c>
     </row>
     <row r="35">
@@ -5635,10 +5635,10 @@
         <v>0.88</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4159</v>
+        <v>-0.3732</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.0611</v>
+        <v>-10.8228</v>
       </c>
     </row>
     <row r="36">
@@ -5675,10 +5675,10 @@
         <v>0.84</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5152</v>
+        <v>-0.4743</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.9408</v>
+        <v>-13.7547</v>
       </c>
     </row>
     <row r="37">
@@ -5715,10 +5715,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.424</v>
+        <v>0.3685</v>
       </c>
       <c r="J37" t="n">
-        <v>12.296</v>
+        <v>10.6865</v>
       </c>
     </row>
     <row r="38">
@@ -5755,10 +5755,10 @@
         <v>1.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1537</v>
+        <v>0.1182</v>
       </c>
       <c r="J38" t="n">
-        <v>4.4573</v>
+        <v>3.4278</v>
       </c>
     </row>
     <row r="39">
@@ -5795,10 +5795,10 @@
         <v>0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0563</v>
+        <v>-0.0447</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6327</v>
+        <v>-1.2963</v>
       </c>
     </row>
     <row r="40">
@@ -5835,10 +5835,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1982</v>
+        <v>-0.1778</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.7478</v>
+        <v>-5.1562</v>
       </c>
     </row>
     <row r="41">
@@ -5875,10 +5875,10 @@
         <v>0.76</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2881</v>
+        <v>-0.2694</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.354900000000001</v>
+        <v>-7.8126</v>
       </c>
     </row>
     <row r="42">
@@ -5915,10 +5915,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3784</v>
+        <v>0.3163</v>
       </c>
       <c r="J42" t="n">
-        <v>13.6224</v>
+        <v>11.3868</v>
       </c>
     </row>
     <row r="43">
@@ -5955,10 +5955,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2364</v>
+        <v>2.3328</v>
       </c>
     </row>
     <row r="44">
@@ -5995,10 +5995,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0721</v>
+        <v>0.0509</v>
       </c>
       <c r="J44" t="n">
-        <v>2.5956</v>
+        <v>1.8324</v>
       </c>
     </row>
     <row r="45">
@@ -6035,10 +6035,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0273</v>
+        <v>-0.0193</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9828</v>
+        <v>-0.6948</v>
       </c>
     </row>
     <row r="46">
@@ -6075,10 +6075,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2043</v>
+        <v>-0.1837</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.3548</v>
+        <v>-6.6132</v>
       </c>
     </row>
     <row r="47">
@@ -6115,10 +6115,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3543</v>
+        <v>0.3468</v>
       </c>
       <c r="J47" t="n">
-        <v>12.7548</v>
+        <v>12.4848</v>
       </c>
     </row>
     <row r="48">
@@ -6155,10 +6155,10 @@
         <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3284</v>
+        <v>0.3189</v>
       </c>
       <c r="J48" t="n">
-        <v>11.8224</v>
+        <v>11.4804</v>
       </c>
     </row>
     <row r="49">
@@ -6195,10 +6195,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1896</v>
+        <v>0.1744</v>
       </c>
       <c r="J49" t="n">
-        <v>6.8256</v>
+        <v>6.2784</v>
       </c>
     </row>
     <row r="50">
@@ -6235,10 +6235,10 @@
         <v>0.97</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0635</v>
+        <v>-0.0497</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.286</v>
+        <v>-1.7892</v>
       </c>
     </row>
     <row r="51">
@@ -6275,10 +6275,10 @@
         <v>0.86</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.197</v>
+        <v>-0.1764</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.092</v>
+        <v>-6.3504</v>
       </c>
     </row>
     <row r="52">
@@ -6315,10 +6315,10 @@
         <v>0.95</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0581</v>
+        <v>-0.0456</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.2201</v>
+        <v>-0.9576</v>
       </c>
     </row>
     <row r="53">
@@ -6355,10 +6355,10 @@
         <v>0.92</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0978</v>
+        <v>-0.0835</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.0538</v>
+        <v>-1.7535</v>
       </c>
     </row>
     <row r="54">
@@ -6395,10 +6395,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2498</v>
+        <v>-0.2338</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.2458</v>
+        <v>-4.9098</v>
       </c>
     </row>
     <row r="55">
@@ -6435,10 +6435,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.35</v>
+        <v>-0.3355</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.35</v>
+        <v>-7.0455</v>
       </c>
     </row>
     <row r="56">
@@ -6475,10 +6475,10 @@
         <v>0.46</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5354</v>
+        <v>-0.5389</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.2434</v>
+        <v>-11.3169</v>
       </c>
     </row>
     <row r="57">
@@ -6515,10 +6515,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8944</v>
+        <v>0.8811</v>
       </c>
       <c r="J57" t="n">
-        <v>18.7824</v>
+        <v>18.5031</v>
       </c>
     </row>
     <row r="58">
@@ -6555,10 +6555,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7155</v>
+        <v>0.705</v>
       </c>
       <c r="J58" t="n">
-        <v>15.0255</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="59">
@@ -6595,10 +6595,10 @@
         <v>1.31</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6736</v>
+        <v>0.6646</v>
       </c>
       <c r="J59" t="n">
-        <v>14.1456</v>
+        <v>13.9566</v>
       </c>
     </row>
     <row r="60">
@@ -6635,10 +6635,10 @@
         <v>1.3</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6593</v>
+        <v>0.6509</v>
       </c>
       <c r="J60" t="n">
-        <v>13.8453</v>
+        <v>13.6689</v>
       </c>
     </row>
     <row r="61">
@@ -6675,10 +6675,10 @@
         <v>1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4892</v>
+        <v>0.4766</v>
       </c>
       <c r="J61" t="n">
-        <v>10.2732</v>
+        <v>10.0086</v>
       </c>
     </row>
     <row r="62">
@@ -6715,10 +6715,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3801</v>
+        <v>0.3253</v>
       </c>
       <c r="J62" t="n">
-        <v>10.6428</v>
+        <v>9.1084</v>
       </c>
     </row>
     <row r="63">
@@ -6755,10 +6755,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0542</v>
+        <v>-0.0435</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.5176</v>
+        <v>-1.218</v>
       </c>
     </row>
     <row r="64">
@@ -6795,10 +6795,10 @@
         <v>0.89</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1526</v>
+        <v>-0.1336</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.2728</v>
+        <v>-3.7408</v>
       </c>
     </row>
     <row r="65">
@@ -6835,10 +6835,10 @@
         <v>0.83</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2161</v>
+        <v>-0.1959</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.0508</v>
+        <v>-5.4852</v>
       </c>
     </row>
     <row r="66">
@@ -6875,10 +6875,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2263</v>
+        <v>-0.2061</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.3364</v>
+        <v>-5.7708</v>
       </c>
     </row>
     <row r="67">
@@ -6915,10 +6915,10 @@
         <v>1.29</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6713</v>
+        <v>0.6565</v>
       </c>
       <c r="J67" t="n">
-        <v>18.7964</v>
+        <v>18.382</v>
       </c>
     </row>
     <row r="68">
@@ -6955,10 +6955,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5442</v>
+        <v>0.5337</v>
       </c>
       <c r="J68" t="n">
-        <v>15.2376</v>
+        <v>14.9436</v>
       </c>
     </row>
     <row r="69">
@@ -6995,10 +6995,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.46</v>
+        <v>0.4286</v>
       </c>
       <c r="J69" t="n">
-        <v>12.88</v>
+        <v>12.0008</v>
       </c>
     </row>
     <row r="70">
@@ -7035,10 +7035,10 @@
         <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.185</v>
+        <v>0.1566</v>
       </c>
       <c r="J70" t="n">
-        <v>5.18</v>
+        <v>4.3848</v>
       </c>
     </row>
     <row r="71">
@@ -7075,10 +7075,10 @@
         <v>0.83</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.4987</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.0864</v>
+        <v>-13.9636</v>
       </c>
     </row>
     <row r="72">
@@ -7115,10 +7115,10 @@
         <v>0.87</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1546</v>
+        <v>-0.1391</v>
       </c>
       <c r="J72" t="n">
-        <v>-3.2466</v>
+        <v>-2.9211</v>
       </c>
     </row>
     <row r="73">
@@ -7155,10 +7155,10 @@
         <v>0.75</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2765</v>
+        <v>-0.2609</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.8065</v>
+        <v>-5.4789</v>
       </c>
     </row>
     <row r="74">
@@ -7195,10 +7195,10 @@
         <v>0.75</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2765</v>
+        <v>-0.2609</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.8065</v>
+        <v>-5.4789</v>
       </c>
     </row>
     <row r="75">
@@ -7235,10 +7235,10 @@
         <v>0.74</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2853</v>
+        <v>-0.2698</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.9913</v>
+        <v>-5.6658</v>
       </c>
     </row>
     <row r="76">
@@ -7275,10 +7275,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4111</v>
+        <v>-0.4006</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.633100000000001</v>
+        <v>-8.412599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -7315,10 +7315,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2394</v>
+        <v>1.2378</v>
       </c>
       <c r="J77" t="n">
-        <v>26.0274</v>
+        <v>25.9938</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.46</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8774</v>
+        <v>0.8649</v>
       </c>
       <c r="J78" t="n">
-        <v>18.4254</v>
+        <v>18.1629</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>1.39</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7825</v>
+        <v>0.7711</v>
       </c>
       <c r="J79" t="n">
-        <v>16.4325</v>
+        <v>16.1931</v>
       </c>
     </row>
     <row r="80">
@@ -7435,10 +7435,10 @@
         <v>1.15</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4104</v>
+        <v>0.3793</v>
       </c>
       <c r="J80" t="n">
-        <v>8.618399999999999</v>
+        <v>7.9653</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0581</v>
+        <v>-0.0545</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.2201</v>
+        <v>-1.1445</v>
       </c>
     </row>
     <row r="82">
@@ -7515,10 +7515,10 @@
         <v>0.7</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2627</v>
+        <v>-0.2438</v>
       </c>
       <c r="J82" t="n">
-        <v>-4.9913</v>
+        <v>-4.6322</v>
       </c>
     </row>
     <row r="83">
@@ -7555,10 +7555,10 @@
         <v>0.68</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2844</v>
+        <v>-0.2684</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.4036</v>
+        <v>-5.0996</v>
       </c>
     </row>
     <row r="84">
@@ -7595,10 +7595,10 @@
         <v>0.35</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5919</v>
+        <v>-0.601</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.2461</v>
+        <v>-11.419</v>
       </c>
     </row>
     <row r="85">
@@ -7635,10 +7635,10 @@
         <v>0.34</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.601</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.419</v>
+        <v>-11.6166</v>
       </c>
     </row>
     <row r="86">
@@ -7675,10 +7675,10 @@
         <v>0.29</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.647</v>
+        <v>-0.6645</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.293</v>
+        <v>-12.6255</v>
       </c>
     </row>
     <row r="87">
@@ -7715,10 +7715,10 @@
         <v>2.14</v>
       </c>
       <c r="I87" t="n">
-        <v>1.6534</v>
+        <v>1.6847</v>
       </c>
       <c r="J87" t="n">
-        <v>31.4146</v>
+        <v>32.0093</v>
       </c>
     </row>
     <row r="88">
@@ -7755,10 +7755,10 @@
         <v>1.63</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0667</v>
+        <v>1.0648</v>
       </c>
       <c r="J88" t="n">
-        <v>20.2673</v>
+        <v>20.2312</v>
       </c>
     </row>
     <row r="89">
@@ -7795,10 +7795,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9433</v>
+        <v>0.9399</v>
       </c>
       <c r="J89" t="n">
-        <v>17.9227</v>
+        <v>17.8581</v>
       </c>
     </row>
     <row r="90">
@@ -7835,10 +7835,10 @@
         <v>1.46</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8522</v>
+        <v>0.8481</v>
       </c>
       <c r="J90" t="n">
-        <v>16.1918</v>
+        <v>16.1139</v>
       </c>
     </row>
     <row r="91">
@@ -7875,10 +7875,10 @@
         <v>1.45</v>
       </c>
       <c r="I91" t="n">
-        <v>0.8389</v>
+        <v>0.8348</v>
       </c>
       <c r="J91" t="n">
-        <v>15.9391</v>
+        <v>15.8612</v>
       </c>
     </row>
     <row r="92">
@@ -7915,10 +7915,10 @@
         <v>1.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6369</v>
+        <v>0.5971</v>
       </c>
       <c r="J92" t="n">
-        <v>17.1963</v>
+        <v>16.1217</v>
       </c>
     </row>
     <row r="93">
@@ -7955,10 +7955,10 @@
         <v>1.19</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2911</v>
+        <v>0.238</v>
       </c>
       <c r="J93" t="n">
-        <v>7.8597</v>
+        <v>6.426</v>
       </c>
     </row>
     <row r="94">
@@ -7995,10 +7995,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1891</v>
+        <v>0.1491</v>
       </c>
       <c r="J94" t="n">
-        <v>5.1057</v>
+        <v>4.0257</v>
       </c>
     </row>
     <row r="95">
@@ -8035,10 +8035,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0535</v>
+        <v>-0.0413</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.4445</v>
+        <v>-1.1151</v>
       </c>
     </row>
     <row r="96">
@@ -8075,10 +8075,10 @@
         <v>0.86</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2029</v>
+        <v>-0.1828</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.4783</v>
+        <v>-4.9356</v>
       </c>
     </row>
     <row r="97">
@@ -8115,10 +8115,10 @@
         <v>1.14</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2702</v>
+        <v>0.2566</v>
       </c>
       <c r="J97" t="n">
-        <v>7.2954</v>
+        <v>6.9282</v>
       </c>
     </row>
     <row r="98">
@@ -8155,10 +8155,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2097</v>
+        <v>0.1932</v>
       </c>
       <c r="J98" t="n">
-        <v>5.6619</v>
+        <v>5.2164</v>
       </c>
     </row>
     <row r="99">
@@ -8195,10 +8195,10 @@
         <v>1.08</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1776</v>
+        <v>0.1604</v>
       </c>
       <c r="J99" t="n">
-        <v>4.7952</v>
+        <v>4.3308</v>
       </c>
     </row>
     <row r="100">
@@ -8235,10 +8235,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2846</v>
+        <v>-0.2658</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.6842</v>
+        <v>-7.1766</v>
       </c>
     </row>
     <row r="101">
@@ -8275,10 +8275,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4659</v>
+        <v>-0.4622</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.5793</v>
+        <v>-12.4794</v>
       </c>
     </row>
     <row r="102">
@@ -8315,10 +8315,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.763</v>
+        <v>0.726</v>
       </c>
       <c r="J102" t="n">
-        <v>21.364</v>
+        <v>20.328</v>
       </c>
     </row>
     <row r="103">
@@ -8355,10 +8355,10 @@
         <v>1.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4548</v>
+        <v>0.404</v>
       </c>
       <c r="J103" t="n">
-        <v>12.7344</v>
+        <v>11.312</v>
       </c>
     </row>
     <row r="104">
@@ -8395,10 +8395,10 @@
         <v>1.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1364</v>
+        <v>0.1073</v>
       </c>
       <c r="J104" t="n">
-        <v>3.8192</v>
+        <v>3.0044</v>
       </c>
     </row>
     <row r="105">
@@ -8435,10 +8435,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0885</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>2.478</v>
+        <v>1.8788</v>
       </c>
     </row>
     <row r="106">
@@ -8475,10 +8475,10 @@
         <v>0.73</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.329</v>
+        <v>-0.3139</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.212</v>
+        <v>-8.789199999999999</v>
       </c>
     </row>
     <row r="107">
@@ -8515,10 +8515,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7015</v>
+        <v>0.6861</v>
       </c>
       <c r="J107" t="n">
-        <v>19.642</v>
+        <v>19.2108</v>
       </c>
     </row>
     <row r="108">
@@ -8555,10 +8555,10 @@
         <v>1.27</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6541</v>
+        <v>0.6395</v>
       </c>
       <c r="J108" t="n">
-        <v>18.3148</v>
+        <v>17.906</v>
       </c>
     </row>
     <row r="109">
@@ -8595,10 +8595,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1762</v>
+        <v>-0.143</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.9336</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="110">
@@ -8635,10 +8635,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3234</v>
+        <v>-0.2815</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.055199999999999</v>
+        <v>-7.882</v>
       </c>
     </row>
     <row r="111">
@@ -8675,10 +8675,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6644</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.6032</v>
+        <v>-17.626</v>
       </c>
     </row>
     <row r="112">
@@ -8715,10 +8715,10 @@
         <v>0.98</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0181</v>
+        <v>-0.0104</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.3982</v>
+        <v>-0.2288</v>
       </c>
     </row>
     <row r="113">
@@ -8755,10 +8755,10 @@
         <v>0.92</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.103</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.266</v>
+        <v>-1.9558</v>
       </c>
     </row>
     <row r="114">
@@ -8795,10 +8795,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2519</v>
+        <v>-0.2349</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.5418</v>
+        <v>-5.1678</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2891</v>
+        <v>-0.2721</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.3602</v>
+        <v>-5.9862</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4954</v>
+        <v>-0.4938</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.8988</v>
+        <v>-10.8636</v>
       </c>
     </row>
     <row r="117">
@@ -8915,10 +8915,10 @@
         <v>1.89</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4032</v>
+        <v>1.4128</v>
       </c>
       <c r="J117" t="n">
-        <v>30.8704</v>
+        <v>31.0816</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>1.47</v>
       </c>
       <c r="I118" t="n">
-        <v>0.881</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>19.382</v>
+        <v>19.173</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>1.41</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7943</v>
       </c>
       <c r="J119" t="n">
-        <v>17.6638</v>
+        <v>17.4746</v>
       </c>
     </row>
     <row r="120">
@@ -9035,10 +9035,10 @@
         <v>1.24</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5565</v>
+        <v>0.5548</v>
       </c>
       <c r="J120" t="n">
-        <v>12.243</v>
+        <v>12.2056</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4924</v>
+        <v>0.4822</v>
       </c>
       <c r="J121" t="n">
-        <v>10.8328</v>
+        <v>10.6084</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.95</v>
       </c>
       <c r="I122" t="n">
-        <v>1.4846</v>
+        <v>1.5017</v>
       </c>
       <c r="J122" t="n">
-        <v>34.1458</v>
+        <v>34.5391</v>
       </c>
     </row>
     <row r="123">
@@ -9155,10 +9155,10 @@
         <v>1.6</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0541</v>
+        <v>1.0448</v>
       </c>
       <c r="J123" t="n">
-        <v>24.2443</v>
+        <v>24.0304</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>1.37</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7521</v>
+        <v>0.7431</v>
       </c>
       <c r="J124" t="n">
-        <v>17.2983</v>
+        <v>17.0913</v>
       </c>
     </row>
     <row r="125">
@@ -9235,10 +9235,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.577</v>
+        <v>0.574</v>
       </c>
       <c r="J125" t="n">
-        <v>13.271</v>
+        <v>13.202</v>
       </c>
     </row>
     <row r="126">
@@ -9275,10 +9275,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6317</v>
+        <v>-0.604</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.5291</v>
+        <v>-13.892</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.25</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5854</v>
+        <v>0.5787</v>
       </c>
       <c r="J127" t="n">
-        <v>13.4642</v>
+        <v>13.3101</v>
       </c>
     </row>
     <row r="128">
@@ -9355,10 +9355,10 @@
         <v>0.86</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1614</v>
+        <v>-0.1458</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.7122</v>
+        <v>-3.3534</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>0.59</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.417</v>
+        <v>-0.4071</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.590999999999999</v>
+        <v>-9.363300000000001</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>0.5</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4963</v>
+        <v>-0.4942</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.4149</v>
+        <v>-11.3666</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.39</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5916</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.6068</v>
+        <v>-13.8759</v>
       </c>
     </row>
     <row r="132">
@@ -9515,10 +9515,10 @@
         <v>1.22</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5626</v>
+        <v>0.5517</v>
       </c>
       <c r="J132" t="n">
-        <v>20.2536</v>
+        <v>19.8612</v>
       </c>
     </row>
     <row r="133">
@@ -9555,10 +9555,10 @@
         <v>1.11</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3496</v>
+        <v>0.3115</v>
       </c>
       <c r="J133" t="n">
-        <v>12.5856</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="134">
@@ -9595,10 +9595,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2168</v>
+        <v>0.1854</v>
       </c>
       <c r="J134" t="n">
-        <v>7.8048</v>
+        <v>6.6744</v>
       </c>
     </row>
     <row r="135">
@@ -9635,10 +9635,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1869</v>
+        <v>0.158</v>
       </c>
       <c r="J135" t="n">
-        <v>6.7284</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="136">
@@ -9675,10 +9675,10 @@
         <v>1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1556</v>
+        <v>0.1294</v>
       </c>
       <c r="J136" t="n">
-        <v>5.6016</v>
+        <v>4.6584</v>
       </c>
     </row>
     <row r="137">
@@ -9715,10 +9715,10 @@
         <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4566</v>
+        <v>0.4053</v>
       </c>
       <c r="J137" t="n">
-        <v>16.4376</v>
+        <v>14.5908</v>
       </c>
     </row>
     <row r="138">
@@ -9755,10 +9755,10 @@
         <v>1.15</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3429</v>
+        <v>0.2896</v>
       </c>
       <c r="J138" t="n">
-        <v>12.3444</v>
+        <v>10.4256</v>
       </c>
     </row>
     <row r="139">
@@ -9795,10 +9795,10 @@
         <v>1.05</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1457</v>
+        <v>0.1124</v>
       </c>
       <c r="J139" t="n">
-        <v>5.2452</v>
+        <v>4.0464</v>
       </c>
     </row>
     <row r="140">
@@ -9835,10 +9835,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1128</v>
+        <v>-0.0948</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.0608</v>
+        <v>-3.4128</v>
       </c>
     </row>
     <row r="141">
@@ -9875,10 +9875,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3212</v>
+        <v>-0.3047</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.5632</v>
+        <v>-10.9692</v>
       </c>
     </row>
     <row r="142">
@@ -9915,10 +9915,10 @@
         <v>1.28</v>
       </c>
       <c r="I142" t="n">
-        <v>0.661</v>
+        <v>0.6463</v>
       </c>
       <c r="J142" t="n">
-        <v>23.796</v>
+        <v>23.2668</v>
       </c>
     </row>
     <row r="143">
@@ -9955,10 +9955,10 @@
         <v>1.15</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4449</v>
+        <v>0.4087</v>
       </c>
       <c r="J143" t="n">
-        <v>16.0164</v>
+        <v>14.7132</v>
       </c>
     </row>
     <row r="144">
@@ -9995,10 +9995,10 @@
         <v>1.08</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2742</v>
+        <v>0.2385</v>
       </c>
       <c r="J144" t="n">
-        <v>9.8712</v>
+        <v>8.586</v>
       </c>
     </row>
     <row r="145">
@@ -10035,10 +10035,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0883</v>
+        <v>0.0698</v>
       </c>
       <c r="J145" t="n">
-        <v>3.1788</v>
+        <v>2.5128</v>
       </c>
     </row>
     <row r="146">
@@ -10075,10 +10075,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4105</v>
+        <v>-0.3675</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.778</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="147">
@@ -10115,10 +10115,10 @@
         <v>1.31</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5672</v>
+        <v>0.5412</v>
       </c>
       <c r="J147" t="n">
-        <v>20.4192</v>
+        <v>19.4832</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>1.18</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3987</v>
+        <v>0.3426</v>
       </c>
       <c r="J148" t="n">
-        <v>14.3532</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>1.12</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2905</v>
+        <v>0.2407</v>
       </c>
       <c r="J149" t="n">
-        <v>10.458</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.76</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2916</v>
+        <v>-0.2733</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.4976</v>
+        <v>-9.838800000000001</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4021</v>
+        <v>-0.3921</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.4756</v>
+        <v>-14.1156</v>
       </c>
     </row>
     <row r="152">
@@ -10315,10 +10315,10 @@
         <v>1.12</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3849</v>
+        <v>0.3432</v>
       </c>
       <c r="J152" t="n">
-        <v>13.0866</v>
+        <v>11.6688</v>
       </c>
     </row>
     <row r="153">
@@ -10355,10 +10355,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.28</v>
+        <v>0.2418</v>
       </c>
       <c r="J153" t="n">
-        <v>9.52</v>
+        <v>8.2212</v>
       </c>
     </row>
     <row r="154">
@@ -10395,10 +10395,10 @@
         <v>1.02</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0951</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>3.2334</v>
+        <v>2.5296</v>
       </c>
     </row>
     <row r="155">
@@ -10435,10 +10435,10 @@
         <v>1.02</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0951</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>3.2334</v>
+        <v>2.5296</v>
       </c>
     </row>
     <row r="156">
@@ -10475,10 +10475,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2072</v>
+        <v>-0.1714</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.0448</v>
+        <v>-5.8276</v>
       </c>
     </row>
     <row r="157">
@@ -10515,10 +10515,10 @@
         <v>1.47</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7444</v>
+        <v>0.7107</v>
       </c>
       <c r="J157" t="n">
-        <v>25.3096</v>
+        <v>24.1638</v>
       </c>
     </row>
     <row r="158">
@@ -10555,10 +10555,10 @@
         <v>1.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1689</v>
+        <v>0.1321</v>
       </c>
       <c r="J158" t="n">
-        <v>5.7426</v>
+        <v>4.4914</v>
       </c>
     </row>
     <row r="159">
@@ -10595,10 +10595,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0827</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.3864</v>
+        <v>-2.8118</v>
       </c>
     </row>
     <row r="160">
@@ -10635,10 +10635,10 @@
         <v>0.93</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1122</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.8148</v>
+        <v>-3.2062</v>
       </c>
     </row>
     <row r="161">
@@ -10675,10 +10675,10 @@
         <v>0.64</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4026</v>
+        <v>-0.3927</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.6884</v>
+        <v>-13.3518</v>
       </c>
     </row>
     <row r="162">
@@ -10715,10 +10715,10 @@
         <v>1.19</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4244</v>
+        <v>0.3674</v>
       </c>
       <c r="J162" t="n">
-        <v>10.61</v>
+        <v>9.185</v>
       </c>
     </row>
     <row r="163">
@@ -10755,10 +10755,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1972</v>
+        <v>0.1561</v>
       </c>
       <c r="J163" t="n">
-        <v>4.93</v>
+        <v>3.9025</v>
       </c>
     </row>
     <row r="164">
@@ -10795,10 +10795,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0472</v>
+        <v>0.0315</v>
       </c>
       <c r="J164" t="n">
-        <v>1.18</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="165">
@@ -10835,10 +10835,10 @@
         <v>0.82</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2294</v>
+        <v>-0.2091</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.735</v>
+        <v>-5.2275</v>
       </c>
     </row>
     <row r="166">
@@ -10875,10 +10875,10 @@
         <v>0.75</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.298</v>
+        <v>-0.2799</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.45</v>
+        <v>-6.9975</v>
       </c>
     </row>
     <row r="167">
@@ -10915,10 +10915,10 @@
         <v>1.38</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9157</v>
+        <v>0.8998</v>
       </c>
       <c r="J167" t="n">
-        <v>22.8925</v>
+        <v>22.495</v>
       </c>
     </row>
     <row r="168">
@@ -10955,10 +10955,10 @@
         <v>1.2</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5118</v>
       </c>
       <c r="J168" t="n">
-        <v>13.6725</v>
+        <v>12.795</v>
       </c>
     </row>
     <row r="169">
@@ -10995,10 +10995,10 @@
         <v>1.18</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5037</v>
+        <v>0.4682</v>
       </c>
       <c r="J169" t="n">
-        <v>12.5925</v>
+        <v>11.705</v>
       </c>
     </row>
     <row r="170">
@@ -11035,10 +11035,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3131</v>
+        <v>0.2798</v>
       </c>
       <c r="J170" t="n">
-        <v>7.8275</v>
+        <v>6.995</v>
       </c>
     </row>
     <row r="171">
@@ -11075,10 +11075,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1726</v>
+        <v>0.1462</v>
       </c>
       <c r="J171" t="n">
-        <v>4.315</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="172">
@@ -11115,10 +11115,10 @@
         <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0298</v>
+        <v>0.0545</v>
       </c>
       <c r="J172" t="n">
-        <v>0.6854</v>
+        <v>1.2535</v>
       </c>
     </row>
     <row r="173">
@@ -11155,10 +11155,10 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3478</v>
+        <v>-0.3367</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.9994</v>
+        <v>-7.7441</v>
       </c>
     </row>
     <row r="174">
@@ -11195,10 +11195,10 @@
         <v>0.61</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3904</v>
+        <v>-0.3803</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.979200000000001</v>
+        <v>-8.7469</v>
       </c>
     </row>
     <row r="175">
@@ -11235,10 +11235,10 @@
         <v>0.55</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.1913</v>
+        <v>-10.0257</v>
       </c>
     </row>
     <row r="176">
@@ -11275,10 +11275,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5427</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.4154</v>
+        <v>-12.4821</v>
       </c>
     </row>
     <row r="177">
@@ -11315,10 +11315,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2522</v>
+        <v>1.2701</v>
       </c>
       <c r="J177" t="n">
-        <v>28.8006</v>
+        <v>29.2123</v>
       </c>
     </row>
     <row r="178">
@@ -11355,10 +11355,10 @@
         <v>1.44</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9842</v>
+        <v>0.9853</v>
       </c>
       <c r="J178" t="n">
-        <v>22.6366</v>
+        <v>22.6619</v>
       </c>
     </row>
     <row r="179">
@@ -11395,10 +11395,10 @@
         <v>1.41</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9341</v>
+        <v>0.9288</v>
       </c>
       <c r="J179" t="n">
-        <v>21.4843</v>
+        <v>21.3624</v>
       </c>
     </row>
     <row r="180">
@@ -11435,10 +11435,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6466</v>
+        <v>0.6234</v>
       </c>
       <c r="J180" t="n">
-        <v>14.8718</v>
+        <v>14.3382</v>
       </c>
     </row>
     <row r="181">
@@ -11475,10 +11475,10 @@
         <v>1.23</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5835</v>
+        <v>0.5574</v>
       </c>
       <c r="J181" t="n">
-        <v>13.4205</v>
+        <v>12.8202</v>
       </c>
     </row>
     <row r="182">
@@ -11515,10 +11515,10 @@
         <v>1.47</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0747</v>
+        <v>1.0837</v>
       </c>
       <c r="J182" t="n">
-        <v>29.0169</v>
+        <v>29.2599</v>
       </c>
     </row>
     <row r="183">
@@ -11555,10 +11555,10 @@
         <v>1.19</v>
       </c>
       <c r="I183" t="n">
-        <v>0.53</v>
+        <v>0.4928</v>
       </c>
       <c r="J183" t="n">
-        <v>14.31</v>
+        <v>13.3056</v>
       </c>
     </row>
     <row r="184">
@@ -11595,10 +11595,10 @@
         <v>1.18</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5077</v>
+        <v>0.4703</v>
       </c>
       <c r="J184" t="n">
-        <v>13.7079</v>
+        <v>12.6981</v>
       </c>
     </row>
     <row r="185">
@@ -11635,10 +11635,10 @@
         <v>1.05</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1787</v>
+        <v>0.1516</v>
       </c>
       <c r="J185" t="n">
-        <v>4.8249</v>
+        <v>4.0932</v>
       </c>
     </row>
     <row r="186">
@@ -11675,10 +11675,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5219</v>
+        <v>-0.4819</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.0913</v>
+        <v>-13.0113</v>
       </c>
     </row>
     <row r="187">
@@ -11715,10 +11715,10 @@
         <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6862</v>
+        <v>0.6309</v>
       </c>
       <c r="J187" t="n">
-        <v>18.5274</v>
+        <v>17.0343</v>
       </c>
     </row>
     <row r="188">
@@ -11755,10 +11755,10 @@
         <v>1.07</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1976</v>
+        <v>0.1564</v>
       </c>
       <c r="J188" t="n">
-        <v>5.3352</v>
+        <v>4.2228</v>
       </c>
     </row>
     <row r="189">
@@ -11795,10 +11795,10 @@
         <v>0.89</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1553</v>
+        <v>-0.1357</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.1931</v>
+        <v>-3.6639</v>
       </c>
     </row>
     <row r="190">
@@ -11835,10 +11835,10 @@
         <v>0.86</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1879</v>
+        <v>-0.1675</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.0733</v>
+        <v>-4.5225</v>
       </c>
     </row>
     <row r="191">
@@ -11875,10 +11875,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.381</v>
+        <v>-0.3687</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.287</v>
+        <v>-9.9549</v>
       </c>
     </row>
     <row r="192">
@@ -11915,10 +11915,10 @@
         <v>1.54</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1454</v>
+        <v>1.1584</v>
       </c>
       <c r="J192" t="n">
-        <v>25.1988</v>
+        <v>25.4848</v>
       </c>
     </row>
     <row r="193">
@@ -11955,10 +11955,10 @@
         <v>1.5</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0916</v>
+        <v>1.1025</v>
       </c>
       <c r="J193" t="n">
-        <v>24.0152</v>
+        <v>24.255</v>
       </c>
     </row>
     <row r="194">
@@ -11995,10 +11995,10 @@
         <v>1.4</v>
       </c>
       <c r="I194" t="n">
-        <v>0.9353</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>20.5766</v>
+        <v>20.3258</v>
       </c>
     </row>
     <row r="195">
@@ -12035,10 +12035,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.246</v>
+        <v>0.2158</v>
       </c>
       <c r="J195" t="n">
-        <v>5.412</v>
+        <v>4.7476</v>
       </c>
     </row>
     <row r="196">
@@ -12075,10 +12075,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6357</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-13.9854</v>
+        <v>-13.2946</v>
       </c>
     </row>
     <row r="197">
@@ -12115,10 +12115,10 @@
         <v>0.97</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0369</v>
+        <v>-0.0276</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.8118</v>
+        <v>-0.6072</v>
       </c>
     </row>
     <row r="198">
@@ -12155,10 +12155,10 @@
         <v>0.9</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1293</v>
+        <v>-0.1142</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.8446</v>
+        <v>-2.5124</v>
       </c>
     </row>
     <row r="199">
@@ -12195,10 +12195,10 @@
         <v>0.88</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1522</v>
+        <v>-0.1364</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.3484</v>
+        <v>-3.0008</v>
       </c>
     </row>
     <row r="200">
@@ -12235,10 +12235,10 @@
         <v>0.73</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2998</v>
+        <v>-0.2828</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.5956</v>
+        <v>-6.2216</v>
       </c>
     </row>
     <row r="201">
@@ -12275,10 +12275,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4882</v>
+        <v>-0.4859</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.7404</v>
+        <v>-10.6898</v>
       </c>
     </row>
     <row r="202">
@@ -12315,10 +12315,10 @@
         <v>1.19</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2965</v>
+        <v>0.2418</v>
       </c>
       <c r="J202" t="n">
-        <v>8.895</v>
+        <v>7.254</v>
       </c>
     </row>
     <row r="203">
@@ -12355,10 +12355,10 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2714</v>
+        <v>0.2194</v>
       </c>
       <c r="J203" t="n">
-        <v>8.141999999999999</v>
+        <v>6.582</v>
       </c>
     </row>
     <row r="204">
@@ -12395,10 +12395,10 @@
         <v>1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2326</v>
+        <v>0.1853</v>
       </c>
       <c r="J204" t="n">
-        <v>6.978</v>
+        <v>5.559</v>
       </c>
     </row>
     <row r="205">
@@ -12435,10 +12435,10 @@
         <v>0.99</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0316</v>
+        <v>-0.0227</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.948</v>
+        <v>-0.681</v>
       </c>
     </row>
     <row r="206">
@@ -12475,10 +12475,10 @@
         <v>0.96</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0796</v>
+        <v>-0.064</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.388</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="207">
@@ -12515,10 +12515,10 @@
         <v>1.15</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2695</v>
+        <v>0.2556</v>
       </c>
       <c r="J207" t="n">
-        <v>8.085000000000001</v>
+        <v>7.668</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.241</v>
+        <v>0.2257</v>
       </c>
       <c r="J208" t="n">
-        <v>7.23</v>
+        <v>6.771</v>
       </c>
     </row>
     <row r="209">
@@ -12595,10 +12595,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1964</v>
+        <v>0.1798</v>
       </c>
       <c r="J209" t="n">
-        <v>5.892</v>
+        <v>5.394</v>
       </c>
     </row>
     <row r="210">
@@ -12635,10 +12635,10 @@
         <v>1.02</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0567</v>
+        <v>0.0457</v>
       </c>
       <c r="J210" t="n">
-        <v>1.701</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.65</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3939</v>
+        <v>-0.3831</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.817</v>
+        <v>-11.493</v>
       </c>
     </row>
     <row r="212">
@@ -12715,10 +12715,10 @@
         <v>0.91</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0819</v>
+        <v>-0.062</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.4742</v>
+        <v>-1.116</v>
       </c>
     </row>
     <row r="213">
@@ -12755,10 +12755,10 @@
         <v>0.83</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1771</v>
+        <v>-0.1602</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.1878</v>
+        <v>-2.8836</v>
       </c>
     </row>
     <row r="214">
@@ -12795,10 +12795,10 @@
         <v>0.53</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4593</v>
+        <v>-0.4535</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.2674</v>
+        <v>-8.163</v>
       </c>
     </row>
     <row r="215">
@@ -12835,10 +12835,10 @@
         <v>0.46</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5208</v>
+        <v>-0.5213</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.3744</v>
+        <v>-9.3834</v>
       </c>
     </row>
     <row r="216">
@@ -12875,10 +12875,10 @@
         <v>0.46</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5208</v>
+        <v>-0.5213</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.3744</v>
+        <v>-9.3834</v>
       </c>
     </row>
     <row r="217">
@@ -12915,10 +12915,10 @@
         <v>2.21</v>
       </c>
       <c r="I217" t="n">
-        <v>1.909</v>
+        <v>1.9792</v>
       </c>
       <c r="J217" t="n">
-        <v>34.362</v>
+        <v>35.6256</v>
       </c>
     </row>
     <row r="218">
@@ -12955,10 +12955,10 @@
         <v>1.86</v>
       </c>
       <c r="I218" t="n">
-        <v>1.5049</v>
+        <v>1.5369</v>
       </c>
       <c r="J218" t="n">
-        <v>27.0882</v>
+        <v>27.6642</v>
       </c>
     </row>
     <row r="219">
@@ -12995,10 +12995,10 @@
         <v>1.35</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8123</v>
+        <v>0.8016</v>
       </c>
       <c r="J219" t="n">
-        <v>14.6214</v>
+        <v>14.4288</v>
       </c>
     </row>
     <row r="220">
@@ -13035,10 +13035,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1825</v>
+        <v>0.1502</v>
       </c>
       <c r="J220" t="n">
-        <v>3.285</v>
+        <v>2.7036</v>
       </c>
     </row>
     <row r="221">
@@ -13075,10 +13075,10 @@
         <v>0.99</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1393</v>
+        <v>-0.1246</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.5074</v>
+        <v>-2.2428</v>
       </c>
     </row>
     <row r="222">
@@ -13115,10 +13115,10 @@
         <v>1.05</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1667</v>
+        <v>0.1295</v>
       </c>
       <c r="J222" t="n">
-        <v>4.5009</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="223">
@@ -13155,10 +13155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0925</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.4975</v>
+        <v>-2.1114</v>
       </c>
     </row>
     <row r="224">
@@ -13195,10 +13195,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.161</v>
+        <v>-0.1424</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.347</v>
+        <v>-3.8448</v>
       </c>
     </row>
     <row r="225">
@@ -13235,10 +13235,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1822</v>
+        <v>-0.1629</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.9194</v>
+        <v>-4.3983</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2627</v>
+        <v>-0.2434</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.0929</v>
+        <v>-6.5718</v>
       </c>
     </row>
     <row r="227">
@@ -13315,10 +13315,10 @@
         <v>1.55</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1666</v>
+        <v>1.1802</v>
       </c>
       <c r="J227" t="n">
-        <v>31.4982</v>
+        <v>31.8654</v>
       </c>
     </row>
     <row r="228">
@@ -13355,10 +13355,10 @@
         <v>1.24</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6262</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>16.9074</v>
+        <v>16.0731</v>
       </c>
     </row>
     <row r="229">
@@ -13395,10 +13395,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6057</v>
+        <v>0.5742</v>
       </c>
       <c r="J229" t="n">
-        <v>16.3539</v>
+        <v>15.5034</v>
       </c>
     </row>
     <row r="230">
@@ -13435,10 +13435,10 @@
         <v>1.2</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5427</v>
+        <v>0.5099</v>
       </c>
       <c r="J230" t="n">
-        <v>14.6529</v>
+        <v>13.7673</v>
       </c>
     </row>
     <row r="231">
@@ -13475,10 +13475,10 @@
         <v>0.91</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3577</v>
+        <v>-0.3175</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.6579</v>
+        <v>-8.5725</v>
       </c>
     </row>
     <row r="232">
@@ -13515,10 +13515,10 @@
         <v>1.2</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3287</v>
+        <v>0.3191</v>
       </c>
       <c r="J232" t="n">
-        <v>11.5045</v>
+        <v>11.1685</v>
       </c>
     </row>
     <row r="233">
@@ -13555,10 +13555,10 @@
         <v>1.2</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3287</v>
+        <v>0.3191</v>
       </c>
       <c r="J233" t="n">
-        <v>11.5045</v>
+        <v>11.1685</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>1.1</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1898</v>
+        <v>0.1745</v>
       </c>
       <c r="J234" t="n">
-        <v>6.643</v>
+        <v>6.1075</v>
       </c>
     </row>
     <row r="235">
@@ -13635,10 +13635,10 @@
         <v>1.05</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1104</v>
+        <v>0.0969</v>
       </c>
       <c r="J235" t="n">
-        <v>3.864</v>
+        <v>3.3915</v>
       </c>
     </row>
     <row r="236">
@@ -13675,10 +13675,10 @@
         <v>0.79</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2683</v>
+        <v>-0.2493</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.390499999999999</v>
+        <v>-8.7255</v>
       </c>
     </row>
     <row r="237">
@@ -13715,10 +13715,10 @@
         <v>1.4</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5448</v>
+        <v>0.4756</v>
       </c>
       <c r="J237" t="n">
-        <v>19.068</v>
+        <v>16.646</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3253</v>
+        <v>0.2674</v>
       </c>
       <c r="J238" t="n">
-        <v>11.3855</v>
+        <v>9.359</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.04</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0883</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J239" t="n">
-        <v>3.0905</v>
+        <v>2.247</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2172</v>
+        <v>-0.1967</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.602</v>
+        <v>-6.8845</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2478</v>
+        <v>-0.228</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.673</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="242">
@@ -13915,10 +13915,10 @@
         <v>1.59</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2027</v>
+        <v>1.2179</v>
       </c>
       <c r="J242" t="n">
-        <v>31.2702</v>
+        <v>31.6654</v>
       </c>
     </row>
     <row r="243">
@@ -13955,10 +13955,10 @@
         <v>1.54</v>
       </c>
       <c r="I243" t="n">
-        <v>1.137</v>
+        <v>1.1503</v>
       </c>
       <c r="J243" t="n">
-        <v>29.562</v>
+        <v>29.9078</v>
       </c>
     </row>
     <row r="244">
@@ -13995,10 +13995,10 @@
         <v>1.45</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0119</v>
+        <v>1.0134</v>
       </c>
       <c r="J244" t="n">
-        <v>26.3094</v>
+        <v>26.3484</v>
       </c>
     </row>
     <row r="245">
@@ -14035,10 +14035,10 @@
         <v>1.15</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4168</v>
+        <v>0.3849</v>
       </c>
       <c r="J245" t="n">
-        <v>10.8368</v>
+        <v>10.0074</v>
       </c>
     </row>
     <row r="246">
@@ -14075,10 +14075,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5964</v>
+        <v>-0.5641</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.5064</v>
+        <v>-14.6666</v>
       </c>
     </row>
     <row r="247">
@@ -14115,10 +14115,10 @@
         <v>1.04</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1675</v>
+        <v>0.1338</v>
       </c>
       <c r="J247" t="n">
-        <v>4.355</v>
+        <v>3.4788</v>
       </c>
     </row>
     <row r="248">
@@ -14155,10 +14155,10 @@
         <v>0.85</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1861</v>
+        <v>-0.1691</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.8386</v>
+        <v>-4.3966</v>
       </c>
     </row>
     <row r="249">
@@ -14195,10 +14195,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2826</v>
+        <v>-0.2649</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.3476</v>
+        <v>-6.8874</v>
       </c>
     </row>
     <row r="250">
@@ -14235,10 +14235,10 @@
         <v>0.72</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3106</v>
+        <v>-0.2937</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.0756</v>
+        <v>-7.6362</v>
       </c>
     </row>
     <row r="251">
@@ -14275,10 +14275,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3199</v>
+        <v>-0.3033</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.317399999999999</v>
+        <v>-7.8858</v>
       </c>
     </row>
     <row r="252">
@@ -14315,10 +14315,10 @@
         <v>1.63</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2794</v>
+        <v>1.2986</v>
       </c>
       <c r="J252" t="n">
-        <v>38.382</v>
+        <v>38.958</v>
       </c>
     </row>
     <row r="253">
@@ -14355,10 +14355,10 @@
         <v>1.27</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6918</v>
+        <v>0.6616</v>
       </c>
       <c r="J253" t="n">
-        <v>20.754</v>
+        <v>19.848</v>
       </c>
     </row>
     <row r="254">
@@ -14395,10 +14395,10 @@
         <v>1.26</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6711</v>
+        <v>0.6402</v>
       </c>
       <c r="J254" t="n">
-        <v>20.133</v>
+        <v>19.206</v>
       </c>
     </row>
     <row r="255">
@@ -14435,10 +14435,10 @@
         <v>1.13</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J255" t="n">
-        <v>11.574</v>
+        <v>10.548</v>
       </c>
     </row>
     <row r="256">
@@ -14475,10 +14475,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8237</v>
+        <v>-0.8057</v>
       </c>
       <c r="J256" t="n">
-        <v>-24.711</v>
+        <v>-24.171</v>
       </c>
     </row>
     <row r="257">
@@ -14515,10 +14515,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4661</v>
+        <v>0.4087</v>
       </c>
       <c r="J257" t="n">
-        <v>13.983</v>
+        <v>12.261</v>
       </c>
     </row>
     <row r="258">
@@ -14555,10 +14555,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1579</v>
+        <v>0.1216</v>
       </c>
       <c r="J258" t="n">
-        <v>4.737</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="259">
@@ -14595,10 +14595,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1091</v>
+        <v>0.0804</v>
       </c>
       <c r="J259" t="n">
-        <v>3.273</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="260">
@@ -14635,10 +14635,10 @@
         <v>0.79</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2569</v>
+        <v>-0.2371</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.707</v>
+        <v>-7.113</v>
       </c>
     </row>
     <row r="261">
@@ -14675,10 +14675,10 @@
         <v>0.63</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4057</v>
+        <v>-0.3955</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.171</v>
+        <v>-11.865</v>
       </c>
     </row>
     <row r="262">
@@ -14715,10 +14715,10 @@
         <v>1.46</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8078</v>
+        <v>0.7531</v>
       </c>
       <c r="J262" t="n">
-        <v>23.4262</v>
+        <v>21.8399</v>
       </c>
     </row>
     <row r="263">
@@ -14755,10 +14755,10 @@
         <v>1.15</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3286</v>
+        <v>0.2783</v>
       </c>
       <c r="J263" t="n">
-        <v>9.529400000000001</v>
+        <v>8.0707</v>
       </c>
     </row>
     <row r="264">
@@ -14795,10 +14795,10 @@
         <v>1.04</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1136</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>3.2944</v>
+        <v>2.552</v>
       </c>
     </row>
     <row r="265">
@@ -14835,10 +14835,10 @@
         <v>0.98</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0506</v>
+        <v>-0.0386</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.4674</v>
+        <v>-1.1194</v>
       </c>
     </row>
     <row r="266">
@@ -14875,10 +14875,10 @@
         <v>0.9</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1559</v>
+        <v>-0.1359</v>
       </c>
       <c r="J266" t="n">
-        <v>-4.5211</v>
+        <v>-3.9411</v>
       </c>
     </row>
     <row r="267">
@@ -14915,10 +14915,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6249</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>18.1221</v>
+        <v>17.0288</v>
       </c>
     </row>
     <row r="268">
@@ -14955,10 +14955,10 @@
         <v>1.19</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5565</v>
+        <v>0.516</v>
       </c>
       <c r="J268" t="n">
-        <v>16.1385</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="269">
@@ -14995,10 +14995,10 @@
         <v>1.1</v>
       </c>
       <c r="I269" t="n">
-        <v>0.336</v>
+        <v>0.295</v>
       </c>
       <c r="J269" t="n">
-        <v>9.744</v>
+        <v>8.555</v>
       </c>
     </row>
     <row r="270">
@@ -15035,10 +15035,10 @@
         <v>0.91</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3203</v>
+        <v>-0.2786</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.2887</v>
+        <v>-8.0794</v>
       </c>
     </row>
     <row r="271">
@@ -15075,10 +15075,10 @@
         <v>0.71</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7929</v>
+        <v>-0.7674</v>
       </c>
       <c r="J271" t="n">
-        <v>-22.9941</v>
+        <v>-22.2546</v>
       </c>
     </row>
     <row r="272">
@@ -15115,10 +15115,10 @@
         <v>1.83</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4623</v>
+        <v>1.4921</v>
       </c>
       <c r="J272" t="n">
-        <v>32.1706</v>
+        <v>32.8262</v>
       </c>
     </row>
     <row r="273">
@@ -15155,10 +15155,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4504</v>
+        <v>1.4796</v>
       </c>
       <c r="J273" t="n">
-        <v>31.9088</v>
+        <v>32.5512</v>
       </c>
     </row>
     <row r="274">
@@ -15195,10 +15195,10 @@
         <v>1.47</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0181</v>
+        <v>1.03</v>
       </c>
       <c r="J274" t="n">
-        <v>22.3982</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>1.4</v>
       </c>
       <c r="I275" t="n">
-        <v>0.901</v>
+        <v>0.8985</v>
       </c>
       <c r="J275" t="n">
-        <v>19.822</v>
+        <v>19.767</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>1.18</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4525</v>
+        <v>0.4214</v>
       </c>
       <c r="J276" t="n">
-        <v>9.955</v>
+        <v>9.270799999999999</v>
       </c>
     </row>
     <row r="277">
@@ -15315,10 +15315,10 @@
         <v>0.82</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1707</v>
+        <v>-0.1504</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.7554</v>
+        <v>-3.3088</v>
       </c>
     </row>
     <row r="278">
@@ -15355,10 +15355,10 @@
         <v>0.74</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2575</v>
+        <v>-0.2435</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.665</v>
+        <v>-5.357</v>
       </c>
     </row>
     <row r="279">
@@ -15395,10 +15395,10 @@
         <v>0.57</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4165</v>
+        <v>-0.4101</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.163</v>
+        <v>-9.0222</v>
       </c>
     </row>
     <row r="280">
@@ -15435,10 +15435,10 @@
         <v>0.45</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5212</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.4554</v>
+        <v>-11.4664</v>
       </c>
     </row>
     <row r="281">
@@ -15475,10 +15475,10 @@
         <v>0.31</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6449</v>
+        <v>-0.6637</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.1878</v>
+        <v>-14.6014</v>
       </c>
     </row>
     <row r="282">
@@ -15515,10 +15515,10 @@
         <v>1.23</v>
       </c>
       <c r="I282" t="n">
-        <v>0.496</v>
+        <v>0.4379</v>
       </c>
       <c r="J282" t="n">
-        <v>13.888</v>
+        <v>12.2612</v>
       </c>
     </row>
     <row r="283">
@@ -15555,10 +15555,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3562</v>
+        <v>0.3021</v>
       </c>
       <c r="J283" t="n">
-        <v>9.973599999999999</v>
+        <v>8.4588</v>
       </c>
     </row>
     <row r="284">
@@ -15595,10 +15595,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.96</v>
+        <v>-1.5904</v>
       </c>
     </row>
     <row r="285">
@@ -15635,10 +15635,10 @@
         <v>0.79</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2582</v>
+        <v>-0.2385</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.2296</v>
+        <v>-6.678</v>
       </c>
     </row>
     <row r="286">
@@ -15675,10 +15675,10 @@
         <v>0.65</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3891</v>
+        <v>-0.3774</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.8948</v>
+        <v>-10.5672</v>
       </c>
     </row>
     <row r="287">
@@ -15715,10 +15715,10 @@
         <v>1.16</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4722</v>
+        <v>0.4317</v>
       </c>
       <c r="J287" t="n">
-        <v>13.2216</v>
+        <v>12.0876</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.13</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4005</v>
+        <v>0.3605</v>
       </c>
       <c r="J288" t="n">
-        <v>11.214</v>
+        <v>10.094</v>
       </c>
     </row>
     <row r="289">
@@ -15795,10 +15795,10 @@
         <v>1.13</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4005</v>
+        <v>0.3605</v>
       </c>
       <c r="J289" t="n">
-        <v>11.214</v>
+        <v>10.094</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>1.06</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2182</v>
+        <v>0.1864</v>
       </c>
       <c r="J290" t="n">
-        <v>6.1096</v>
+        <v>5.2192</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.95</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2163</v>
+        <v>-0.1795</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.0564</v>
+        <v>-5.026</v>
       </c>
     </row>
     <row r="292">
@@ -15915,10 +15915,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8903</v>
+        <v>0.8416</v>
       </c>
       <c r="J292" t="n">
-        <v>24.9284</v>
+        <v>23.5648</v>
       </c>
     </row>
     <row r="293">
@@ -15955,10 +15955,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2615</v>
+        <v>0.2157</v>
       </c>
       <c r="J293" t="n">
-        <v>7.322</v>
+        <v>6.0396</v>
       </c>
     </row>
     <row r="294">
@@ -15995,10 +15995,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2036</v>
+        <v>0.1641</v>
       </c>
       <c r="J294" t="n">
-        <v>5.7008</v>
+        <v>4.5948</v>
       </c>
     </row>
     <row r="295">
@@ -16035,10 +16035,10 @@
         <v>0.82</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2382</v>
+        <v>-0.2182</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.6696</v>
+        <v>-6.1096</v>
       </c>
     </row>
     <row r="296">
@@ -16075,10 +16075,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2483</v>
+        <v>-0.2285</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.9524</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="297">
@@ -16115,10 +16115,10 @@
         <v>1.29</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7487</v>
+        <v>0.7189</v>
       </c>
       <c r="J297" t="n">
-        <v>20.9636</v>
+        <v>20.1292</v>
       </c>
     </row>
     <row r="298">
@@ -16155,10 +16155,10 @@
         <v>1.26</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6857</v>
+        <v>0.6525</v>
       </c>
       <c r="J298" t="n">
-        <v>19.1996</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="299">
@@ -16195,10 +16195,10 @@
         <v>1.17</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4881</v>
+        <v>0.4496</v>
       </c>
       <c r="J299" t="n">
-        <v>13.6668</v>
+        <v>12.5888</v>
       </c>
     </row>
     <row r="300">
@@ -16235,10 +16235,10 @@
         <v>1.02</v>
       </c>
       <c r="I300" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0636</v>
       </c>
       <c r="J300" t="n">
-        <v>2.2596</v>
+        <v>1.7808</v>
       </c>
     </row>
     <row r="301">
@@ -16275,10 +16275,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3931</v>
+        <v>-0.3506</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.0068</v>
+        <v>-9.816800000000001</v>
       </c>
     </row>
     <row r="302">
@@ -16315,10 +16315,10 @@
         <v>1.48</v>
       </c>
       <c r="I302" t="n">
-        <v>1.0845</v>
+        <v>1.0945</v>
       </c>
       <c r="J302" t="n">
-        <v>31.4505</v>
+        <v>31.7405</v>
       </c>
     </row>
     <row r="303">
@@ -16355,10 +16355,10 @@
         <v>1.14</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4149</v>
+        <v>0.3788</v>
       </c>
       <c r="J303" t="n">
-        <v>12.0321</v>
+        <v>10.9852</v>
       </c>
     </row>
     <row r="304">
@@ -16395,10 +16395,10 @@
         <v>1.08</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2626</v>
+        <v>0.2307</v>
       </c>
       <c r="J304" t="n">
-        <v>7.6154</v>
+        <v>6.6903</v>
       </c>
     </row>
     <row r="305">
@@ -16435,10 +16435,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2626</v>
+        <v>0.2307</v>
       </c>
       <c r="J305" t="n">
-        <v>7.6154</v>
+        <v>6.6903</v>
       </c>
     </row>
     <row r="306">
@@ -16475,10 +16475,10 @@
         <v>1.04</v>
       </c>
       <c r="I306" t="n">
-        <v>0.144</v>
+        <v>0.1199</v>
       </c>
       <c r="J306" t="n">
-        <v>4.176</v>
+        <v>3.4771</v>
       </c>
     </row>
     <row r="307">
@@ -16515,10 +16515,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0048</v>
+        <v>0.9831</v>
       </c>
       <c r="J307" t="n">
-        <v>29.1392</v>
+        <v>28.5099</v>
       </c>
     </row>
     <row r="308">
@@ -16555,10 +16555,10 @@
         <v>0.91</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.1303</v>
+        <v>-0.1124</v>
       </c>
       <c r="J308" t="n">
-        <v>-3.7787</v>
+        <v>-3.2596</v>
       </c>
     </row>
     <row r="309">
@@ -16595,10 +16595,10 @@
         <v>0.88</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1637</v>
+        <v>-0.1443</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.7473</v>
+        <v>-4.1847</v>
       </c>
     </row>
     <row r="310">
@@ -16635,10 +16635,10 @@
         <v>0.74</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3044</v>
+        <v>-0.2865</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.8276</v>
+        <v>-8.3085</v>
       </c>
     </row>
     <row r="311">
@@ -16675,10 +16675,10 @@
         <v>0.59</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4405</v>
+        <v>-0.4339</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.7745</v>
+        <v>-12.5831</v>
       </c>
     </row>
     <row r="312">
@@ -16715,10 +16715,10 @@
         <v>1.4</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9507</v>
+        <v>0.9395</v>
       </c>
       <c r="J312" t="n">
-        <v>26.6196</v>
+        <v>26.306</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.26</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6725</v>
+        <v>0.6412</v>
       </c>
       <c r="J313" t="n">
-        <v>18.83</v>
+        <v>17.9536</v>
       </c>
     </row>
     <row r="314">
@@ -16795,10 +16795,10 @@
         <v>1.18</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5028</v>
+        <v>0.4678</v>
       </c>
       <c r="J314" t="n">
-        <v>14.0784</v>
+        <v>13.0984</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>1.1</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3115</v>
+        <v>0.2785</v>
       </c>
       <c r="J315" t="n">
-        <v>8.722</v>
+        <v>7.798</v>
       </c>
     </row>
     <row r="316">
@@ -16875,10 +16875,10 @@
         <v>1.02</v>
       </c>
       <c r="I316" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0529</v>
       </c>
       <c r="J316" t="n">
-        <v>1.932</v>
+        <v>1.4812</v>
       </c>
     </row>
     <row r="317">
@@ -16915,10 +16915,10 @@
         <v>1.17</v>
       </c>
       <c r="I317" t="n">
-        <v>0.396</v>
+        <v>0.3404</v>
       </c>
       <c r="J317" t="n">
-        <v>11.088</v>
+        <v>9.5312</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.11</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2841</v>
+        <v>0.2347</v>
       </c>
       <c r="J318" t="n">
-        <v>7.9548</v>
+        <v>6.5716</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0951</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.6628</v>
+        <v>-2.2316</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>0.88</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1642</v>
+        <v>-0.1447</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.5976</v>
+        <v>-4.0516</v>
       </c>
     </row>
     <row r="321">
@@ -17075,10 +17075,10 @@
         <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4234</v>
+        <v>-0.415</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.8552</v>
+        <v>-11.62</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>3.01</v>
       </c>
       <c r="I322" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J322" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>1.61</v>
       </c>
       <c r="I323" t="n">
-        <v>1.184</v>
+        <v>1.2095</v>
       </c>
       <c r="J323" t="n">
-        <v>20.128</v>
+        <v>20.5615</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>1.41</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8963</v>
+        <v>0.8964</v>
       </c>
       <c r="J324" t="n">
-        <v>15.2371</v>
+        <v>15.2388</v>
       </c>
     </row>
     <row r="325">
@@ -17235,10 +17235,10 @@
         <v>1.31</v>
       </c>
       <c r="I325" t="n">
-        <v>0.7042</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J325" t="n">
-        <v>11.9714</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="326">
@@ -17275,10 +17275,10 @@
         <v>1.28</v>
       </c>
       <c r="I326" t="n">
-        <v>0.6437</v>
+        <v>0.6218</v>
       </c>
       <c r="J326" t="n">
-        <v>10.9429</v>
+        <v>10.5706</v>
       </c>
     </row>
     <row r="327">
@@ -17315,10 +17315,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.2718</v>
+        <v>-0.2538</v>
       </c>
       <c r="J327" t="n">
-        <v>-4.6206</v>
+        <v>-4.3146</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>0.67</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2934</v>
+        <v>-0.2783</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.9878</v>
+        <v>-4.7311</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>0.37</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.5729</v>
+        <v>-0.5799</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.7393</v>
+        <v>-9.8583</v>
       </c>
     </row>
     <row r="330">
@@ -17435,10 +17435,10 @@
         <v>0.35</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5911</v>
+        <v>-0.6002</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.0487</v>
+        <v>-10.2034</v>
       </c>
     </row>
     <row r="331">
@@ -17475,10 +17475,10 @@
         <v>0.26</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6741</v>
+        <v>-0.6965</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.4597</v>
+        <v>-11.8405</v>
       </c>
     </row>
     <row r="332">
@@ -17515,10 +17515,10 @@
         <v>1.09</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2699</v>
+        <v>0.2242</v>
       </c>
       <c r="J332" t="n">
-        <v>5.9378</v>
+        <v>4.9324</v>
       </c>
     </row>
     <row r="333">
@@ -17555,10 +17555,10 @@
         <v>0.95</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.0733</v>
+        <v>-0.0612</v>
       </c>
       <c r="J333" t="n">
-        <v>-1.6126</v>
+        <v>-1.3464</v>
       </c>
     </row>
     <row r="334">
@@ -17595,10 +17595,10 @@
         <v>0.88</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1575</v>
+        <v>-0.1406</v>
       </c>
       <c r="J334" t="n">
-        <v>-3.465</v>
+        <v>-3.0932</v>
       </c>
     </row>
     <row r="335">
@@ -17635,10 +17635,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.342</v>
+        <v>-0.3263</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.524</v>
+        <v>-7.1786</v>
       </c>
     </row>
     <row r="336">
@@ -17675,10 +17675,10 @@
         <v>0.63</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3964</v>
+        <v>-0.3847</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.720800000000001</v>
+        <v>-8.4634</v>
       </c>
     </row>
     <row r="337">
@@ -17715,10 +17715,10 @@
         <v>1.65</v>
       </c>
       <c r="I337" t="n">
-        <v>1.2731</v>
+        <v>1.2912</v>
       </c>
       <c r="J337" t="n">
-        <v>28.0082</v>
+        <v>28.4064</v>
       </c>
     </row>
     <row r="338">
@@ -17755,10 +17755,10 @@
         <v>1.52</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1046</v>
+        <v>1.1178</v>
       </c>
       <c r="J338" t="n">
-        <v>24.3012</v>
+        <v>24.5916</v>
       </c>
     </row>
     <row r="339">
@@ -17795,10 +17795,10 @@
         <v>1.33</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7922</v>
+        <v>0.7745</v>
       </c>
       <c r="J339" t="n">
-        <v>17.4284</v>
+        <v>17.039</v>
       </c>
     </row>
     <row r="340">
@@ -17835,10 +17835,10 @@
         <v>1.18</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4805</v>
+        <v>0.4503</v>
       </c>
       <c r="J340" t="n">
-        <v>10.571</v>
+        <v>9.906599999999999</v>
       </c>
     </row>
     <row r="341">
@@ -17875,10 +17875,10 @@
         <v>1.06</v>
       </c>
       <c r="I341" t="n">
-        <v>0.1753</v>
+        <v>0.147</v>
       </c>
       <c r="J341" t="n">
-        <v>3.8566</v>
+        <v>3.234</v>
       </c>
     </row>
     <row r="342">
@@ -17915,10 +17915,10 @@
         <v>1.16</v>
       </c>
       <c r="I342" t="n">
-        <v>0.3882</v>
+        <v>0.3338</v>
       </c>
       <c r="J342" t="n">
-        <v>11.646</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="343">
@@ -17955,10 +17955,10 @@
         <v>0.93</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1052</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J343" t="n">
-        <v>-3.156</v>
+        <v>-2.697</v>
       </c>
     </row>
     <row r="344">
@@ -17995,10 +17995,10 @@
         <v>0.84</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2033</v>
+        <v>-0.1835</v>
       </c>
       <c r="J344" t="n">
-        <v>-6.099</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="345">
@@ -18035,10 +18035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2336</v>
+        <v>-0.2138</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.008</v>
+        <v>-6.414</v>
       </c>
     </row>
     <row r="346">
@@ -18075,10 +18075,10 @@
         <v>0.79</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2534</v>
+        <v>-0.2338</v>
       </c>
       <c r="J346" t="n">
-        <v>-7.602</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="347">
@@ -18115,10 +18115,10 @@
         <v>1.32</v>
       </c>
       <c r="I347" t="n">
-        <v>0.7992</v>
+        <v>0.7739</v>
       </c>
       <c r="J347" t="n">
-        <v>23.976</v>
+        <v>23.217</v>
       </c>
     </row>
     <row r="348">
@@ -18155,10 +18155,10 @@
         <v>1.27</v>
       </c>
       <c r="I348" t="n">
-        <v>0.6969</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J348" t="n">
-        <v>20.907</v>
+        <v>19.974</v>
       </c>
     </row>
     <row r="349">
@@ -18195,10 +18195,10 @@
         <v>1.14</v>
       </c>
       <c r="I349" t="n">
-        <v>0.4139</v>
+        <v>0.3782</v>
       </c>
       <c r="J349" t="n">
-        <v>12.417</v>
+        <v>11.346</v>
       </c>
     </row>
     <row r="350">
@@ -18235,10 +18235,10 @@
         <v>1.07</v>
       </c>
       <c r="I350" t="n">
-        <v>0.2334</v>
+        <v>0.2031</v>
       </c>
       <c r="J350" t="n">
-        <v>7.002</v>
+        <v>6.093</v>
       </c>
     </row>
     <row r="351">
@@ -18275,10 +18275,10 @@
         <v>1.06</v>
       </c>
       <c r="I351" t="n">
-        <v>0.2044</v>
+        <v>0.1758</v>
       </c>
       <c r="J351" t="n">
-        <v>6.132</v>
+        <v>5.274</v>
       </c>
     </row>
     <row r="352">
@@ -18315,10 +18315,10 @@
         <v>1.42</v>
       </c>
       <c r="I352" t="n">
-        <v>0.9764</v>
+        <v>0.97</v>
       </c>
       <c r="J352" t="n">
-        <v>26.3628</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="353">
@@ -18355,10 +18355,10 @@
         <v>1.38</v>
       </c>
       <c r="I353" t="n">
-        <v>0.9035</v>
+        <v>0.8878</v>
       </c>
       <c r="J353" t="n">
-        <v>24.3945</v>
+        <v>23.9706</v>
       </c>
     </row>
     <row r="354">
@@ -18395,10 +18395,10 @@
         <v>1.29</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7266</v>
+        <v>0.6998</v>
       </c>
       <c r="J354" t="n">
-        <v>19.6182</v>
+        <v>18.8946</v>
       </c>
     </row>
     <row r="355">
@@ -18435,10 +18435,10 @@
         <v>1.08</v>
       </c>
       <c r="I355" t="n">
-        <v>0.2507</v>
+        <v>0.2202</v>
       </c>
       <c r="J355" t="n">
-        <v>6.7689</v>
+        <v>5.9454</v>
       </c>
     </row>
     <row r="356">
@@ -18475,10 +18475,10 @@
         <v>1.01</v>
       </c>
       <c r="I356" t="n">
-        <v>0.02</v>
+        <v>0.0101</v>
       </c>
       <c r="J356" t="n">
-        <v>0.54</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="357">
@@ -18515,10 +18515,10 @@
         <v>1.13</v>
       </c>
       <c r="I357" t="n">
-        <v>0.3424</v>
+        <v>0.2912</v>
       </c>
       <c r="J357" t="n">
-        <v>9.2448</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="358">
@@ -18555,10 +18555,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.18</v>
+        <v>-0.1615</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.86</v>
+        <v>-4.3605</v>
       </c>
     </row>
     <row r="359">
@@ -18595,10 +18595,10 @@
         <v>0.83</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.6835</v>
+        <v>-5.1624</v>
       </c>
     </row>
     <row r="360">
@@ -18635,10 +18635,10 @@
         <v>0.8</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2403</v>
+        <v>-0.2209</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.4881</v>
+        <v>-5.9643</v>
       </c>
     </row>
     <row r="361">
@@ -18675,10 +18675,10 @@
         <v>0.74</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.298</v>
+        <v>-0.28</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.045999999999999</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="362">
@@ -18715,10 +18715,10 @@
         <v>1.63</v>
       </c>
       <c r="I362" t="n">
-        <v>1.271</v>
+        <v>1.2892</v>
       </c>
       <c r="J362" t="n">
-        <v>33.046</v>
+        <v>33.5192</v>
       </c>
     </row>
     <row r="363">
@@ -18755,10 +18755,10 @@
         <v>1.27</v>
       </c>
       <c r="I363" t="n">
-        <v>0.6866</v>
+        <v>0.658</v>
       </c>
       <c r="J363" t="n">
-        <v>17.8516</v>
+        <v>17.108</v>
       </c>
     </row>
     <row r="364">
@@ -18795,10 +18795,10 @@
         <v>1.22</v>
       </c>
       <c r="I364" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J364" t="n">
-        <v>15.197</v>
+        <v>14.3728</v>
       </c>
     </row>
     <row r="365">
@@ -18835,10 +18835,10 @@
         <v>1.2</v>
       </c>
       <c r="I365" t="n">
-        <v>0.5417</v>
+        <v>0.5093</v>
       </c>
       <c r="J365" t="n">
-        <v>14.0842</v>
+        <v>13.2418</v>
       </c>
     </row>
     <row r="366">
@@ -18875,10 +18875,10 @@
         <v>0.85</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.513</v>
+        <v>-0.4748</v>
       </c>
       <c r="J366" t="n">
-        <v>-13.338</v>
+        <v>-12.3448</v>
       </c>
     </row>
     <row r="367">
@@ -18915,10 +18915,10 @@
         <v>1.08</v>
       </c>
       <c r="I367" t="n">
-        <v>0.2332</v>
+        <v>0.1886</v>
       </c>
       <c r="J367" t="n">
-        <v>6.0632</v>
+        <v>4.9036</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>0.98</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0354</v>
+        <v>-0.0276</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.9204</v>
+        <v>-0.7176</v>
       </c>
     </row>
     <row r="369">
@@ -18995,10 +18995,10 @@
         <v>0.92</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1169</v>
+        <v>-0.1008</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.0394</v>
+        <v>-2.6208</v>
       </c>
     </row>
     <row r="370">
@@ -19035,10 +19035,10 @@
         <v>0.86</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1822</v>
+        <v>-0.1629</v>
       </c>
       <c r="J370" t="n">
-        <v>-4.7372</v>
+        <v>-4.2354</v>
       </c>
     </row>
     <row r="371">
@@ -19075,10 +19075,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3659</v>
+        <v>-0.3519</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.513400000000001</v>
+        <v>-9.1494</v>
       </c>
     </row>
     <row r="372">
@@ -19115,10 +19115,10 @@
         <v>1.61</v>
       </c>
       <c r="I372" t="n">
-        <v>1.2319</v>
+        <v>1.248</v>
       </c>
       <c r="J372" t="n">
-        <v>28.3337</v>
+        <v>28.704</v>
       </c>
     </row>
     <row r="373">
@@ -19155,10 +19155,10 @@
         <v>1.44</v>
       </c>
       <c r="I373" t="n">
-        <v>0.9987</v>
+        <v>0.9976</v>
       </c>
       <c r="J373" t="n">
-        <v>22.9701</v>
+        <v>22.9448</v>
       </c>
     </row>
     <row r="374">
@@ -19195,10 +19195,10 @@
         <v>1.23</v>
       </c>
       <c r="I374" t="n">
-        <v>0.5982</v>
+        <v>0.5697</v>
       </c>
       <c r="J374" t="n">
-        <v>13.7586</v>
+        <v>13.1031</v>
       </c>
     </row>
     <row r="375">
@@ -19235,10 +19235,10 @@
         <v>1.1</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2949</v>
+        <v>0.2634</v>
       </c>
       <c r="J375" t="n">
-        <v>6.7827</v>
+        <v>6.0582</v>
       </c>
     </row>
     <row r="376">
@@ -19275,10 +19275,10 @@
         <v>1.09</v>
       </c>
       <c r="I376" t="n">
-        <v>0.2684</v>
+        <v>0.2374</v>
       </c>
       <c r="J376" t="n">
-        <v>6.1732</v>
+        <v>5.4602</v>
       </c>
     </row>
     <row r="377">
@@ -19315,10 +19315,10 @@
         <v>1.03</v>
       </c>
       <c r="I377" t="n">
-        <v>0.149</v>
+        <v>0.1196</v>
       </c>
       <c r="J377" t="n">
-        <v>3.427</v>
+        <v>2.7508</v>
       </c>
     </row>
     <row r="378">
@@ -19355,10 +19355,10 @@
         <v>1.03</v>
       </c>
       <c r="I378" t="n">
-        <v>0.149</v>
+        <v>0.1196</v>
       </c>
       <c r="J378" t="n">
-        <v>3.427</v>
+        <v>2.7508</v>
       </c>
     </row>
     <row r="379">
@@ -19395,10 +19395,10 @@
         <v>0.89</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1397</v>
+        <v>-0.1244</v>
       </c>
       <c r="J379" t="n">
-        <v>-3.2131</v>
+        <v>-2.8612</v>
       </c>
     </row>
     <row r="380">
@@ -19435,10 +19435,10 @@
         <v>0.52</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4874</v>
+        <v>-0.4848</v>
       </c>
       <c r="J380" t="n">
-        <v>-11.2102</v>
+        <v>-11.1504</v>
       </c>
     </row>
     <row r="381">
@@ -19475,10 +19475,10 @@
         <v>0.49</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5134</v>
+        <v>-0.5142</v>
       </c>
       <c r="J381" t="n">
-        <v>-11.8082</v>
+        <v>-11.8266</v>
       </c>
     </row>
     <row r="382">
@@ -19515,10 +19515,10 @@
         <v>1.99</v>
       </c>
       <c r="I382" t="n">
-        <v>1.651</v>
+        <v>1.6942</v>
       </c>
       <c r="J382" t="n">
-        <v>33.02</v>
+        <v>33.884</v>
       </c>
     </row>
     <row r="383">
@@ -19555,10 +19555,10 @@
         <v>1.67</v>
       </c>
       <c r="I383" t="n">
-        <v>1.2712</v>
+        <v>1.2926</v>
       </c>
       <c r="J383" t="n">
-        <v>25.424</v>
+        <v>25.852</v>
       </c>
     </row>
     <row r="384">
@@ -19595,10 +19595,10 @@
         <v>1.6</v>
       </c>
       <c r="I384" t="n">
-        <v>1.1852</v>
+        <v>1.2048</v>
       </c>
       <c r="J384" t="n">
-        <v>23.704</v>
+        <v>24.096</v>
       </c>
     </row>
     <row r="385">
@@ -19635,10 +19635,10 @@
         <v>1.51</v>
       </c>
       <c r="I385" t="n">
-        <v>1.0737</v>
+        <v>1.0911</v>
       </c>
       <c r="J385" t="n">
-        <v>21.474</v>
+        <v>21.822</v>
       </c>
     </row>
     <row r="386">
@@ -19675,10 +19675,10 @@
         <v>0.88</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4804</v>
+        <v>-0.4506</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.608000000000001</v>
+        <v>-9.012</v>
       </c>
     </row>
     <row r="387">
@@ -19715,10 +19715,10 @@
         <v>0.68</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.3125</v>
+        <v>-0.3021</v>
       </c>
       <c r="J387" t="n">
-        <v>-6.25</v>
+        <v>-6.042</v>
       </c>
     </row>
     <row r="388">
@@ -19755,10 +19755,10 @@
         <v>0.61</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3792</v>
+        <v>-0.3727</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.584</v>
+        <v>-7.454</v>
       </c>
     </row>
     <row r="389">
@@ -19795,10 +19795,10 @@
         <v>0.52</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.456</v>
+        <v>-0.4519</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.038</v>
       </c>
     </row>
     <row r="390">
@@ -19835,10 +19835,10 @@
         <v>0.5</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4733</v>
+        <v>-0.4701</v>
       </c>
       <c r="J390" t="n">
-        <v>-9.465999999999999</v>
+        <v>-9.401999999999999</v>
       </c>
     </row>
     <row r="391">
@@ -19875,10 +19875,10 @@
         <v>0.47</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4996</v>
+        <v>-0.4983</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.992000000000001</v>
+        <v>-9.965999999999999</v>
       </c>
     </row>
     <row r="392">
@@ -19915,10 +19915,10 @@
         <v>1.56</v>
       </c>
       <c r="I392" t="n">
-        <v>1.159</v>
+        <v>1.1732</v>
       </c>
       <c r="J392" t="n">
-        <v>26.657</v>
+        <v>26.9836</v>
       </c>
     </row>
     <row r="393">
@@ -19955,10 +19955,10 @@
         <v>1.46</v>
       </c>
       <c r="I393" t="n">
-        <v>1.0232</v>
+        <v>1.0273</v>
       </c>
       <c r="J393" t="n">
-        <v>23.5336</v>
+        <v>23.6279</v>
       </c>
     </row>
     <row r="394">
@@ -19995,10 +19995,10 @@
         <v>1.31</v>
       </c>
       <c r="I394" t="n">
-        <v>0.755</v>
+        <v>0.7348</v>
       </c>
       <c r="J394" t="n">
-        <v>17.365</v>
+        <v>16.9004</v>
       </c>
     </row>
     <row r="395">
@@ -20035,10 +20035,10 @@
         <v>1.29</v>
       </c>
       <c r="I395" t="n">
-        <v>0.7157</v>
+        <v>0.6936</v>
       </c>
       <c r="J395" t="n">
-        <v>16.4611</v>
+        <v>15.9528</v>
       </c>
     </row>
     <row r="396">
@@ -20075,10 +20075,10 @@
         <v>1.06</v>
       </c>
       <c r="I396" t="n">
-        <v>0.1772</v>
+        <v>0.149</v>
       </c>
       <c r="J396" t="n">
-        <v>4.0756</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="397">
@@ -20115,10 +20115,10 @@
         <v>1.44</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9008</v>
+        <v>0.8798</v>
       </c>
       <c r="J397" t="n">
-        <v>20.7184</v>
+        <v>20.2354</v>
       </c>
     </row>
     <row r="398">
@@ -20155,10 +20155,10 @@
         <v>0.85</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.1853</v>
+        <v>-0.1685</v>
       </c>
       <c r="J398" t="n">
-        <v>-4.2619</v>
+        <v>-3.8755</v>
       </c>
     </row>
     <row r="399">
@@ -20195,10 +20195,10 @@
         <v>0.68</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.3466</v>
+        <v>-0.3313</v>
       </c>
       <c r="J399" t="n">
-        <v>-7.9718</v>
+        <v>-7.6199</v>
       </c>
     </row>
     <row r="400">
@@ -20235,10 +20235,10 @@
         <v>0.62</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4008</v>
+        <v>-0.3893</v>
       </c>
       <c r="J400" t="n">
-        <v>-9.218400000000001</v>
+        <v>-8.953900000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20275,10 +20275,10 @@
         <v>0.44</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5577</v>
+        <v>-0.5652</v>
       </c>
       <c r="J401" t="n">
-        <v>-12.8271</v>
+        <v>-12.9996</v>
       </c>
     </row>
     <row r="402">
@@ -20315,10 +20315,10 @@
         <v>1.4</v>
       </c>
       <c r="I402" t="n">
-        <v>0.7532</v>
+        <v>0.6995</v>
       </c>
       <c r="J402" t="n">
-        <v>21.8428</v>
+        <v>20.2855</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.08</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J403" t="n">
-        <v>6.1886</v>
+        <v>4.9532</v>
       </c>
     </row>
     <row r="404">
@@ -20395,10 +20395,10 @@
         <v>0.85</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2009</v>
+        <v>-0.1803</v>
       </c>
       <c r="J404" t="n">
-        <v>-5.8261</v>
+        <v>-5.2287</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>0.83</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2217</v>
+        <v>-0.2011</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.4293</v>
+        <v>-5.8319</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2419</v>
+        <v>-0.2217</v>
       </c>
       <c r="J406" t="n">
-        <v>-7.0151</v>
+        <v>-6.4293</v>
       </c>
     </row>
     <row r="407">
@@ -20515,10 +20515,10 @@
         <v>1.34</v>
       </c>
       <c r="I407" t="n">
-        <v>0.8661</v>
+        <v>0.845</v>
       </c>
       <c r="J407" t="n">
-        <v>25.1169</v>
+        <v>24.505</v>
       </c>
     </row>
     <row r="408">
@@ -20555,10 +20555,10 @@
         <v>1.22</v>
       </c>
       <c r="I408" t="n">
-        <v>0.6111</v>
+        <v>0.5733</v>
       </c>
       <c r="J408" t="n">
-        <v>17.7219</v>
+        <v>16.6257</v>
       </c>
     </row>
     <row r="409">
@@ -20595,10 +20595,10 @@
         <v>1.09</v>
       </c>
       <c r="I409" t="n">
-        <v>0.301</v>
+        <v>0.2637</v>
       </c>
       <c r="J409" t="n">
-        <v>8.728999999999999</v>
+        <v>7.6473</v>
       </c>
     </row>
     <row r="410">
@@ -20635,10 +20635,10 @@
         <v>0.96</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.1826</v>
+        <v>-0.1485</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.2954</v>
+        <v>-4.3065</v>
       </c>
     </row>
     <row r="411">
@@ -20675,10 +20675,10 @@
         <v>0.77</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.6711</v>
+        <v>-0.6373</v>
       </c>
       <c r="J411" t="n">
-        <v>-19.4619</v>
+        <v>-18.4817</v>
       </c>
     </row>
     <row r="412">
@@ -20715,10 +20715,10 @@
         <v>1.41</v>
       </c>
       <c r="I412" t="n">
-        <v>0.9802</v>
+        <v>0.9734</v>
       </c>
       <c r="J412" t="n">
-        <v>27.4456</v>
+        <v>27.2552</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.18</v>
       </c>
       <c r="I413" t="n">
-        <v>0.5077</v>
+        <v>0.4703</v>
       </c>
       <c r="J413" t="n">
-        <v>14.2156</v>
+        <v>13.1684</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>1.17</v>
       </c>
       <c r="I414" t="n">
-        <v>0.4852</v>
+        <v>0.4477</v>
       </c>
       <c r="J414" t="n">
-        <v>13.5856</v>
+        <v>12.5356</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.09</v>
       </c>
       <c r="I415" t="n">
-        <v>0.2925</v>
+        <v>0.2588</v>
       </c>
       <c r="J415" t="n">
-        <v>8.19</v>
+        <v>7.2464</v>
       </c>
     </row>
     <row r="416">
@@ -20875,10 +20875,10 @@
         <v>0.88</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.4226</v>
+        <v>-0.3806</v>
       </c>
       <c r="J416" t="n">
-        <v>-11.8328</v>
+        <v>-10.6568</v>
       </c>
     </row>
     <row r="417">
@@ -20915,10 +20915,10 @@
         <v>1.3</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6088</v>
+        <v>0.5513</v>
       </c>
       <c r="J417" t="n">
-        <v>17.0464</v>
+        <v>15.4364</v>
       </c>
     </row>
     <row r="418">
@@ -20955,10 +20955,10 @@
         <v>0.99</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.0232</v>
+        <v>-0.0171</v>
       </c>
       <c r="J418" t="n">
-        <v>-0.6496</v>
+        <v>-0.4788</v>
       </c>
     </row>
     <row r="419">
@@ -20995,10 +20995,10 @@
         <v>0.95</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.0834</v>
+        <v>-0.0687</v>
       </c>
       <c r="J419" t="n">
-        <v>-2.3352</v>
+        <v>-1.9236</v>
       </c>
     </row>
     <row r="420">
@@ -21035,10 +21035,10 @@
         <v>0.87</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.1768</v>
+        <v>-0.1567</v>
       </c>
       <c r="J420" t="n">
-        <v>-4.9504</v>
+        <v>-4.3876</v>
       </c>
     </row>
     <row r="421">
@@ -21075,10 +21075,10 @@
         <v>0.7</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3442</v>
+        <v>-0.3289</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.637600000000001</v>
+        <v>-9.209199999999999</v>
       </c>
     </row>
   </sheetData>
